--- a/source_status.xlsx
+++ b/source_status.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
     </row>
@@ -866,12 +866,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Herencias en Florida: la nueva ley firmada por DeSantis que reduce trámites judiciales desde el 1° de julio</t>
+          <t>La empresa del crucero en el que se registró un brote de hantavirus emitió un comunicado</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/estados-unidos/florida/herencias-en-florida-la-nueva-ley-firmada-por-desantis-que-reduce-tramites-judiciales-desde-el-1-de-nid04052026/</t>
+          <t>https://www.lanacion.com.ar/sociedad/la-empresa-del-crucero-en-el-que-se-registro-un-brote-de-hantavirus-emitio-un-comunicado-nid04052026/</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>El gobernador de Florida, Ron DeSantis, firmó la ley HB 1337; conoce los detalles de la norma, que reduce trámites judiciales para herencias, aumenta límites de bienes y entra en vigor el 1° de julio.</t>
+          <t>La compañía neerlandesa Oceanwide Expeditions informó que hay un pasajero en terapia intensiva y dos tripulantes que requirieron atención urgente</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>La empresa del crucero en el que se registró un brote de hantavirus emitió un comunicado</t>
+          <t>Los secretos detrás del emblemático modelo de los 70 que enamoró a los argentinos</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/sociedad/la-empresa-del-crucero-en-el-que-se-registro-un-brote-de-hantavirus-emitio-un-comunicado-nid04052026/</t>
+          <t>https://www.lanacion.com.ar/autos/los-secretos-detras-del-emblematico-modelo-de-los-70-que-enamoro-a-los-argentinos-nid03052026/</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -923,19 +923,19 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>La compañía neerlandesa Oceanwide Expeditions informó que hay un pasajero en terapia intensiva y dos tripulantes que requirieron atención urgente</t>
+          <t>Este modelo argentino logró cruzar la línea de llegada de las 84 Horas de Nürburgring, una carrera de resistencia que tomó lugar en Alemania en 1969</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Los secretos detrás del emblemático modelo de los 70 que enamoró a los argentinos</t>
+          <t>Las razones por las que en tan poco tiempo la industria automotriz china revolucionó al mercado mundial</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/autos/los-secretos-detras-del-emblematico-modelo-de-los-70-que-enamoro-a-los-argentinos-nid03052026/</t>
+          <t>https://www.lanacion.com.ar/autos/las-razones-por-las-que-en-tan-poco-tiempo-la-industria-automotriz-china-revoluciono-al-mercado-nid28042026/</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -955,19 +955,19 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Este modelo argentino logró cruzar la línea de llegada de las 84 Horas de Nürburgring, una carrera de resistencia que tomó lugar en Alemania en 1969</t>
+          <t>China es hoy el mayor productor y exportador de vehículos en el mundo, asimismo, su mercado local acompaña estas cifras</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Las razones por las que en tan poco tiempo la industria automotriz china revolucionó al mercado mundial</t>
+          <t>Un especialista revela qué hacer si te cruzan un auto para robarte: la maniobra clave para escapar</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/autos/las-razones-por-las-que-en-tan-poco-tiempo-la-industria-automotriz-china-revoluciono-al-mercado-nid28042026/</t>
+          <t>https://www.lanacion.com.ar/autos/un-especialista-revela-que-hacer-si-te-cruzan-un-auto-para-robarte-la-maniobra-clave-para-escapar-nid23042026/</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -987,19 +987,19 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>China es hoy el mayor productor y exportador de vehículos en el mundo, asimismo, su mercado local acompaña estas cifras</t>
+          <t>El avance de la inseguridad  obliga a repensar la conducción defensiva; un instructor especializado explica paso a paso cómo reaccionar y qué errores evitar</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Un especialista revela qué hacer si te cruzan un auto para robarte: la maniobra clave para escapar</t>
+          <t>Cómo es el nuevo modelo de una automotriz alemana del que vendió 20 millones de unidades en el mundo</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/autos/un-especialista-revela-que-hacer-si-te-cruzan-un-auto-para-robarte-la-maniobra-clave-para-escapar-nid23042026/</t>
+          <t>https://www.lanacion.com.ar/autos/como-es-el-nuevo-modelo-de-una-automotriz-alemana-del-que-vendio-20-millones-de-unidades-en-el-mundo-nid02052026/</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1019,19 +1019,19 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>El avance de la inseguridad  obliga a repensar la conducción defensiva; un instructor especializado explica paso a paso cómo reaccionar y qué errores evitar</t>
+          <t>Volkswagen presentó en Alemania la evolución del Polo,; sus características y precio</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Cómo es el nuevo modelo de una automotriz alemana del que vendió 20 millones de unidades en el mundo</t>
+          <t>Por qué algunas casas antiguas tienen puertas muy altas: la historia detrás del diseño</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/autos/como-es-el-nuevo-modelo-de-una-automotriz-alemana-del-que-vendio-20-millones-de-unidades-en-el-mundo-nid02052026/</t>
+          <t>https://www.lanacion.com.ar/propiedades/por-que-algunas-casas-antiguas-tienen-puertas-muy-altas-la-historia-detras-del-diseno-nid29042026/</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1051,19 +1051,19 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Volkswagen presentó en Alemania la evolución del Polo,; sus características y precio</t>
+          <t>La arquitectura porteña de fines del siglo XIX y comienzos del XX privilegiaba los ambientes grandes para regular la temperatura y favorecer la circulación del aire</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Por qué algunas casas antiguas tienen puertas muy altas: la historia detrás del diseño</t>
+          <t>El rumbo y la matriz productiva del crecimiento argentino</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/propiedades/por-que-algunas-casas-antiguas-tienen-puertas-muy-altas-la-historia-detras-del-diseno-nid29042026/</t>
+          <t>https://www.lanacion.com.ar/opinion/el-rumbo-y-la-matriz-productiva-del-crecimiento-argentino-nid04052026/</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1083,19 +1083,19 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>La arquitectura porteña de fines del siglo XIX y comienzos del XX privilegiaba los ambientes grandes para regular la temperatura y favorecer la circulación del aire</t>
+          <t>El país necesita consolidar la estabilidad sobre sus ventajas comparativas y liberar su potencial como productor y exportador</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>El rumbo y la matriz productiva del crecimiento argentino</t>
+          <t>Construyeron un rascacielos de 200 metros de altura y se olvidaron el hueco del ascensor</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/opinion/el-rumbo-y-la-matriz-productiva-del-crecimiento-argentino-nid04052026/</t>
+          <t>https://www.lanacion.com.ar/propiedades/construccion-y-diseno/insolito-construyeron-un-rascacielos-de-200-metros-de-altura-y-se-olvidaron-el-hueco-del-ascensor-nid30042026/</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1115,19 +1115,19 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>El país necesita consolidar la estabilidad sobre sus ventajas comparativas y liberar su potencial como productor y exportador</t>
+          <t>Benidorm es la segunda ciudad del mundo con más rascacielos por habitante</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Construyeron un rascacielos de 200 metros de altura y se olvidaron el hueco del ascensor</t>
+          <t>La agenda de la TV del lunes: se completa la fecha del Apertura, la Premier League y la Serie A</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/propiedades/construccion-y-diseno/insolito-construyeron-un-rascacielos-de-200-metros-de-altura-y-se-olvidaron-el-hueco-del-ascensor-nid30042026/</t>
+          <t>https://www.lanacion.com.ar/deportes/futbol/la-agenda-de-la-tv-del-lunes-se-completa-la-fecha-del-apertura-la-premier-league-y-la-serie-a-nid03052026/</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1147,19 +1147,19 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Benidorm es la segunda ciudad del mundo con más rascacielos por habitante</t>
+          <t>La actividad deportiva en el inicio de la semana, disponible a través de las pantallas</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>La agenda de la TV del lunes: se completa la fecha del Apertura, la Premier League y la Serie A</t>
+          <t>Federico Sturzenegger confirmó que en junio enviará la desregulación inmobiliaria al Congreso para bajar costos en la compraventa</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/deportes/futbol/la-agenda-de-la-tv-del-lunes-se-completa-la-fecha-del-apertura-la-premier-league-y-la-serie-a-nid03052026/</t>
+          <t>https://www.lanacion.com.ar/propiedades/casas-y-departamentos/federico-sturzenegger-confirmo-que-en-junio-enviara-la-desregulacion-inmobiliaria-al-congreso-para-nid28042026/</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1179,19 +1179,19 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>La actividad deportiva en el inicio de la semana, disponible a través de las pantallas</t>
+          <t>Frente a desarrolladores e inmobiliarios, el ministro cuestionó el rol actual de los colegios inmobiliarios y retomó la idea de desregular la actividad</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Federico Sturzenegger confirmó que en junio enviará la desregulación inmobiliaria al Congreso para bajar costos en la compraventa</t>
+          <t>El derrumbe de la recaudación propia y de la coparticipación bonaerense pone en alerta a los municipios</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/propiedades/casas-y-departamentos/federico-sturzenegger-confirmo-que-en-junio-enviara-la-desregulacion-inmobiliaria-al-congreso-para-nid28042026/</t>
+          <t>https://www.lanacion.com.ar/politica/el-derrumbe-de-la-recaudacion-propia-y-de-la-coparticipacion-bonaerense-pone-en-alerta-a-los-nid03052026/</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1211,19 +1211,19 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Frente a desarrolladores e inmobiliarios, el ministro cuestionó el rol actual de los colegios inmobiliarios y retomó la idea de desregular la actividad</t>
+          <t>Los fondos por tasas y los que llegan desde el gobierno provincial se redujeron; en algunas intendencias afirman que se postergan gastos con el objetivo de garantizar prestaciones salariales y sociales</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Agendalo en tu calendario: las fechas clave para ahorrar dólares en tus compras al exterior</t>
+          <t>Intercambiá tu casa para no gastar dólares en alojamiento: cómo funciona esta propuesta</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/agendalo-tu-calendario-las-fechas-clave-ahorrar-dolares-tus-compras-al-exterior-n6271788</t>
+          <t>https://www.ambito.com/economia/intercambia-tu-casa-no-gastar-dolares-alojamiento-como-funciona-esta-propuesta-n6272776</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1238,24 +1238,24 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Si estás pensando en realizar consumos internacionales, antes vas a tener que conocer estos días que te pueden favorecer.</t>
+          <t>Una alternativa distinta para el turismo reduce los costos y abre las puertas a experiencias únicas en distintos destinos.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Referentes de la economía del conocimiento destacaron el potencial de Argentina en IA: "Siempre se diferencia por calidad"</t>
+          <t>Scott Bessent prevé una caída del petróleo tras el conflicto en Medio Oriente, pese al fuerte salto de los precios</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/referentes-la-del-conocimiento-destacaron-el-potencial-argentina-ia-siempre-se-diferencia-calidad-n6272370</t>
+          <t>https://www.ambito.com/economia/scott-bessent-preve-una-caida-del-petroleo-el-conflicto-medio-oriente-pese-al-fuerte-salto-los-precios-n6273376</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>En el marco de la Expo EFI, representantes del sector destacaron las ventajas comparativas que tiene el país y expusieron las habilidades que solicitará el mercado laboral: "No vamos a necesitar meros contadores, sino contadores tecnológicos".</t>
+          <t>El secretario del Tesoro de EEUU aseguró que la suba actual de la energía es transitoria y anticipó una baja cuando se normalice la situación. Mientras tanto, el petróleo y la gasolina siguen en niveles elevados por el impacto del conflicto con Irán.</t>
         </is>
       </c>
     </row>
@@ -3394,12 +3394,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Descuentos Cuenta DNI: todo lo que tenés que saber para ahorrar este lunes 27 de abril</t>
+          <t>La industria de China aumentó sus ganancias empresarias a pesar de la guerra en Medio Oriente</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/descuentos-cuenta-dni-todo-lo-que-tenes-que-saber-ahorrar-este-lunes-27-abril-n6270081</t>
+          <t>https://www.ambito.com/economia/la-industria-china-aumento-sus-ganancias-empresarias-pesar-la-guerra-medio-oriente-n6271308</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -3419,19 +3419,19 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>La billetera virtual del Banco Provincia suma beneficios en supermercados, carnicerías, comercios de cercanía, marcas seleccionadas, ferias y librerías.</t>
+          <t>Los datos oficiales mostraron que las ganas industriales crecieron a su mejor ritmo en seis meses. Sin embargo, el riesgo de un impacto de la guerra sobre el entramado productivo chino sigue latente.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>La industria de China aumentó sus ganancias empresarias a pesar de la guerra en Medio Oriente</t>
+          <t>Las tasas se desploman en el mercado, pero el costo de los préstamos personales sube en términos reales</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/la-industria-china-aumento-sus-ganancias-empresarias-pesar-la-guerra-medio-oriente-n6271308</t>
+          <t>https://www.ambito.com/economia/las-tasas-se-desploman-el-mercado-pero-el-costo-los-prestamos-personales-sube-terminos-reales-n6271213</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -3451,19 +3451,19 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Los datos oficiales mostraron que las ganas industriales crecieron a su mejor ritmo en seis meses. Sin embargo, el riesgo de un impacto de la guerra sobre el entramado productivo chino sigue latente.</t>
+          <t>A pesar de la caída de las tasas de interés generales, los préstamos personales se mantienen estables en comparación con 2022, afectando a familias endeudadas.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Las tasas se desploman en el mercado, pero el costo de los préstamos personales sube en términos reales</t>
+          <t>Chau plazo fijo: así operan los principales bancos hoy, lunes 27 de abril</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/las-tasas-se-desploman-el-mercado-pero-el-costo-los-prestamos-personales-sube-terminos-reales-n6271213</t>
+          <t>https://www.ambito.com/economia/chau-plazo-fijo-asi-operan-los-principales-bancos-hoy-lunes-27-abril-n6271206</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -3483,19 +3483,19 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>A pesar de la caída de las tasas de interés generales, los préstamos personales se mantienen estables en comparación con 2022, afectando a familias endeudadas.</t>
+          <t>Las entidades mantienen rendimientos moderados y el mapa de tasas sigue mostrando diferencias para quienes buscan cuidar pesos.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Chau plazo fijo: así operan los principales bancos hoy, lunes 27 de abril</t>
+          <t>Salarios y paritarias de metalúrgicos: cuánto cobrarán en mayo de 2026 tras el último acuerdo</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/chau-plazo-fijo-asi-operan-los-principales-bancos-hoy-lunes-27-abril-n6271206</t>
+          <t>https://www.ambito.com/economia/salarios-y-paritarias-metalurgicos-cuanto-cobraran-mayo-2026-el-ultimo-acuerdo-n6271204</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -3515,19 +3515,19 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Las entidades mantienen rendimientos moderados y el mapa de tasas sigue mostrando diferencias para quienes buscan cuidar pesos.</t>
+          <t>Los metalúrgicos cobrarán en mayo los sueldos de abril con escalas actualizadas. No es un aumento nuevo, sino la aplicación del último acuerdo vigente.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Salarios y paritarias de metalúrgicos: cuánto cobrarán en mayo de 2026 tras el último acuerdo</t>
+          <t>Lanzan Kit 4.0, el programa del Gobierno para impulsar la transformación tecnológica de las pymes</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/salarios-y-paritarias-metalurgicos-cuanto-cobraran-mayo-2026-el-ultimo-acuerdo-n6271204</t>
+          <t>https://www.ambito.com/economia/lanzan-kit-40-el-programa-del-gobierno-impulsar-impulsa-la-transformacion-tecnologica-las-pymes-n6271132</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -3547,19 +3547,19 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Los metalúrgicos cobrarán en mayo los sueldos de abril con escalas actualizadas. No es un aumento nuevo, sino la aplicación del último acuerdo vigente.</t>
+          <t>La iniciativa del Ministerio De Economía apunta a impulsar la adopción de tecnología e Industria 4.0 mediante aportes del FONPEC y un esquema de cofinanciamiento.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Lanzan Kit 4.0, el programa del Gobierno para impulsar la transformación tecnológica de las pymes</t>
+          <t>Ni Shein ni Temu: la nueva plataforma para compras en el exterior que es furor</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/lanzan-kit-40-el-programa-del-gobierno-impulsar-impulsa-la-transformacion-tecnologica-las-pymes-n6271132</t>
+          <t>https://www.ambito.com/economia/ni-shein-ni-temu-la-nueva-plataforma-compras-el-exterior-que-es-furor-n6270242</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -3574,24 +3574,24 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>La iniciativa del Ministerio De Economía apunta a impulsar la adopción de tecnología e Industria 4.0 mediante aportes del FONPEC y un esquema de cofinanciamiento.</t>
+          <t>El avance de apps de compras extranjeras cambió los hábitos, brindando una alternativa con beneficios inéditos y precios imbatibles.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Ni Shein ni Temu: la nueva plataforma para compras en el exterior que es furor</t>
+          <t>La guerra en Medio Oriente también impacta en un alimento inesperado: se disparó el precio mundial del pistacho</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/ni-shein-ni-temu-la-nueva-plataforma-compras-el-exterior-que-es-furor-n6270242</t>
+          <t>https://www.ambito.com/economia/la-guerra-medio-oriente-tambien-impacta-un-alimento-inesperado-se-disparo-el-precio-mundial-del-pistacho-n6271007</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -3611,19 +3611,19 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>El avance de apps de compras extranjeras cambió los hábitos, brindando una alternativa con beneficios inéditos y precios imbatibles.</t>
+          <t>El conflicto entre Estados Unidos, Israel e Irán alteró el comercio global del pistacho, cuya producción se concentra en esa región. El valor internacional alcanzó máximos de ocho años y Argentina busca aprovechar la oportunidad con fuerte expansión del cultivo en dos provincias clave.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>La guerra en Medio Oriente también impacta en un alimento inesperado: se disparó el precio mundial del pistacho</t>
+          <t>La industria repuntó en marzo y cortó racha de ocho meses de caídas interanuales, según Orlando Ferreres</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/la-guerra-medio-oriente-tambien-impacta-un-alimento-inesperado-se-disparo-el-precio-mundial-del-pistacho-n6271007</t>
+          <t>https://www.ambito.com/economia/la-industria-repunto-marzo-y-corto-racha-ocho-meses-caidas-interanuales-segun-orlando-ferreres-n6271004</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -3643,19 +3643,19 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>El conflicto entre Estados Unidos, Israel e Irán alteró el comercio global del pistacho, cuya producción se concentra en esa región. El valor internacional alcanzó máximos de ocho años y Argentina busca aprovechar la oportunidad con fuerte expansión del cultivo en dos provincias clave.</t>
+          <t>Según el Índice de Producción Industrial, la actividad fabril subió 0,8% mensual desestacionalizado y 0,7% interanual. Pese a la mejora de marzo, el primer trimestre cerró con saldo negativo y persisten dudas sobre la demanda.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>La industria repuntó en marzo y cortó racha de ocho meses de caídas interanuales, según Orlando Ferreres</t>
+          <t>Buepp acepta pagos con NFC: cómo usarlo para obtener los descuentos</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/la-industria-repunto-marzo-y-corto-racha-ocho-meses-caidas-interanuales-segun-orlando-ferreres-n6271004</t>
+          <t>https://www.ambito.com/economia/buepp-acepta-pagos-nfc-como-usarlo-obtener-los-descuentos-n6270169</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -3675,24 +3675,24 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Según el Índice de Producción Industrial, la actividad fabril subió 0,8% mensual desestacionalizado y 0,7% interanual. Pese a la mejora de marzo, el primer trimestre cerró con saldo negativo y persisten dudas sobre la demanda.</t>
+          <t>La billetera virtual del Banco Provincia establece reintegros en todos los ámbitos del consumo cotidiano con beneficios diarios.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Buepp acepta pagos con NFC: cómo usarlo para obtener los descuentos</t>
+          <t>El Banco Central compró más de US$ 7.000 millones en el primer cuatrimestre - Perfil</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/buepp-acepta-pagos-nfc-como-usarlo-obtener-los-descuentos-n6270169</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPVThjRG9tNTdFVjNISjN2VnY0QXFETnppdGVUVnVXci1tNTRTRTlKNkl6NHBFYkV3TE04RVBpWFpHdnN6T0ZfWlVpWU1oeDVCU3VUaVpnUDBKVW9sMDhUYzVHTHJ6QXdzWHN5MzdJajdUeVgzUnk0clg3OTNtOWtxX0hxb1pjVUYyd1NxRGtneFdFc3gzZDV3U2swbmg3RDA5MS1lZzktYXdxTmxxZWxuaFZ4bFVzT3dacG1ock130gHDAUFVX3lxTE9ycFFRWkVSWS1pNEh6ZFVORnBObHVJOERrd3pKS1VBaVlQSFhzUEFBaGo4UEtpQlFCZndpREdZOGxaS1M5UXBTMzhXX2VJMU15eFVFdVRzSGNjMDBscEFjNkFmRThTUEtaNXFiMkRVeXNrQVZvY1lHRUdIMUlSZWZrOXllT2dGVVVxa1R6c0pJWE9PRUlJVU9ZWkFBc3ItRENHOFcyRnlaUzExSlhOMnZjdEQxV0tMX2xKYl94TlNWdFMtNA?oc=5</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Ambito - Economia</t>
+          <t>Google News - BCRA</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -3702,24 +3702,24 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>La billetera virtual del Banco Provincia establece reintegros en todos los ámbitos del consumo cotidiano con beneficios diarios.</t>
+          <t>El Banco Central compró más de US$ 7.000 millones en el primer cuatrimestre    Perfil</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>El Banco Central compró más de US$ 7.000 millones en el primer cuatrimestre - Perfil</t>
+          <t>El presidente del BCRA aseguró que los bancos "ya vieron el pico de morosidad" - MinutoUno</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPVThjRG9tNTdFVjNISjN2VnY0QXFETnppdGVUVnVXci1tNTRTRTlKNkl6NHBFYkV3TE04RVBpWFpHdnN6T0ZfWlVpWU1oeDVCU3VUaVpnUDBKVW9sMDhUYzVHTHJ6QXdzWHN5MzdJajdUeVgzUnk0clg3OTNtOWtxX0hxb1pjVUYyd1NxRGtneFdFc3gzZDV3U2swbmg3RDA5MS1lZzktYXdxTmxxZWxuaFZ4bFVzT3dacG1ock130gHDAUFVX3lxTE9ycFFRWkVSWS1pNEh6ZFVORnBObHVJOERrd3pKS1VBaVlQSFhzUEFBaGo4UEtpQlFCZndpREdZOGxaS1M5UXBTMzhXX2VJMU15eFVFdVRzSGNjMDBscEFjNkFmRThTUEtaNXFiMkRVeXNrQVZvY1lHRUdIMUlSZWZrOXllT2dGVVVxa1R6c0pJWE9PRUlJVU9ZWkFBc3ItRENHOFcyRnlaUzExSlhOMnZjdEQxV0tMX2xKYl94TlNWdFMtNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNcnZqcnVkSGhTZ3d5czFHQ2s4UC00MXZuQmdpRkpKb0RCNUtXaTMxdWxnQ25vNFVqN21NZVRiQm51YnFXS29ZRGRCeTBWcWhnLTZhWDlKYVZ2MG5XTmwzNmNHd3FpdzNlUk03X29kTVJ0ZHR3V0lQYnBNczNtTnlmanRmZTBuMXZkWXVKWDZRb2hXeVNZQkN5X1R6VEdaeEZteHRuVldJRlJYYXE4elh0c3N4TFJHNW440gG4AUFVX3lxTE1ydmpydWRIaFNnd3lzMUdDazhQLTQxdm5CZ2lGSkpvREI1S1dpMzF1bGdDbm80VWo3bU1lVGJCbnVicVdLb1lEZEJ5MFZxaGctNmFYOUphVnYwbldObDM2Y0d3cWl3M2VSTTdfb2RNUnRkdHdXSVBicE1zM21OeWZqdGZlMG4xdmRZdUpYNlFvaFd5U1lCQ3lfVHpUR1p4Rm14dG5WV0lGUlhhcTh6WHRzc3hMUkc1bjg?oc=5</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -3734,24 +3734,24 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>El Banco Central compró más de US$ 7.000 millones en el primer cuatrimestre    Perfil</t>
+          <t>El presidente del BCRA aseguró que los bancos "ya vieron el pico de morosidad"    MinutoUno</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>El presidente del BCRA aseguró que los bancos "ya vieron el pico de morosidad" - MinutoUno</t>
+          <t>El BCRA reconoció presión inflacionaria, pero confía en una baja en los próximos meses - Diario Mendoza</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNcnZqcnVkSGhTZ3d5czFHQ2s4UC00MXZuQmdpRkpKb0RCNUtXaTMxdWxnQ25vNFVqN21NZVRiQm51YnFXS29ZRGRCeTBWcWhnLTZhWDlKYVZ2MG5XTmwzNmNHd3FpdzNlUk03X29kTVJ0ZHR3V0lQYnBNczNtTnlmanRmZTBuMXZkWXVKWDZRb2hXeVNZQkN5X1R6VEdaeEZteHRuVldJRlJYYXE4elh0c3N4TFJHNW440gG4AUFVX3lxTE1ydmpydWRIaFNnd3lzMUdDazhQLTQxdm5CZ2lGSkpvREI1S1dpMzF1bGdDbm80VWo3bU1lVGJCbnVicVdLb1lEZEJ5MFZxaGctNmFYOUphVnYwbldObDM2Y0d3cWl3M2VSTTdfb2RNUnRkdHdXSVBicE1zM21OeWZqdGZlMG4xdmRZdUpYNlFvaFd5U1lCQ3lfVHpUR1p4Rm14dG5WV0lGUlhhcTh6WHRzc3hMUkc1bjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOYlJwcGxycmdoQWo4allRYk04N09wY3EzOXVfVGhtSVdNNVcwenEydUtSMXo0ajZqNmxDaEg5QVlxNUN3VXZoOVNQS3NKU2RKcmdSTnZnZWY2bVNFZnR5eGdoZUY5WHVBWWl4dERma1VVQ21oNC10enBSenpIN1Y4Q2VyLW1zcFdJYU5xU25HVnhicmZWclVBVEZPRHZNaVpiOTFSckY5WUFyc1R5SDRmRkg5QUlLSEVGLU92eGpkZl9HQ0XSAcgBQVVfeXFMT19mQW9UemljUDJiZnJLd2Q0X2I1Z2F5NnotRzFucFphQm1FTWRld3lKTFJNaFBKS1JQY01lelVRUlJmV0tRdlRSb2ptcjJHNkJXQmd2VWM5eUFXZmVMN1VCXzFPbTRNRENQNl9SUTVfeHVWZjBJRlBKaGJPMHlRaENfXzRsWnh1MFZEYTZ5VmV4cGh3U204ZkpDVERId01TaEVzTzlLNmZjNjNaZ1NWUXZfbF93X3E0Vl9EV3F4NENFTVZLcWFzNWE?oc=5</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -3771,19 +3771,19 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>El presidente del BCRA aseguró que los bancos "ya vieron el pico de morosidad"    MinutoUno</t>
+          <t>El BCRA reconoció presión inflacionaria, pero confía en una baja en los próximos meses    Diario Mendoza</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>El BCRA reconoció presión inflacionaria, pero confía en una baja en los próximos meses - Diario Mendoza</t>
+          <t>Paro en el BCRA: impacto en la actividad financiera - Vive La Plata</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOYlJwcGxycmdoQWo4allRYk04N09wY3EzOXVfVGhtSVdNNVcwenEydUtSMXo0ajZqNmxDaEg5QVlxNUN3VXZoOVNQS3NKU2RKcmdSTnZnZWY2bVNFZnR5eGdoZUY5WHVBWWl4dERma1VVQ21oNC10enBSenpIN1Y4Q2VyLW1zcFdJYU5xU25HVnhicmZWclVBVEZPRHZNaVpiOTFSckY5WUFyc1R5SDRmRkg5QUlLSEVGLU92eGpkZl9HQ0XSAcgBQVVfeXFMT19mQW9UemljUDJiZnJLd2Q0X2I1Z2F5NnotRzFucFphQm1FTWRld3lKTFJNaFBKS1JQY01lelVRUlJmV0tRdlRSb2ptcjJHNkJXQmd2VWM5eUFXZmVMN1VCXzFPbTRNRENQNl9SUTVfeHVWZjBJRlBKaGJPMHlRaENfXzRsWnh1MFZEYTZ5VmV4cGh3U204ZkpDVERId01TaEVzTzlLNmZjNjNaZ1NWUXZfbF93X3E0Vl9EV3F4NENFTVZLcWFzNWE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNcXFTTXdza3UxdHk1QWxPNDNWcktfUTJRb2R6Wk5PUEVvczc2cExQYTV2STBJdm02eC1ZNzh5aExjZmJlaElsUHZnNi10QU5UbVdLbUo5cTR4ZXNmcTg5SGdiMWpVV3QzVGU0WVVjQk94eVZVVERnc3V0N2VPMDRGOXdYRmI?oc=5</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -3798,56 +3798,56 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>El BCRA reconoció presión inflacionaria, pero confía en una baja en los próximos meses    Diario Mendoza</t>
+          <t>Paro en el BCRA: impacto en la actividad financiera    Vive La Plata</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Paro en el BCRA: impacto en la actividad financiera - Vive La Plata</t>
+          <t>Dólar hoy: a cuánto cotiza este lunes 4 de mayo</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNcXFTTXdza3UxdHk1QWxPNDNWcktfUTJRb2R6Wk5PUEVvczc2cExQYTV2STBJdm02eC1ZNzh5aExjZmJlaElsUHZnNi10QU5UbVdLbUo5cTR4ZXNmcTg5SGdiMWpVV3QzVGU0WVVjQk94eVZVVERnc3V0N2VPMDRGOXdYRmI?oc=5</t>
+          <t>https://www.ambito.com/finanzas/dolar-hoy-cuanto-cotiza-este-lunes-4-mayo-n6273493</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Google News - BCRA</t>
+          <t>Ambito - Finanzas</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Macro &amp; Policy</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Paro en el BCRA: impacto en la actividad financiera    Vive La Plata</t>
+          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Dólar hoy: a cuánto cotiza este lunes 4 de mayo</t>
+          <t>Dólar blue hoy: a cuánto opera este lunes 4 de mayo</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/dolar-hoy-cuanto-cotiza-este-lunes-4-mayo-n6273493</t>
+          <t>https://www.ambito.com/finanzas/dolar-blue-hoy-cuanto-opera-este-lunes-4-mayo-n6273494</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Dólar blue hoy: a cuánto opera este lunes 4 de mayo</t>
+          <t>Euro hoy y Euro blue hoy: a cuánto cotiza este lunes 4 de mayo</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/dolar-blue-hoy-cuanto-opera-este-lunes-4-mayo-n6273494</t>
+          <t>https://www.ambito.com/finanzas/euro-hoy-y-euro-blue-hoy-cuanto-cotiza-este-lunes-4-mayo-n6273457</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -3931,19 +3931,19 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
+          <t>Mirá a cuánto cotizan el euro oficial y el euro blue.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Euro hoy y Euro blue hoy: a cuánto cotiza este lunes 4 de mayo</t>
+          <t>Real blue: a cuánto opera este lunes 4 de mayo</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/euro-hoy-y-euro-blue-hoy-cuanto-cotiza-este-lunes-4-mayo-n6273457</t>
+          <t>https://www.ambito.com/finanzas/real-blue-cuanto-opera-este-lunes-4-mayo-n6273466</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -3963,19 +3963,19 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Mirá a cuánto cotizan el euro oficial y el euro blue.</t>
+          <t>La cotización minuto a minuto para la compra y venta de la divisa brasileña en nuestro país.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Real blue: a cuánto opera este lunes 4 de mayo</t>
+          <t>Mientras el mercado ya mira el 2027, llegan 15 balances de empresas argentinas: los datos clave a seguir en la semana</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/real-blue-cuanto-opera-este-lunes-4-mayo-n6273466</t>
+          <t>https://www.ambito.com/finanzas/mientras-el-mercado-ya-mira-el-2027-llegan-15-balances-empresas-argentinas-los-datos-clave-seguir-la-semana-n6273394</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -3995,19 +3995,19 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>La cotización minuto a minuto para la compra y venta de la divisa brasileña en nuestro país.</t>
+          <t>El deterioro en la actividad, la inflación y los salarios empieza a impactar en las expectativas. Mientras el Gobierno sostiene el frente financiero sin sobresaltos, los inversores exigen mejor tasa a 2028 y analizan las opciones en pesos.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Mientras el mercado ya mira el 2027, llegan 15 balances de empresas argentinas: los datos clave a seguir en la semana</t>
+          <t>Dólar hoy: a cuánto cotiza este domingo 3 de mayo</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/mientras-el-mercado-ya-mira-el-2027-llegan-15-balances-empresas-argentinas-los-datos-clave-seguir-la-semana-n6273394</t>
+          <t>https://www.ambito.com/finanzas/dolar-hoy-cuanto-cotiza-este-domingo-3-mayo-n6273285</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -4027,19 +4027,19 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>El deterioro en la actividad, la inflación y los salarios empieza a impactar en las expectativas. Mientras el Gobierno sostiene el frente financiero sin sobresaltos, los inversores exigen mejor tasa a 2028 y analizan las opciones en pesos.</t>
+          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Dólar hoy: a cuánto cotiza este domingo 3 de mayo</t>
+          <t>Dólar blue hoy: a cuánto opera este domingo 3 de mayo</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/dolar-hoy-cuanto-cotiza-este-domingo-3-mayo-n6273285</t>
+          <t>https://www.ambito.com/finanzas/dolar-blue-hoy-cuanto-opera-este-domingo-3-mayo-n6273286</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Dólar blue hoy: a cuánto opera este domingo 3 de mayo</t>
+          <t>Dólar hoy: a cuánto cotiza este sábado 2 de mayo</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/dolar-blue-hoy-cuanto-opera-este-domingo-3-mayo-n6273286</t>
+          <t>https://www.ambito.com/finanzas/dolar-hoy-cuanto-cotiza-este-sabado-2-mayo-n6273106</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -4098,12 +4098,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Dólar hoy: a cuánto cotiza este sábado 2 de mayo</t>
+          <t>Dólar blue hoy: a cuánto opera este sábado 2 de mayo</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/dolar-hoy-cuanto-cotiza-este-sabado-2-mayo-n6273106</t>
+          <t>https://www.ambito.com/finanzas/dolar-blue-hoy-cuanto-opera-este-sabado-2-mayo-n6273107</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -4130,12 +4130,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Dólar blue hoy: a cuánto opera este sábado 2 de mayo</t>
+          <t>Morosidad: alerta por el nivel del GBA, mientras que el BCRA y los bancos aseguran que el pico ya pasó</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/dolar-blue-hoy-cuanto-opera-este-sabado-2-mayo-n6273107</t>
+          <t>https://www.ambito.com/finanzas/morosidad-alerta-el-nivel-del-gba-mientras-que-el-bcra-y-los-bancos-aseguran-que-el-pico-ya-paso-n6273159</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -4150,24 +4150,24 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
+          <t>En las últimas semanas, creció la preocupación por el nivel de morosidad, que en el Gran Buenos Aires ya se cuadruplicó durante el último año, según datos que se desprenden de un informe del BCRA. Mientras tanto, distintos actores del sistema financiero aseguran que el "pico ya pasó".</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Morosidad: alerta por el nivel del GBA, mientras que el BCRA y los bancos aseguran que el pico ya pasó</t>
+          <t>Deuda: Economía enfrenta vencimientos por $6,9 billones en mayo y seguirá con la política de estirar plazos</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/morosidad-alerta-el-nivel-del-gba-mientras-que-el-bcra-y-los-bancos-aseguran-que-el-pico-ya-paso-n6273159</t>
+          <t>https://www.ambito.com/finanzas/deuda-economia-enfrenta-vencimientos-69-billones-mayo-y-seguira-la-politica-estirar-plazos-n6272821</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -4187,19 +4187,19 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>En las últimas semanas, creció la preocupación por el nivel de morosidad, que en el Gran Buenos Aires ya se cuadruplicó durante el último año, según datos que se desprenden de un informe del BCRA. Mientras tanto, distintos actores del sistema financiero aseguran que el "pico ya pasó".</t>
+          <t>Se espera que el Tesoro trate de ir nuevamente por niveles de rollover por encima del 100%. Las colocaciones hard dollar ya superan los u$s2.250 millones.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Deuda: Economía enfrenta vencimientos por $6,9 billones en mayo y seguirá con la política de estirar plazos</t>
+          <t>Mercado de capitales: más comitentes, nuevos instrumentos y el impulso de las nuevas generaciones</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/deuda-economia-enfrenta-vencimientos-69-billones-mayo-y-seguira-la-politica-estirar-plazos-n6272821</t>
+          <t>https://www.ambito.com/finanzas/mercado-capitales-mas-comitentes-nuevos-instrumentos-y-el-impulso-las-nuevas-generaciones-n6272341</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -4214,24 +4214,24 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Se espera que el Tesoro trate de ir nuevamente por niveles de rollover por encima del 100%. Las colocaciones hard dollar ya superan los u$s2.250 millones.</t>
+          <t>Los actores del sistema financiero celebran el aumento del volumen de las operatorias y la canalización del ahorro a una función productiva.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Mercado de capitales: más comitentes, nuevos instrumentos y el impulso de las nuevas generaciones</t>
+          <t>Cambios en los pagos digitales: cómo deben adecuarse las fintech a la nueva norma del BCRA</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/mercado-capitales-mas-comitentes-nuevos-instrumentos-y-el-impulso-las-nuevas-generaciones-n6272341</t>
+          <t>https://www.ambito.com/finanzas/cambios-los-pagos-digitales-como-deben-adecuarse-las-fintech-la-nueva-norma-del-bcra-n6272979</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -4251,19 +4251,19 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Los actores del sistema financiero celebran el aumento del volumen de las operatorias y la canalización del ahorro a una función productiva.</t>
+          <t>La nueva normativa del BCRA pone fin a los grises legales al regular a las fintech que operan bajo la modalidad de servicio en pagos digitales.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Cambios en los pagos digitales: cómo deben adecuarse las fintech a la nueva norma del BCRA</t>
+          <t>Dólar hoy: a cuánto cotiza este viernes 1 de mayo</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/cambios-los-pagos-digitales-como-deben-adecuarse-las-fintech-la-nueva-norma-del-bcra-n6272979</t>
+          <t>https://www.ambito.com/finanzas/dolar-hoy-cuanto-cotiza-este-viernes-1-mayo-n6272879</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -4283,19 +4283,19 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>La nueva normativa del BCRA pone fin a los grises legales al regular a las fintech que operan bajo la modalidad de servicio en pagos digitales.</t>
+          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Dólar hoy: a cuánto cotiza este viernes 1 de mayo</t>
+          <t>Dólar blue hoy: a cuánto opera este viernes 1 de mayo</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/dolar-hoy-cuanto-cotiza-este-viernes-1-mayo-n6272879</t>
+          <t>https://www.ambito.com/finanzas/dolar-blue-hoy-cuanto-opera-este-viernes-1-mayo-n6272880</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -4322,17 +4322,17 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Dólar blue hoy: a cuánto opera este viernes 1 de mayo</t>
+          <t>Qué está pasando en el Congreso: elecciones presidenciales y falta de quórum frenan la agenda legislativa</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/dolar-blue-hoy-cuanto-opera-este-viernes-1-mayo-n6272880</t>
+          <t>https://www.infobae.com/colombia/2026/05/04/que-esta-pasando-en-el-congreso-elecciones-presidenciales-y-falta-de-quorum-frenan-la-agenda-legislativa/</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Ambito - Finanzas</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -4342,24 +4342,24 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
+          <t>El avance de la agenda legislativa se ha visto interrumpido por sesiones que no logran continuar con el orden del día, lo que ha impedido la discusión y votación de varios proyectos. A esto se suman tensiones entre bancadas y cruces de señalamientos sobre la responsabilidad del estancamiento</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>El Gobierno aprobó las nuevas subas en las boletas de luz y bonificó el consumo de gas</t>
+          <t>Del frío a la ciclogénesis: cómo estará el tiempo en el AMBA esta semana</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/economia/2026/05/04/aumento-de-luz-y-bonificacion-al-consumo-de-gas-las-actualizaciones-que-regiran-a-partir-de-mayo/</t>
+          <t>https://www.infobae.com/sociedad/2026/05/04/del-frio-a-la-ciclogenesis-como-estara-el-tiempo-en-el-amba-esta-semana/</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -4379,24 +4379,24 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Mediante una serie de resoluciones, el Gobierno estableció los porcentajes de incrementos que se aplicarán sobre las tarifas de marzo e informó un descuento sobre la boleta de gas</t>
+          <t>La segunda mitad de la semana estará marcada por vientos extremos, tormentas y lluvias abundantes que afectarían algunas zonas de la provincia durante al menos 72 horas</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Se registró un temblor de magnitud 4.1 en Arequipa</t>
+          <t>Cómo impacta en los bonos en dólares de Argentina el calendario electoral 2027 - Bloomberg Línea</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/peru/2026/05/04/se-registro-un-temblor-de-magnitud-41-en-arequipa/</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOcWIyRXJBNEFncnpkbkt5QWlSTlJya28tRGRuM3NRQnpNSWhaNE9qWV9OZUFVQlJmNjRrWjlBWXE4QXlndmJtN3RoblMtbGZwV1Q3TW1wZ0d2dzN1cWRfYTBsYnV5NmhFMU1aNmRIcmtlMlJ6Vk9tNFBQUUdYcWo2eEF3Wksta2dqZFNIN2FycF83cnNDRU1RT0N5WC1sM0IwMXNRTW54M2k4YTZSa2ZtV1hBeU4ydnJnaWhaRjhqQmIzbjFwS3N6Qi10MFN0dDjSAeMBQVVfeXFMT2dhSlh5QUw3d3M1d0RmMXJmWk9VNG83V0lXMnNpeEJLSEhSb0ZXa3BIWmhnZXdpVzVGa2VGRy0tQXZkS0FOMzlfRnI5RFpUVVUyZGF5WUhoZDBmei16ZkV2TVM5Qzhac0ZESXRJN2paUzZoWGQxN0xnM19VUlg3VnNoeU9tWnROLTQ2Nm1nblJKZzYwV05OcEZ2Ti1ub3hLTjZIREMzNXZfNkxGVkM4akl5ZFVYQmNsM2FEZWl6c1RJVHZFcjlDdWhWSHZOelc1V0tOU0RGWkcwY21aQ0oxdnlIZkE?oc=5</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Google News - Mercados</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -4406,56 +4406,56 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>A lo largo de su historia, la nación ha enfrentado diversos sismos que han dejado miles de muertos, heridos e innumerables daños materiales</t>
+          <t>Cómo impacta en los bonos en dólares de Argentina el calendario electoral 2027    Bloomberg Línea</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Cómo impacta en los bonos en dólares de Argentina el calendario electoral 2027 - Bloomberg Línea</t>
+          <t>El Gobierno se apoyó en el Tesoro de los EEUU para pagarle al FMI: cómo fue la operación - Infobae</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOcWIyRXJBNEFncnpkbkt5QWlSTlJya28tRGRuM3NRQnpNSWhaNE9qWV9OZUFVQlJmNjRrWjlBWXE4QXlndmJtN3RoblMtbGZwV1Q3TW1wZ0d2dzN1cWRfYTBsYnV5NmhFMU1aNmRIcmtlMlJ6Vk9tNFBQUUdYcWo2eEF3Wksta2dqZFNIN2FycF83cnNDRU1RT0N5WC1sM0IwMXNRTW54M2k4YTZSa2ZtV1hBeU4ydnJnaWhaRjhqQmIzbjFwS3N6Qi10MFN0dDjSAeMBQVVfeXFMT2dhSlh5QUw3d3M1d0RmMXJmWk9VNG83V0lXMnNpeEJLSEhSb0ZXa3BIWmhnZXdpVzVGa2VGRy0tQXZkS0FOMzlfRnI5RFpUVVUyZGF5WUhoZDBmei16ZkV2TVM5Qzhac0ZESXRJN2paUzZoWGQxN0xnM19VUlg3VnNoeU9tWnROLTQ2Nm1nblJKZzYwV05OcEZ2Ti1ub3hLTjZIREMzNXZfNkxGVkM4akl5ZFVYQmNsM2FEZWl6c1RJVHZFcjlDdWhWSHZOelc1V0tOU0RGWkcwY21aQ0oxdnlIZkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQY3ZmRDA1Qmx6UHBXM0xfN1Vna3Z2VmU5YlpiV29FRE5VTk1UVGJadl9RRGx6OS1NN1d5Q0syelp1LUJ5S0tidUw3MkwzcXZ6RGFOMDlYdjhWUy1ZbmM3OF9KUFV0RUhnSGkxeUNkd0VLOEVHS0FXYVRtNFJhQjBzbXhTNEpJOG1rdzc2YXB4M1JKTlhRRjhKb3N2eWV6OUZFNkh3MUhBV2Zsa1Vua3VyVk9ScE9tOWJLNWppU0hYVF9nQ0VCdERSbWFWdGbSAecBQVVfeXFMTm12VUNIaTMzQ1pDNGpBUndLZXlBNlFqbFhJd0w0QjR0TDRjRkdSTTNBU2tTNDE3ZlFwZGN2dGpDcXY1QjZoNHgtUG1aSjVJT0FmY1JET0F3c2hMd3Ewcl8zcVh2RU41aWl6WExQY3EwV3BkcWhUaWQ5MjVfNTFmN2xvZVBmVlBMZUZWTllPMDQwbW5QVHdDenhJcFZHRzJlUVNmc3NITml4NUpia2Qza0RxR1Rrdmd3MEpRbkhCcjlGSU4yQmREWHhKZ1FPWmVvRzZ2UFZ3X1o5Q091b0E0T0FFQ25lXzNZ?oc=5</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Google News - Mercados</t>
+          <t>Google News - FMI</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Financial Markets</t>
+          <t>International Impact</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Cómo impacta en los bonos en dólares de Argentina el calendario electoral 2027    Bloomberg Línea</t>
+          <t>El Gobierno se apoyó en el Tesoro de los EEUU para pagarle al FMI: cómo fue la operación    Infobae</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>El Gobierno se apoyó en el Tesoro de los EEUU para pagarle al FMI: cómo fue la operación - Infobae</t>
+          <t>La deuda externa es la más alta de la historia y se multiplicaron por cuatro los vencimientos de corto plazo - La Política Online</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQY3ZmRDA1Qmx6UHBXM0xfN1Vna3Z2VmU5YlpiV29FRE5VTk1UVGJadl9RRGx6OS1NN1d5Q0syelp1LUJ5S0tidUw3MkwzcXZ6RGFOMDlYdjhWUy1ZbmM3OF9KUFV0RUhnSGkxeUNkd0VLOEVHS0FXYVRtNFJhQjBzbXhTNEpJOG1rdzc2YXB4M1JKTlhRRjhKb3N2eWV6OUZFNkh3MUhBV2Zsa1Vua3VyVk9ScE9tOWJLNWppU0hYVF9nQ0VCdERSbWFWdGbSAecBQVVfeXFMTm12VUNIaTMzQ1pDNGpBUndLZXlBNlFqbFhJd0w0QjR0TDRjRkdSTTNBU2tTNDE3ZlFwZGN2dGpDcXY1QjZoNHgtUG1aSjVJT0FmY1JET0F3c2hMd3Ewcl8zcVh2RU41aWl6WExQY3EwV3BkcWhUaWQ5MjVfNTFmN2xvZVBmVlBMZUZWTllPMDQwbW5QVHdDenhJcFZHRzJlUVNmc3NITml4NUpia2Qza0RxR1Rrdmd3MEpRbkhCcjlGSU4yQmREWHhKZ1FPWmVvRzZ2UFZ3X1o5Q091b0E0T0FFQ25lXzNZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPU1NIUmZsQ3M2LWktOUVlZlM4bGZBQ1NxQzJWZmdfYTVXZ2s2T1Y3QUNTZV82T2ZGeXZSWDhKUEZBUjM5WVd3V3I5MERuX1B6ekZLM29qUTdITlI3cUg3amV2T3RUazkybXYyZVNFUVpDNGRPQ21JcmcyX2ludWk5elp3bzd0ZDZtWnFwSGtqTVR1REFRNlRyOFZQb044bWh6Zm1FZkVyUlRWWjY1RHVEMUViSlF5Y19Lbktnc9IB6AFBVV95cUxPYmRyRzhJRkhEN3JtM1hiOFAtTmY0d3FzNmRHWjBwenVObEQ1amFfNGpGZmxoOXI1WFJrS2RzdUZaeGtDbkl0SGI5b2ZSMi1WYXdQOTZ3b3lqVUFzNkFyTkhxMzNxdHkyY3VRV01sNGVwa2ViMXB5UUY5YkM4QXQwTlpLOERqZENEQl8yNVA2eDR3SjhkUlFfUkVVaHBHM2t5MnpGNjhLWEQ1UERRVzUtZllKUmhwOC1DRjRobjhiX0FUa1VQMXZlbE1LX2tsUnFBTFNyX3RvWTBnREtMWGM2bE8yUWtIOEgt?oc=5</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -4470,24 +4470,24 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>El Gobierno se apoyó en el Tesoro de los EEUU para pagarle al FMI: cómo fue la operación    Infobae</t>
+          <t>La deuda externa es la más alta de la historia y se multiplicaron por cuatro los vencimientos de corto plazo    La Política Online</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>La deuda externa es la más alta de la historia y se multiplicaron por cuatro los vencimientos de corto plazo - La Política Online</t>
+          <t>La deuda externa más alta de la historia: cuánto endeudaron al Estado los últimos gobiernos - Enterate Noticias</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPU1NIUmZsQ3M2LWktOUVlZlM4bGZBQ1NxQzJWZmdfYTVXZ2s2T1Y3QUNTZV82T2ZGeXZSWDhKUEZBUjM5WVd3V3I5MERuX1B6ekZLM29qUTdITlI3cUg3amV2T3RUazkybXYyZVNFUVpDNGRPQ21JcmcyX2ludWk5elp3bzd0ZDZtWnFwSGtqTVR1REFRNlRyOFZQb044bWh6Zm1FZkVyUlRWWjY1RHVEMUViSlF5Y19Lbktnc9IB6AFBVV95cUxPYmRyRzhJRkhEN3JtM1hiOFAtTmY0d3FzNmRHWjBwenVObEQ1amFfNGpGZmxoOXI1WFJrS2RzdUZaeGtDbkl0SGI5b2ZSMi1WYXdQOTZ3b3lqVUFzNkFyTkhxMzNxdHkyY3VRV01sNGVwa2ViMXB5UUY5YkM4QXQwTlpLOERqZENEQl8yNVA2eDR3SjhkUlFfUkVVaHBHM2t5MnpGNjhLWEQ1UERRVzUtZllKUmhwOC1DRjRobjhiX0FUa1VQMXZlbE1LX2tsUnFBTFNyX3RvWTBnREtMWGM2bE8yUWtIOEgt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNNVF4UFVaY3AxdEphcWRsZldPbElSUW14b0haYVBzWjR3eGVTM3B6REdHN0pvOW5hZEJ2M00ySDdMZF9vVW9VOWpvY2VUcTJWMnl5YVpoN1pGSm50VEd0YXc3bUJvbmpYQ0E0ZTBiNksyWnByNHA3Y1dQdkkwODRzUGpsOEFtd29NQW9HMFU0QmQxOXdBNm1Rb1lTTTRtdkN3allTcC1fQ1FwWGVaTi1STnoyUzRKcFB2ZUp6VzlRUdIBuAFBVV95cUxQMVh5RWNDak5fTmYzUi16dGxXQnVERVJYQnNpSTMyNU1HUUlGcXBoQ0JYWGxFY1dJX3lYNTdacU9rQXpIV2E5dkN5UWZxMEJIal92UFBNaHRLeU55QVBSaGFLMUpYUnFMcGZJOFE3R3I1cHBLUnF2d0VaWW5GUFdSeVU3a2hyMmRYVWJUS2xUcXhtVmZRd0dyTUd6cjdGWkNIUXpwT0pORDZIOXg2UnBGQllBcnYxenJr?oc=5</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -4502,24 +4502,24 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>La deuda externa es la más alta de la historia y se multiplicaron por cuatro los vencimientos de corto plazo    La Política Online</t>
+          <t>La deuda externa más alta de la historia: cuánto endeudaron al Estado los últimos gobiernos    Enterate Noticias</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>La deuda externa más alta de la historia: cuánto endeudaron al Estado los últimos gobiernos - Enterate Noticias</t>
+          <t>La Argentina le compró DEG a Estados Unidos por US$819 millones para pagarle intereses al FMI - La Nación</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNNVF4UFVaY3AxdEphcWRsZldPbElSUW14b0haYVBzWjR3eGVTM3B6REdHN0pvOW5hZEJ2M00ySDdMZF9vVW9VOWpvY2VUcTJWMnl5YVpoN1pGSm50VEd0YXc3bUJvbmpYQ0E0ZTBiNksyWnByNHA3Y1dQdkkwODRzUGpsOEFtd29NQW9HMFU0QmQxOXdBNm1Rb1lTTTRtdkN3allTcC1fQ1FwWGVaTi1STnoyUzRKcFB2ZUp6VzlRUdIBuAFBVV95cUxQMVh5RWNDak5fTmYzUi16dGxXQnVERVJYQnNpSTMyNU1HUUlGcXBoQ0JYWGxFY1dJX3lYNTdacU9rQXpIV2E5dkN5UWZxMEJIal92UFBNaHRLeU55QVBSaGFLMUpYUnFMcGZJOFE3R3I1cHBLUnF2d0VaWW5GUFdSeVU3a2hyMmRYVWJUS2xUcXhtVmZRd0dyTUd6cjdGWkNIUXpwT0pORDZIOXg2UnBGQllBcnYxenJr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPUHQ2SDRDSnJLdzZfUGR2RjhidU42QWtHX1FZV2pDaDBIWVFkQ05SV3hYSUhnbDJEeHdicVlkWjgxVEU1b0xaZzY0c0UzQjc0cktVVEE4ZDkwSFZkc3d3MERyY3FIOU1NMnFqcTVYcHB1c0Zkd0F0NWNMQkNhZUZFU0hqd2dteFQ2NEVJVmZyX04yM1JFUjlNT1ZjdXB3T1JXTHluY0EtWnRrQXdUUzRkTWMteTRZdENXLUx5NDgtM2NIck5QT25wQ2RoRFJVYWZVcjdNaVEtWExyZw?oc=5</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -4534,24 +4534,24 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>La deuda externa más alta de la historia: cuánto endeudaron al Estado los últimos gobiernos    Enterate Noticias</t>
+          <t>La Argentina le compró DEG a Estados Unidos por US$819 millones para pagarle intereses al FMI    La Nación</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>La Argentina le compró DEG a Estados Unidos por US$819 millones para pagarle intereses al FMI - La Nación</t>
+          <t>El Gobierno concretó un nuevo DEG con el Tesoro de Estados Unidos por US$ 819 millones para pagar deuda al FMI - Diario Río Negro</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPUHQ2SDRDSnJLdzZfUGR2RjhidU42QWtHX1FZV2pDaDBIWVFkQ05SV3hYSUhnbDJEeHdicVlkWjgxVEU1b0xaZzY0c0UzQjc0cktVVEE4ZDkwSFZkc3d3MERyY3FIOU1NMnFqcTVYcHB1c0Zkd0F0NWNMQkNhZUZFU0hqd2dteFQ2NEVJVmZyX04yM1JFUjlNT1ZjdXB3T1JXTHluY0EtWnRrQXdUUzRkTWMteTRZdENXLUx5NDgtM2NIck5QT25wQ2RoRFJVYWZVcjdNaVEtWExyZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQc2FQT3A3eVVmbWNhaDFMNEpYd19BM3BPRm1EaTZmSkdMeUZ2RDZEMDZRWjhDakV2eF9sRFVTc05HSWNRSGY2TmpQWExPZFVMaUdPRWhtTGJUek02ekJsUHg3ZTM3aVZGa1hGMThNTW11UjZxNnY2ektqdFBVaTJfeU5sTWJPdnBPZGYzTWVfTUJGQjU0cTZXem1lMC10cF9xRjhxcUFhVXRpUTFMQ2xzMW1SRV9iMWFTT2ZzaUtaUEFUMzRrSkw4Z1hiY1VqVE9lekNfcdIB3AFBVV95cUxPaE10VXJmSHVjWlFRVmE3RXJsc2lUcWZTMFJOSnVCX3VON3dOZS1sSjhYTG5PZE5PVWhKSExYTkVTYUpEMkVIOFdwUUlmaTJNU2Z5WUowV1NVcjBQZmtyMUw2MG85cEhRdUNPUE9NNGdLUW1tUGk1V0lJYW5xLXd2Q1paTmVFTlVJTmlTaVkxX0hNVTFXX1lQNGRVRURSX1NvQlpFNU1fVUpJa1JfTWprZm9hOXVmRDV3WVA1bkNCNkVma3hSWTgxX0tMdnVKZjYxRkJiWld1TGY4blN0?oc=5</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -4571,19 +4571,19 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>La Argentina le compró DEG a Estados Unidos por US$819 millones para pagarle intereses al FMI    La Nación</t>
+          <t>El Gobierno concretó un nuevo DEG con el Tesoro de Estados Unidos por US$ 819 millones para pagar deuda al FMI    Diario Río Negro</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>El Gobierno concretó un nuevo DEG con el Tesoro de Estados Unidos por US$ 819 millones para pagar deuda al FMI - Diario Río Negro</t>
+          <t>Deuda con el FMI: el Gobierno concretó una operación financiera con EEUU para pagar más de U$S800 millones - La Gaceta</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQc2FQT3A3eVVmbWNhaDFMNEpYd19BM3BPRm1EaTZmSkdMeUZ2RDZEMDZRWjhDakV2eF9sRFVTc05HSWNRSGY2TmpQWExPZFVMaUdPRWhtTGJUek02ekJsUHg3ZTM3aVZGa1hGMThNTW11UjZxNnY2ektqdFBVaTJfeU5sTWJPdnBPZGYzTWVfTUJGQjU0cTZXem1lMC10cF9xRjhxcUFhVXRpUTFMQ2xzMW1SRV9iMWFTT2ZzaUtaUEFUMzRrSkw4Z1hiY1VqVE9lekNfcdIB3AFBVV95cUxPaE10VXJmSHVjWlFRVmE3RXJsc2lUcWZTMFJOSnVCX3VON3dOZS1sSjhYTG5PZE5PVWhKSExYTkVTYUpEMkVIOFdwUUlmaTJNU2Z5WUowV1NVcjBQZmtyMUw2MG85cEhRdUNPUE9NNGdLUW1tUGk1V0lJYW5xLXd2Q1paTmVFTlVJTmlTaVkxX0hNVTFXX1lQNGRVRURSX1NvQlpFNU1fVUpJa1JfTWprZm9hOXVmRDV3WVA1bkNCNkVma3hSWTgxX0tMdnVKZjYxRkJiWld1TGY4blN0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPdG12TW5FbUpBYjZxWjB3eEQ4RVVtWkl1NXY3TU9tQVFrRlJiRHlSR3c1aENNQXNteFRVOGZOLTg1UHpPWVhNSTdSWGNvZEVCLVhkNEhIcEdzQWxWZGJwWDBCd3B3S2tPemgtMnM3WHYtOUJzWjVRUXlvZk9mWTAtYjZ4cmVhcUJBQTIzeS1HcGYtMlFKcC1kSWxpUzJjOTRWT1pZYjNBbW5rWnM0b0ZuUDNFblY3a1VBbklGY3gwM1lGWmVoN3o0aU1YVmJCU0hCaDlITdIB2gFBVV95cUxQd29NcDE4V3dTbW9tX19VUTdJaGxXQzA3OERQYUZsSC0yY2VPV2xzdG9iRmd1d1JfNlJqMFpuYlZGQkVVdXhRdmtrcXpCYnZqXzdQc1Y4ZkRnMmhURzdBYXhRV3hwUVduSW50Z01CNlZ6bmhJNDhPWjk3OGlUZ3hFZmxmaXUzd1hTUWV3Z2dqcUs2aFkweE8yN1RXRVROVjNaLTJNTEhFU0RoQXJjdWxkeWtTRVdPUk9UMUdYUVRUOUZBX1djZ1NtcDMwNDZPcmRobmIwNXdjMUZtUQ?oc=5</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -4603,19 +4603,19 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>El Gobierno concretó un nuevo DEG con el Tesoro de Estados Unidos por US$ 819 millones para pagar deuda al FMI    Diario Río Negro</t>
+          <t>Deuda con el FMI: el Gobierno concretó una operación financiera con EEUU para pagar más de U$S800 millones    La Gaceta</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Deuda con el FMI: el Gobierno concretó una operación financiera con EEUU para pagar más de U$S800 millones - La Gaceta</t>
+          <t>Exdirector del FMI ve acceso al mercado como llave para resolver la deuda argentina con el organismo - Bloomberg Línea</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPdG12TW5FbUpBYjZxWjB3eEQ4RVVtWkl1NXY3TU9tQVFrRlJiRHlSR3c1aENNQXNteFRVOGZOLTg1UHpPWVhNSTdSWGNvZEVCLVhkNEhIcEdzQWxWZGJwWDBCd3B3S2tPemgtMnM3WHYtOUJzWjVRUXlvZk9mWTAtYjZ4cmVhcUJBQTIzeS1HcGYtMlFKcC1kSWxpUzJjOTRWT1pZYjNBbW5rWnM0b0ZuUDNFblY3a1VBbklGY3gwM1lGWmVoN3o0aU1YVmJCU0hCaDlITdIB2gFBVV95cUxQd29NcDE4V3dTbW9tX19VUTdJaGxXQzA3OERQYUZsSC0yY2VPV2xzdG9iRmd1d1JfNlJqMFpuYlZGQkVVdXhRdmtrcXpCYnZqXzdQc1Y4ZkRnMmhURzdBYXhRV3hwUVduSW50Z01CNlZ6bmhJNDhPWjk3OGlUZ3hFZmxmaXUzd1hTUWV3Z2dqcUs2aFkweE8yN1RXRVROVjNaLTJNTEhFU0RoQXJjdWxkeWtTRVdPUk9UMUdYUVRUOUZBX1djZ1NtcDMwNDZPcmRobmIwNXdjMUZtUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxOeXRqcVlXUm9pelRfRTc5WXN4eEhSa3RmLUhYZTRJODdOTHhYVmM3OUxkaFRpaGxlV0dqdG5PUTFNbVFNdmN1RlJzUVFTUmc0ZVZUbFBkdklSZUQydm1WQUlyV1VJbVJyWEtXczRDdnpHcllHMTNHNllzSnJlbEpzRVU4b0xtMkpRS0laYkczRll0bTdYOHVwcFpLcUV5SDM1elAxX2tTQ3FqUm5Eb0dmUDlWTnpFNnJFRVV3TV9RdFNkcS1vMjEwU0pRWFZHbnNoek9xcTZWYldzX09Wdk1xUGhNeVM3bm1ZZjBybdIBgAJBVV95cUxOdllkZzdGeERqMktHNnRUTGdoSUxreEFZUWhZSkZtZ3lIVW96RzJORWM3aks3Z3JDNURSS0FzTVVCQWs4VVgzcEZENFZpcE1YT1ZtQXJURURWeFIxeEcyU3NkOVRONTVXdUJaRUtObi1YOUpKNXZMRGJGcTB1ZGU5WW1aQVRPU1I2emFzb3ZpMFdfbDRKR2NNdG9VaDMtSnZrVTgycFIwczlQdHZtdkdTMnZJQjJDWmtlQm5DZFdwZkRYZWx2T0VhQ0lpd3JRM0d5Nm5XM1RwVU1QNzRoTUFJbXRvd3JKX1poWDlTcWJPTTBIWkkxdlhGT1Y1T1ZFbVc2?oc=5</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -4630,24 +4630,24 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Deuda con el FMI: el Gobierno concretó una operación financiera con EEUU para pagar más de U$S800 millones    La Gaceta</t>
+          <t>Exdirector del FMI ve acceso al mercado como llave para resolver la deuda argentina con el organismo    Bloomberg Línea</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Exdirector del FMI ve acceso al mercado como llave para resolver la deuda argentina con el organismo - Bloomberg Línea</t>
+          <t>Deuda: el Gobierno volvió a comprarle DEGs a EEUU y le pagó u$s800 millones al FMI - Ambito</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxOeXRqcVlXUm9pelRfRTc5WXN4eEhSa3RmLUhYZTRJODdOTHhYVmM3OUxkaFRpaGxlV0dqdG5PUTFNbVFNdmN1RlJzUVFTUmc0ZVZUbFBkdklSZUQydm1WQUlyV1VJbVJyWEtXczRDdnpHcllHMTNHNllzSnJlbEpzRVU4b0xtMkpRS0laYkczRll0bTdYOHVwcFpLcUV5SDM1elAxX2tTQ3FqUm5Eb0dmUDlWTnpFNnJFRVV3TV9RdFNkcS1vMjEwU0pRWFZHbnNoek9xcTZWYldzX09Wdk1xUGhNeVM3bm1ZZjBybdIBgAJBVV95cUxOdllkZzdGeERqMktHNnRUTGdoSUxreEFZUWhZSkZtZ3lIVW96RzJORWM3aks3Z3JDNURSS0FzTVVCQWs4VVgzcEZENFZpcE1YT1ZtQXJURURWeFIxeEcyU3NkOVRONTVXdUJaRUtObi1YOUpKNXZMRGJGcTB1ZGU5WW1aQVRPU1I2emFzb3ZpMFdfbDRKR2NNdG9VaDMtSnZrVTgycFIwczlQdHZtdkdTMnZJQjJDWmtlQm5DZFdwZkRYZWx2T0VhQ0lpd3JRM0d5Nm5XM1RwVU1QNzRoTUFJbXRvd3JKX1poWDlTcWJPTTBIWkkxdlhGT1Y1T1ZFbVc2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPX01IRnBJTllEY2RRZlBQYkJMMjRlMFdLcVU5cGFJdTY3WkZaVjNOTVRfNmwxTkpNZHdxWnBpYmJRQzFvWkRyU1hkYk1XRjJ5eWxEZkFSSGFVcnhta0VqeU9nVGRCTTkzODJkcmY1ZEJaekNrWnZXcXhZSHpFVlJJYTdzRWdfcEUtZ0lGWFVFTHI1MzVwalROTGNKcW52QlZibzlsRdIBqgFBVV95cUxOcERfdkJYZS1iOE16TWpjQWZBTkZCekI3N3owR1R5eE9EMlFFcmRUb1pXZUpRWVJHME9VR3FYRThOSXhyTkVsWXdnb2o2S0hjUGRKRXRtelN5Z0pqekJJYlQwN19hMFFvU1VlVk02LVhVVmdxeGRSb3pEaW01SkpNeWs1VERTdVBjQ2JkcnNjYnM4dWMwLXhKeURZNWRLdjJ6RnBXTkRDSjIxdw?oc=5</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -4662,24 +4662,24 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Exdirector del FMI ve acceso al mercado como llave para resolver la deuda argentina con el organismo    Bloomberg Línea</t>
+          <t>Deuda: el Gobierno volvió a comprarle DEGs a EEUU y le pagó u$s800 millones al FMI    Ambito</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Deuda: el Gobierno volvió a comprarle DEGs a EEUU y le pagó u$s800 millones al FMI - Ambito</t>
+          <t>Deuda con el FMI: el Gobierno pagará más de USD 800 millones - Border Periodismo</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPX01IRnBJTllEY2RRZlBQYkJMMjRlMFdLcVU5cGFJdTY3WkZaVjNOTVRfNmwxTkpNZHdxWnBpYmJRQzFvWkRyU1hkYk1XRjJ5eWxEZkFSSGFVcnhta0VqeU9nVGRCTTkzODJkcmY1ZEJaekNrWnZXcXhZSHpFVlJJYTdzRWdfcEUtZ0lGWFVFTHI1MzVwalROTGNKcW52QlZibzlsRdIBqgFBVV95cUxOcERfdkJYZS1iOE16TWpjQWZBTkZCekI3N3owR1R5eE9EMlFFcmRUb1pXZUpRWVJHME9VR3FYRThOSXhyTkVsWXdnb2o2S0hjUGRKRXRtelN5Z0pqekJJYlQwN19hMFFvU1VlVk02LVhVVmdxeGRSb3pEaW01SkpNeWs1VERTdVBjQ2JkcnNjYnM4dWMwLXhKeURZNWRLdjJ6RnBXTkRDSjIxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNT09rUTNGUmE5Y0ptdjdHNWR1c05ZUVF5eFhxNHItQUpRY2tjMFhGUVhqeU9kZU1kQjZuWHpldGlQb2tGS2pCVUJzMXpvNnZiLThpbTdOVFJSOWxmcmQ1RXBDTUlER20wYWx6eWY3b2xEVVQwYWRtcm5YQ0loUEZYamFDT3BIT1ZDRk0yQUZkSVpPODc3N1Ztd29FSlBkd0VELVRkM2JKR002dldybVh0SDg0VnoxNTFSQkJVcWRLZThUQ3pXQTJDVW9aRXQ?oc=5</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -4694,24 +4694,24 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Deuda: el Gobierno volvió a comprarle DEGs a EEUU y le pagó u$s800 millones al FMI    Ambito</t>
+          <t>Deuda con el FMI: el Gobierno pagará más de USD 800 millones    Border Periodismo</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Deuda con el FMI: el Gobierno pagará más de USD 800 millones - Border Periodismo</t>
+          <t>Deuda récord: supera los USD 483.000 millones y crecen los vencimientos de corto plazo para Nación - NEA HOY</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNT09rUTNGUmE5Y0ptdjdHNWR1c05ZUVF5eFhxNHItQUpRY2tjMFhGUVhqeU9kZU1kQjZuWHpldGlQb2tGS2pCVUJzMXpvNnZiLThpbTdOVFJSOWxmcmQ1RXBDTUlER20wYWx6eWY3b2xEVVQwYWRtcm5YQ0loUEZYamFDT3BIT1ZDRk0yQUZkSVpPODc3N1Ztd29FSlBkd0VELVRkM2JKR002dldybVh0SDg0VnoxNTFSQkJVcWRLZThUQ3pXQTJDVW9aRXQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNMWl4TkFWdUsxeEN5eUJ4R2RwSDVSaTNLbGYybTA3WDROb29GZkU5QVo4VVczWVg4eFktdlg4SlZXbnpuX1doWHFnbEt6eHg2ZG9ZVEZiTjdKUjBSdElwXzRhVzJNellqQy1aaGRTN2pab0FQRGtmYVpmVHNoMjMwc3N5THV2RGxrbUozZ0hqRmhwTnUwQXlVZDZGaUNoX19MUjhfZGRfRnBNVnhjS3lZNS12dFRVaXhvT0JMMy1ORHV2ZXhhUm9B?oc=5</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -4726,24 +4726,24 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Deuda con el FMI: el Gobierno pagará más de USD 800 millones    Border Periodismo</t>
+          <t>Deuda récord: supera los USD 483.000 millones y crecen los vencimientos de corto plazo para Nación    NEA HOY</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Deuda récord: supera los USD 483.000 millones y crecen los vencimientos de corto plazo para Nación - NEA HOY</t>
+          <t>Uno de los negociadores de la deuda con el FMI en 2021 advierte que con Milei hoy es menos pagable - Perfil</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNMWl4TkFWdUsxeEN5eUJ4R2RwSDVSaTNLbGYybTA3WDROb29GZkU5QVo4VVczWVg4eFktdlg4SlZXbnpuX1doWHFnbEt6eHg2ZG9ZVEZiTjdKUjBSdElwXzRhVzJNellqQy1aaGRTN2pab0FQRGtmYVpmVHNoMjMwc3N5THV2RGxrbUozZ0hqRmhwTnUwQXlVZDZGaUNoX19MUjhfZGRfRnBNVnhjS3lZNS12dFRVaXhvT0JMMy1ORHV2ZXhhUm9B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOejUtLVEtb1pLSTM2VXgxUXJGSm1RMFRDenFjRnhhSVU2ajZPMFpvYjI0T2ZBQVBhZTQyZmc2dkY2X3RsNjdDQjI4dDB2V3ZTdVlvM3FqZG5ZYXBLbXBUS2NlOHMxZEpVOXJ4LXlRaUJveUN3NHBMWUJMdjdyRHVZTnhPY2ppbFZYYkp5MmZGZjkwelZRTFg0RmlmVXFIbmpaSXdhQnBoSG1LUVRvUmR3OXRzanF6QmdIUmxlSVVRdWV0aURhTHZuQTdNWFZLUXlOczc2S1FtTUZMcjFickhWQlVZVjFiMmFlVTZKeXFWN3Rpd9IB9wFBVV95cUxQa2M1ekpER0wzTEI3R2VkX1JmbThDWUI0aFdYVEhFVmpteXhXOExwZTNudW51ay1uN1Y4ajhMRnNtNGNoamFZUVZJblJmMGpuR09EWkVfSTJ2eHIxVzNwZDVJRTRRWHAtVnM2Y0pTLXI3SXA2MkUzOHVjakJJd1pLb2lmamVtMWdkajZsX0FwenhHMFlDRDVPN18xOExEbjZUVDV6Rlc3WW42Szk1eGt4X2lWTHJFZVk4bTBWYmZtVVI2WVBtOE9sZnQweTdQc2thZWFIRi1WLVhLcTdYQ1A1aXZyWWVfVHBZU3FyaXQyVjFKUTFuZDhJ?oc=5</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -4758,24 +4758,24 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Deuda récord: supera los USD 483.000 millones y crecen los vencimientos de corto plazo para Nación    NEA HOY</t>
+          <t>Uno de los negociadores de la deuda con el FMI en 2021 advierte que con Milei hoy es menos pagable    Perfil</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Uno de los negociadores de la deuda con el FMI en 2021 advierte que con Milei hoy es menos pagable - Perfil</t>
+          <t>¿Cuánto endeudaron al Estado los últimos gobiernos y cuál es el saldo parcial de la gestión Milei? - Infobae</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOejUtLVEtb1pLSTM2VXgxUXJGSm1RMFRDenFjRnhhSVU2ajZPMFpvYjI0T2ZBQVBhZTQyZmc2dkY2X3RsNjdDQjI4dDB2V3ZTdVlvM3FqZG5ZYXBLbXBUS2NlOHMxZEpVOXJ4LXlRaUJveUN3NHBMWUJMdjdyRHVZTnhPY2ppbFZYYkp5MmZGZjkwelZRTFg0RmlmVXFIbmpaSXdhQnBoSG1LUVRvUmR3OXRzanF6QmdIUmxlSVVRdWV0aURhTHZuQTdNWFZLUXlOczc2S1FtTUZMcjFickhWQlVZVjFiMmFlVTZKeXFWN3Rpd9IB9wFBVV95cUxQa2M1ekpER0wzTEI3R2VkX1JmbThDWUI0aFdYVEhFVmpteXhXOExwZTNudW51ay1uN1Y4ajhMRnNtNGNoamFZUVZJblJmMGpuR09EWkVfSTJ2eHIxVzNwZDVJRTRRWHAtVnM2Y0pTLXI3SXA2MkUzOHVjakJJd1pLb2lmamVtMWdkajZsX0FwenhHMFlDRDVPN18xOExEbjZUVDV6Rlc3WW42Szk1eGt4X2lWTHJFZVk4bTBWYmZtVVI2WVBtOE9sZnQweTdQc2thZWFIRi1WLVhLcTdYQ1A1aXZyWWVfVHBZU3FyaXQyVjFKUTFuZDhJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNVFB0WTQ2ZG5RZ29lalVNNWwyS0NJdVljTzBSZ2F5MUFUT2tXLXF0ejhSVEJwVS1IWTlGT2Iza1RjYmxUR3daaVo0TXRkaFhuMWtkSjhLbDlNY3p5U2tfd2QtWFAxc0thOF9FYTZvQmQzYzZyWklpemw0SkREeXh6b3hDbGFUaXE5c3VDT2FadHZkbHZ6Z1puMUtNbzE2UzFjLVRkcGprb3R4cE13Z1hBajhNTnp1M09wcWgydGg3UFcxVXR6WEM1aW9XckI0VFlYdldUOFlGNEHSAfMBQVVfeXFMTmZ0LWdWTnJtc09OVWdHcTBRTW5heVJYTldjR3BoOExpZThHNlpUZXZQdXA5VU9nbWYzTlk2OVVzOFFRMk5UTUlTVXhmY2VXc09Wd0hOdnUtZUJQaWZpbnVZdXA2c3VxeW5ZU2I2ZjdkZGhJNUJobEt0RWktOG1VcWVDREoyaFdmTk1KTWlWdnhadVBnWXFxX3pKOFRBQy1Vd1RxYlEwMWZDM3NLNndUX1ZYcVZOaUpyMjFFY2g0UGd1WHFfZzFlbTU4dUkxZHNZVVEtdTNpNG5BQlNBMXV1SjgxMk10Q2cxZVpYdGM3NlJBdVhZ?oc=5</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -4790,24 +4790,24 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Uno de los negociadores de la deuda con el FMI en 2021 advierte que con Milei hoy es menos pagable    Perfil</t>
+          <t>¿Cuánto endeudaron al Estado los últimos gobiernos y cuál es el saldo parcial de la gestión Milei?    Infobae</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>¿Cuánto endeudaron al Estado los últimos gobiernos y cuál es el saldo parcial de la gestión Milei? - Infobae</t>
+          <t>Qué claves mira Wall Street del programa económico de Milei: entusiasmo y una duda para 2027 - Infobae</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNVFB0WTQ2ZG5RZ29lalVNNWwyS0NJdVljTzBSZ2F5MUFUT2tXLXF0ejhSVEJwVS1IWTlGT2Iza1RjYmxUR3daaVo0TXRkaFhuMWtkSjhLbDlNY3p5U2tfd2QtWFAxc0thOF9FYTZvQmQzYzZyWklpemw0SkREeXh6b3hDbGFUaXE5c3VDT2FadHZkbHZ6Z1puMUtNbzE2UzFjLVRkcGprb3R4cE13Z1hBajhNTnp1M09wcWgydGg3UFcxVXR6WEM1aW9XckI0VFlYdldUOFlGNEHSAfMBQVVfeXFMTmZ0LWdWTnJtc09OVWdHcTBRTW5heVJYTldjR3BoOExpZThHNlpUZXZQdXA5VU9nbWYzTlk2OVVzOFFRMk5UTUlTVXhmY2VXc09Wd0hOdnUtZUJQaWZpbnVZdXA2c3VxeW5ZU2I2ZjdkZGhJNUJobEt0RWktOG1VcWVDREoyaFdmTk1KTWlWdnhadVBnWXFxX3pKOFRBQy1Vd1RxYlEwMWZDM3NLNndUX1ZYcVZOaUpyMjFFY2g0UGd1WHFfZzFlbTU4dUkxZHNZVVEtdTNpNG5BQlNBMXV1SjgxMk10Q2cxZVpYdGM3NlJBdVhZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQZm1GaEoyTklZZDFxcVNPQldES0FkRXJ1U0RxUHEybUl5MWw2RzhOWVdCY0pYT0N0cGE2b3U1d2lXdnpmMDZFZUJzQ3pqUFRvMkwwRWhJU1VYdnJkOGs2U0ZYMHVoMkR4N0NqZlQ2UkpyTExDeFRhX3lQM0ZOUDJiSXFlQVVLWjJHQlRNMnJuTDJ5ZmJoZnhPSjllTm8xQzhPMG5JVFBoMlpXQU9WY1o3OU5UcUJrcVJWRWFXV3FrUXYyb2JMcHN3OEVFaHhYWXFsaEHSAewBQVVfeXFMTlFNSnctUlozeHIzazNiZE5PTVZ3R3BHdkNnNDh0RDE4eEJ0TURZZWoya2pjNk95cVpzMEljQUtRTWpfbHhEb0ZPdFVQbHRFRU5fSExiMjlGc29FRWdwal9sVTZBS0FVZExKdUdzZDhUWV9wMFIwTGM0cm5HVzExUUNTX00yQm5GTnR4Tk5ObEIwVXJNLTczY24taTc2Qnowa0VoMmo1YTBMbHVuUF9GaGo5Qk9hT0RKUnZidVUyVDktUC0tVS1TMS1xckgzZV9iMmRjdkdyX1FtSmpOWHFwYmVrRFpCZ1NPTjJ6UmE?oc=5</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -4822,24 +4822,24 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>¿Cuánto endeudaron al Estado los últimos gobiernos y cuál es el saldo parcial de la gestión Milei?    Infobae</t>
+          <t>Qué claves mira Wall Street del programa económico de Milei: entusiasmo y una duda para 2027    Infobae</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Qué claves mira Wall Street del programa económico de Milei: entusiasmo y una duda para 2027 - Infobae</t>
+          <t>Qué implica el próximo desembolso de USD 1.000 millones que llegará desde el FMI - Infobae</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQZm1GaEoyTklZZDFxcVNPQldES0FkRXJ1U0RxUHEybUl5MWw2RzhOWVdCY0pYT0N0cGE2b3U1d2lXdnpmMDZFZUJzQ3pqUFRvMkwwRWhJU1VYdnJkOGs2U0ZYMHVoMkR4N0NqZlQ2UkpyTExDeFRhX3lQM0ZOUDJiSXFlQVVLWjJHQlRNMnJuTDJ5ZmJoZnhPSjllTm8xQzhPMG5JVFBoMlpXQU9WY1o3OU5UcUJrcVJWRWFXV3FrUXYyb2JMcHN3OEVFaHhYWXFsaEHSAewBQVVfeXFMTlFNSnctUlozeHIzazNiZE5PTVZ3R3BHdkNnNDh0RDE4eEJ0TURZZWoya2pjNk95cVpzMEljQUtRTWpfbHhEb0ZPdFVQbHRFRU5fSExiMjlGc29FRWdwal9sVTZBS0FVZExKdUdzZDhUWV9wMFIwTGM0cm5HVzExUUNTX00yQm5GTnR4Tk5ObEIwVXJNLTczY24taTc2Qnowa0VoMmo1YTBMbHVuUF9GaGo5Qk9hT0RKUnZidVUyVDktUC0tVS1TMS1xckgzZV9iMmRjdkdyX1FtSmpOWHFwYmVrRFpCZ1NPTjJ6UmE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQTFAyeHQxeHRqSy1qX1BLNF9TcDNGeEl5T1N1bGxiV2FWd0U0a01wZWp0a1pmOW04Umw5Y05tcm1BNGJVeE5kMkFnWnVyRHNiVzlJRUtfOHFCVG15Yzd3d1IxNlJPM0FlUnBpUmhlRE5mdldmQXVpbGc5QXB1MWVTb3dTQnJxREFObHM3ZjAxS1JFUFFUcnkwT0FTak16SkdnMkJ4Z3ZETHJDRmczSU9hTmM3TFJGcENfRkJybEczS2PSAdsBQVVfeXFMTmdaeUdaQTZCNUpJNkRfTU14STN4S1NsbFpWS29zSTlsaExsUkE4alo3MDNfenNvUGhTR3hxQWU1X2Q4TW9XQzUtX0hxR2tVdzcxa3EtdF9kWXJTMnNOR21xS1dkRDVUUlZMbFd6b2NuVndCNkNXMDhoMWJLcFVCc21NdjZiXzBDYnRSeF9ScXZqXzdZXzR4ZmltUWxLV2VoeE5aWlVod1oxZEFrQWw0eUsxMlRKZFFKd0U1LVY4QnlXNF9HZ0dzUTl4RG1nYk9udWFiM0pHZnpJZFlz?oc=5</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -4859,19 +4859,19 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Qué claves mira Wall Street del programa económico de Milei: entusiasmo y una duda para 2027    Infobae</t>
+          <t>Qué implica el próximo desembolso de USD 1.000 millones que llegará desde el FMI    Infobae</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Qué implica el próximo desembolso de USD 1.000 millones que llegará desde el FMI - Infobae</t>
+          <t>«¿De qué nos sirvió?»: el furioso tuit de Vanesa Siley por la deuda de 70 mil millones con el FMI - El Intransigente</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQTFAyeHQxeHRqSy1qX1BLNF9TcDNGeEl5T1N1bGxiV2FWd0U0a01wZWp0a1pmOW04Umw5Y05tcm1BNGJVeE5kMkFnWnVyRHNiVzlJRUtfOHFCVG15Yzd3d1IxNlJPM0FlUnBpUmhlRE5mdldmQXVpbGc5QXB1MWVTb3dTQnJxREFObHM3ZjAxS1JFUFFUcnkwT0FTak16SkdnMkJ4Z3ZETHJDRmczSU9hTmM3TFJGcENfRkJybEczS2PSAdsBQVVfeXFMTmdaeUdaQTZCNUpJNkRfTU14STN4S1NsbFpWS29zSTlsaExsUkE4alo3MDNfenNvUGhTR3hxQWU1X2Q4TW9XQzUtX0hxR2tVdzcxa3EtdF9kWXJTMnNOR21xS1dkRDVUUlZMbFd6b2NuVndCNkNXMDhoMWJLcFVCc21NdjZiXzBDYnRSeF9ScXZqXzdZXzR4ZmltUWxLV2VoeE5aWlVod1oxZEFrQWw0eUsxMlRKZFFKd0U1LVY4QnlXNF9HZ0dzUTl4RG1nYk9udWFiM0pHZnpJZFlz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQbVhNQzV5eXhSdWdvRXZ1NnNzN3ZfSGFTQUtHY2pDZG5ISlV3OEdIVGYyTXJRN2dneVF5UmhOWmxVM1FvWVRIV3JEZkRpTGU4aW5tV2ZnTTVuTlltQkx3TnFNNFdiQTVCNDRBZnRIbjhlVGd0dTZhZ2tUT0I2cWN3U0c5TnNIT1B3VGlrRkQ4cHdtQ3NTbUVNcXN4aEVIbU91Y1pyYnpiOXI5aWlMOTVldEF2Q2dMY1ZuVlgxN1g5dnJHSnJhTEhDMg?oc=5</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -4886,29 +4886,29 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Qué implica el próximo desembolso de USD 1.000 millones que llegará desde el FMI    Infobae</t>
+          <t>«¿De qué nos sirvió?»: el furioso tuit de Vanesa Siley por la deuda de 70 mil millones con el FMI    El Intransigente</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>«¿De qué nos sirvió?»: el furioso tuit de Vanesa Siley por la deuda de 70 mil millones con el FMI - El Intransigente</t>
+          <t>Top Argentina official resigned after return to markets shelved - Buenos Aires Times</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQbVhNQzV5eXhSdWdvRXZ1NnNzN3ZfSGFTQUtHY2pDZG5ISlV3OEdIVGYyTXJRN2dneVF5UmhOWmxVM1FvWVRIV3JEZkRpTGU4aW5tV2ZnTTVuTlltQkx3TnFNNFdiQTVCNDRBZnRIbjhlVGd0dTZhZ2tUT0I2cWN3U0c5TnNIT1B3VGlrRkQ4cHdtQ3NTbUVNcXN4aEVIbU91Y1pyYnpiOXI5aWlMOTVldEF2Q2dMY1ZuVlgxN1g5dnJHSnJhTEhDMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOSmY3Zm02WTlSdEl2WTl3cEc4MXZyT3JFeFpzU2xhTHdRc2ItczFJaWliYkNJOU95NTd6RkNLeGNVbnZRN3ZEdG1Wc1pPVy0zcWw1bXdPZnZBTldnZGdMSlN2aDl4OEV4TUNRcWNIVGIwY0JvQnN5N2xkQlg0Yl83eXBIVS0wbEhXckxHQzZEUm1ESlB6M2Zpa21iQTB0Zms1TGItVThaNDBBb2FNeXfSAbMBQVVfeXFMTWw3TmJrcWNqcnhmbFU3VENPUzhDbjhmUUk2MXB1ekdWNDEyZHNiNzNRbk0yd2NYenVlNWFSZFRNaW90T3hweGtJYXFSYnV5S2tOSlRGa1lSSWUzWnpEcFBaWVQwY1Y5cGNpbU1qQ0I3c2tfNGQwY1hBcWRZRm03Zk16S2YtOTg3NUVUeVF0bl85dUV1WVJmXzFZOVN2X3I0bkxmcmxtOWxQdFlIMy0tWWRpcUE?oc=5</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Google News - FMI</t>
+          <t>Google News - Argentina EN</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -4918,24 +4918,24 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>«¿De qué nos sirvió?»: el furioso tuit de Vanesa Siley por la deuda de 70 mil millones con el FMI    El Intransigente</t>
+          <t>Top Argentina official resigned after return to markets shelved    Buenos Aires Times</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Top Argentina official resigned after return to markets shelved - Buenos Aires Times</t>
+          <t>Argentina’s economy records sharpest monthly contraction under Javier Milei - Financial Times</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOSmY3Zm02WTlSdEl2WTl3cEc4MXZyT3JFeFpzU2xhTHdRc2ItczFJaWliYkNJOU95NTd6RkNLeGNVbnZRN3ZEdG1Wc1pPVy0zcWw1bXdPZnZBTldnZGdMSlN2aDl4OEV4TUNRcWNIVGIwY0JvQnN5N2xkQlg0Yl83eXBIVS0wbEhXckxHQzZEUm1ESlB6M2Zpa21iQTB0Zms1TGItVThaNDBBb2FNeXfSAbMBQVVfeXFMTWw3TmJrcWNqcnhmbFU3VENPUzhDbjhmUUk2MXB1ekdWNDEyZHNiNzNRbk0yd2NYenVlNWFSZFRNaW90T3hweGtJYXFSYnV5S2tOSlRGa1lSSWUzWnpEcFBaWVQwY1Y5cGNpbU1qQ0I3c2tfNGQwY1hBcWRZRm03Zk16S2YtOTg3NUVUeVF0bl85dUV1WVJmXzFZOVN2X3I0bkxmcmxtOWxQdFlIMy0tWWRpcUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPREc1NDM0ZVZyVEM0ODdORmtnV092cXpGQmtsMTB4UjVkTVZkd0NrZlVHalNzNDJwSFJCV19vOWFabTVLSGszVGtHZHlVVWMxd29BWDc3MnJlSEpiUy05elBUWFhuR0NTTGJvUFhnX1ZnWU5vaE5LVmhqMy1LUklyZVZhdks?oc=5</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -4950,24 +4950,24 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Top Argentina official resigned after return to markets shelved    Buenos Aires Times</t>
+          <t>Argentina’s economy records sharpest monthly contraction under Javier Milei    Financial Times</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Argentina’s economy records sharpest monthly contraction under Javier Milei - Financial Times</t>
+          <t>Argentina - Resources, Power, Economy - Britannica</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPREc1NDM0ZVZyVEM0ODdORmtnV092cXpGQmtsMTB4UjVkTVZkd0NrZlVHalNzNDJwSFJCV19vOWFabTVLSGszVGtHZHlVVWMxd29BWDc3MnJlSEpiUy05elBUWFhuR0NTTGJvUFhnX1ZnWU5vaE5LVmhqMy1LUklyZVZhdks?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5OaWRwb2M3MHFRX2kzRERsVEhjRnJiNTFnRTBPdXVYSFplUlJ1UGJOWFJocWc1TWxlOU5XUU1Cb3VuSzJBN1lfVUIzanBMSnM3MGdBaEI5NFZwQ193YXI5MUNVR21pbW1SeEZLa1QyNA?oc=5</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Argentina’s economy records sharpest monthly contraction under Javier Milei    Financial Times</t>
+          <t>Argentina - Resources, Power, Economy    Britannica</t>
         </is>
       </c>
     </row>

--- a/source_status.xlsx
+++ b/source_status.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
     </row>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
     </row>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
     </row>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
     </row>
@@ -692,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F135"/>
+  <dimension ref="A1:F256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -738,12 +738,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Javier Milei y sus medidas, en vivo: el regreso de Adorni a las conferencias de prensa y el avance de la causa judicial</t>
+          <t>Javier Milei y sus medidas, en vivo: su defensa a Manuel Adorni y la eliminación de las PASO</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/politica/javier-milei-y-sus-medidas-en-vivo-el-regreso-de-adorni-a-las-conferencias-de-prensa-y-el-avance-de-nid04052026/</t>
+          <t>https://www.lanacion.com.ar/politica/javier-milei-y-sus-medidas-en-vivo-su-defensa-a-adorni-y-la-eliminacion-de-las-paso-nid07052026/</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>El Gobierno apuesta a recuperar iniciativa con las conferencias de Adorni y la agenda legislativa</t>
+          <t>El juez volvió a citar a Ariel Vallejo, tras el pedido de detención que hizo la fiscal Incardona</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/politica/el-gobierno-apuesta-a-recuperar-iniciativa-con-las-conferencias-de-adorni-y-la-agenda-legislativa-nid03052026/</t>
+          <t>https://www.lanacion.com.ar/politica/el-juez-volvio-a-citar-a-ariel-vallejo-tras-el-pedido-de-detencion-que-hizo-la-fiscal-incardona-nid06052026/</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -790,24 +790,24 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>En la Casa Rosada creen que el paso del jefe de Gabinete por el Congreso fue una “bisagra”; y daban por “casi segura” la presentación del ministro coordinador ante los periodistas este lunes</t>
+          <t>El magistrado dispuso escucharlo el 26 de mayo; la Cámara de Casación unificó en ese juzgado los casos de Sur Finanzas</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Aprobaron cambios en las pruebas Aprender: cuáles son las novedades y cuándo se implementan</t>
+          <t>Ya factura US$150 millones: sorpresa en un mercado que en la Argentina crece más que las famosas “tasas chinas”</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/sociedad/aprobaron-cambios-en-las-pruebas-aprender-cuales-son-las-novedades-y-cuando-se-implementan-nid03052026/</t>
+          <t>https://www.lanacion.com.ar/economia/campo/ya-factura-us150-millones-sorpresa-en-un-mercado-que-en-la-argentina-crece-mas-que-las-famosas-tasas-nid06052026/</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -822,24 +822,24 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>El Consejo Federal de Educación definió intercalar evaluaciones censales y muestrales; la estrategia</t>
+          <t>Con un avance superior al 14% anual, las industrias de bioinsumos para el agro ganan terreno y abren una nueva etapa productiva</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Solo en Off | El funcionario libertario que debió asimilar la agenda woke de un país europeo</t>
+          <t>Paolo Rocca deja de ser el CEO de Tenaris</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/politica/solo-en-off-el-funcionario-libertario-que-sufrio-la-agenda-woke-de-un-pais-europeo-nid04052026/</t>
+          <t>https://www.lanacion.com.ar/economia/paolo-rocca-deja-de-ser-el-ceo-de-tenaris-nid06052026/</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -854,24 +854,24 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Carrió espanta a sus asesores con sus videos; Nicolini, asesora estrella de Kicillof; y Milei tiene invitación para Londres</t>
+          <t>Se corre de la operación de la empresa insignia que produce tubos sin costura; sin embargo, seguirá siendo presidente de la compañía; asume en su lugar Gabriel Podskubka</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>La empresa del crucero en el que se registró un brote de hantavirus emitió un comunicado</t>
+          <t>Karina-Patricia: una relación con vaivenes entre las dos mujeres más influyentes de LLA</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/sociedad/la-empresa-del-crucero-en-el-que-se-registro-un-brote-de-hantavirus-emitio-un-comunicado-nid04052026/</t>
+          <t>https://www.lanacion.com.ar/politica/karina-patricia-una-relacion-con-vaivenes-entre-las-dos-mujeres-mas-influyentes-de-lla-nid06052026/</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -886,24 +886,24 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>La compañía neerlandesa Oceanwide Expeditions informó que hay un pasajero en terapia intensiva y dos tripulantes que requirieron atención urgente</t>
+          <t>Tienen diferencias sobre el rol de Manuel Adorni en el Gobierno; ya habían tenido rispideces por el protagonismo de la senadora</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Los secretos detrás del emblemático modelo de los 70 que enamoró a los argentinos</t>
+          <t>Abril fue mejor que marzo; ¿Qué pasará en mayo?</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/autos/los-secretos-detras-del-emblematico-modelo-de-los-70-que-enamoro-a-los-argentinos-nid03052026/</t>
+          <t>https://www.lanacion.com.ar/economia/abril-fue-mejor-que-marzo-que-pasara-en-mayo-nid06052026/</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -918,24 +918,24 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Este modelo argentino logró cruzar la línea de llegada de las 84 Horas de Nürburgring, una carrera de resistencia que tomó lugar en Alemania en 1969</t>
+          <t>Las estadísticas son mejores que las informaciones puntuales, por su mayor cobertura, pero demoran más en confeccionarse y publicarse</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Las razones por las que en tan poco tiempo la industria automotriz china revolucionó al mercado mundial</t>
+          <t>Patricia Bullrich le pidió a Adorni que presente de “inmediato” su declaración jurada de bienes</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/autos/las-razones-por-las-que-en-tan-poco-tiempo-la-industria-automotriz-china-revoluciono-al-mercado-nid28042026/</t>
+          <t>https://www.lanacion.com.ar/politica/patricia-bullrich-le-pidio-a-adorni-que-presente-de-inmediato-su-declaracion-jurada-de-bienes-nid06052026/</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -950,24 +950,24 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>China es hoy el mayor productor y exportador de vehículos en el mundo, asimismo, su mercado local acompaña estas cifras</t>
+          <t>La senadora de La Libertad Avanza le hizo este reclamo públicamente al jefe de Gabinete; advirtió que las denuncias “empantanan” a la administración; es la primera vez que una figura oficialista marca diferencias con un asunto tan sensible al poder libertario</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Un especialista revela qué hacer si te cruzan un auto para robarte: la maniobra clave para escapar</t>
+          <t>Javier Milei defendió a Adorni y dijo que el funcionario adelantará su declaración jurada: “No voy a ejecutar a un inocente”</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/autos/un-especialista-revela-que-hacer-si-te-cruzan-un-auto-para-robarte-la-maniobra-clave-para-escapar-nid23042026/</t>
+          <t>https://www.lanacion.com.ar/lnmas/javier-milei-defendio-a-adorni-hablaban-de-una-cascada-y-resulto-que-eran-dos-canitos-de-agua-nid06052026/</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -982,24 +982,24 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>El avance de la inseguridad  obliga a repensar la conducción defensiva; un instructor especializado explica paso a paso cómo reaccionar y qué errores evitar</t>
+          <t>El Presidente habló en exclusiva con LN+ sobre la situación judicial de su jefe de Gabinete, investigado por presunto enriquecimiento ilícito; “Ni en pedo se va”, advirtió</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Cómo es el nuevo modelo de una automotriz alemana del que vendió 20 millones de unidades en el mundo</t>
+          <t>Marcela Pagano cruzó a Milei por acusarla de “mentirosa compulsiva”: “Confundió rating con grandeza”</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/autos/como-es-el-nuevo-modelo-de-una-automotriz-alemana-del-que-vendio-20-millones-de-unidades-en-el-mundo-nid02052026/</t>
+          <t>https://www.lanacion.com.ar/politica/marcela-pagano-cruzo-a-milei-por-acusarla-de-mentirosa-compulsiva-confundio-rating-con-grandeza-nid07052026/</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1014,24 +1014,24 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Volkswagen presentó en Alemania la evolución del Polo,; sus características y precio</t>
+          <t>El Presidente la increpó durante una entrevista con LN+; la diputada enumeró una serie de promesas de campaña que, según su análisis, el mandatario no cumplió</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Por qué algunas casas antiguas tienen puertas muy altas: la historia detrás del diseño</t>
+          <t>Victor Glover, piloto del Artemis II: “Créannos, se ven increíbles, se ven hermosos, y desde aquí se ven como una sola cosa”</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/propiedades/por-que-algunas-casas-antiguas-tienen-puertas-muy-altas-la-historia-detras-del-diseno-nid29042026/</t>
+          <t>https://www.lanacion.com.ar/el-mundo/victor-glover-piloto-del-artemis-ii-creannos-se-ven-increibles-se-ven-hermosos-y-desde-aqui-se-ven-nid07052026/</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1046,24 +1046,24 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>La arquitectura porteña de fines del siglo XIX y comienzos del XX privilegiaba los ambientes grandes para regular la temperatura y favorecer la circulación del aire</t>
+          <t>Se trató de los primeros mensajes a la Tierra mientras realizaban la misión; el astronauta de la cápsula Orión reflexionó sobre la inmensidad del espacio</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>El rumbo y la matriz productiva del crecimiento argentino</t>
+          <t>Alejandra Monteoliva mantuvo reuniones con funcionarios estadounidenses de alto rango</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/opinion/el-rumbo-y-la-matriz-productiva-del-crecimiento-argentino-nid04052026/</t>
+          <t>https://www.lanacion.com.ar/politica/javier-milei-y-sus-medidas-en-vivo-nid06052026/</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1078,29 +1078,29 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>El país necesita consolidar la estabilidad sobre sus ventajas comparativas y liberar su potencial como productor y exportador</t>
+          <t>El minuto a minuto de las decisiones del Presidente, las reacciones de la oposición y las declaraciones de los funcionarios</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Construyeron un rascacielos de 200 metros de altura y se olvidaron el hueco del ascensor</t>
+          <t>La producción de autos no pudo sostener el repunte en abril y se desplomó 18,6% en el primer cuatrimestre</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/propiedades/construccion-y-diseno/insolito-construyeron-un-rascacielos-de-200-metros-de-altura-y-se-olvidaron-el-hueco-del-ascensor-nid30042026/</t>
+          <t>https://www.ambito.com/economia/la-produccion-autos-no-pudo-sostener-el-repunte-abril-y-se-desplomo-186-el-primer-cuatrimestre-n6274779</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>LA NACION</t>
+          <t>Ambito - Economia</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1110,29 +1110,29 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Benidorm es la segunda ciudad del mundo con más rascacielos por habitante</t>
+          <t>La industria automotriz sigue mostrando señales de debilidad, afectada por la apertura comercial y las menores ventas en el mercado interno.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>La agenda de la TV del lunes: se completa la fecha del Apertura, la Premier League y la Serie A</t>
+          <t>Plazo fijo por el piso: cuánto gano si invierto $300.000 a 30 días</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/deportes/futbol/la-agenda-de-la-tv-del-lunes-se-completa-la-fecha-del-apertura-la-premier-league-y-la-serie-a-nid03052026/</t>
+          <t>https://www.ambito.com/economia/plazo-fijo-el-piso-cuanto-gano-si-invierto-300000-30-dias-n6274657</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>LA NACION</t>
+          <t>Ambito - Economia</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1142,29 +1142,29 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>La actividad deportiva en el inicio de la semana, disponible a través de las pantallas</t>
+          <t>Las tasas de interés se mantienen bajas en mayo y el rendimiento de los depósitos a corto plazo se ven reducidos.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Federico Sturzenegger confirmó que en junio enviará la desregulación inmobiliaria al Congreso para bajar costos en la compraventa</t>
+          <t>Atención: la fecha de mayo que te hará ahorrar dólares en tus compras en el exterior</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/propiedades/casas-y-departamentos/federico-sturzenegger-confirmo-que-en-junio-enviara-la-desregulacion-inmobiliaria-al-congreso-para-nid28042026/</t>
+          <t>https://www.ambito.com/economia/atencion-la-fecha-mayo-que-te-hara-ahorrar-dolares-tus-compras-el-exterior-n6274467</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>LA NACION</t>
+          <t>Ambito - Economia</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1174,29 +1174,29 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Frente a desarrolladores e inmobiliarios, el ministro cuestionó el rol actual de los colegios inmobiliarios y retomó la idea de desregular la actividad</t>
+          <t>El atraso cambiario otorga grandes oportunidades para realizar consumos afuera, y más aún si aprovechamos los días claves.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>El derrumbe de la recaudación propia y de la coparticipación bonaerense pone en alerta a los municipios</t>
+          <t>La producción minera marcó un nuevo récord en marzo: en litio saltó 70% anual y más que se duplicó en sal</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/politica/el-derrumbe-de-la-recaudacion-propia-y-de-la-coparticipacion-bonaerense-pone-en-alerta-a-los-nid03052026/</t>
+          <t>https://www.ambito.com/economia/la-produccion-minera-marco-un-nuevo-record-marzo-litio-salto-70-anual-y-mas-que-se-duplico-sal-n6274732</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>LA NACION</t>
+          <t>Ambito - Economia</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1206,24 +1206,24 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Los fondos por tasas y los que llegan desde el gobierno provincial se redujeron; en algunas intendencias afirman que se postergan gastos con el objetivo de garantizar prestaciones salariales y sociales</t>
+          <t>El Índice de Producción Industrial (IPI) minero trepó 10,4% interanual, la variación más alta en más de dos años. Vaca Muerta volvió a explicar el grueso del alza.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Intercambiá tu casa para no gastar dólares en alojamiento: cómo funciona esta propuesta</t>
+          <t>Atención: la fecha de mayo que te hará ahorrar dólares en tus compras en el exterior</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/intercambia-tu-casa-no-gastar-dolares-alojamiento-como-funciona-esta-propuesta-n6272776</t>
+          <t>https://www.ambito.com/economia/atencion-la-fecha-mayo-que-te-hara-ahorrar-dolares-tus-compras-el-exterior-n6274467</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1238,24 +1238,24 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Una alternativa distinta para el turismo reduce los costos y abre las puertas a experiencias únicas en distintos destinos.</t>
+          <t>El atraso cambiario otorga grandes oportunidades para realizar consumos afuera, y más aún si aprovechamos los días claves.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Scott Bessent prevé una caída del petróleo tras el conflicto en Medio Oriente, pese al fuerte salto de los precios</t>
+          <t>La producción minera marcó un nuevo récord en marzo: en litio saltó 70% anual y más que se duplicó en sal</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/scott-bessent-preve-una-caida-del-petroleo-el-conflicto-medio-oriente-pese-al-fuerte-salto-los-precios-n6273376</t>
+          <t>https://www.ambito.com/economia/la-produccion-minera-marco-un-nuevo-record-marzo-litio-salto-70-anual-y-mas-que-se-duplico-sal-n6274732</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>El secretario del Tesoro de EEUU aseguró que la suba actual de la energía es transitoria y anticipó una baja cuando se normalice la situación. Mientras tanto, el petróleo y la gasolina siguen en niveles elevados por el impacto del conflicto con Irán.</t>
+          <t>El Índice de Producción Industrial (IPI) minero trepó 10,4% interanual, la variación más alta en más de dos años. Vaca Muerta volvió a explicar el grueso del alza.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Dólares fuera del sistema: Bloomberg advierte que pese a los incentivos, persiste la desconfianza</t>
+          <t>RIGI: Luis Caputo anunció una inversión de Chevron por más de u$s10.000 millones</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/dolares-fuera-del-sistema-bloomberg-advierte-que-pese-los-incentivos-persiste-la-desconfianza-n6273362</t>
+          <t>https://www.ambito.com/economia/rigi-luis-caputo-anuncio-una-inversion-chevron-mas-us10000-millones-n6274740</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1302,24 +1302,24 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Aunque el Gobierno busca captar los dólares fuera del circuito formal, la mayoría de los argentinos sigue optando por el efectivo. El recuerdo del corralito y la falta de confianza continúan condicionando el comportamiento de los ahorristas.</t>
+          <t>El ministro adelantó un nuevo proyecto de la petrolera en medio de la gira oficial en Estados Unidos y destacó el volumen total de iniciativas presentadas entro del Régimen de Incentivo para Grandes Inversiones (RIGI).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Feriado del Día del Trabajador: viajaron 1,1 millones de turistas y gastaron $235.000 millones, pero con caída real del consumo</t>
+          <t>Radiografía de las exportaciones por provincia: crecimiento exponencial en algunas y bajas considerables en otras</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/feriado-del-dia-del-trabajador-viajaron-11-millones-turistas-y-gastaron-235000-millones-pero-caida-real-del-consumo-n6273337</t>
+          <t>https://www.ambito.com/economia/radiografia-las-exportaciones-provincia-crecimiento-exponencial-algunas-y-bajas-considerables-otras-n6274639</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1334,24 +1334,24 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Durante el fin de semana largo viajaron más de un millón de personas y se generaron $235.000 millones, pero el consumo fue más moderado, con escapadas breves y fuerte foco en gastos básicos.</t>
+          <t>Un reciente informe destacó que en la última década hubo cambios importantes a nivel regional en materia de ventas al exterior.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Petróleo y dólares: el efecto de la suba de producción de la OPEP+ en la economía de la Argentina</t>
+          <t>ARCA: ¿Podrán las pymes acceder al blanqueo laboral con la caída de ventas?</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/petroleo-y-dolares-el-efecto-la-suba-produccion-la-opep-la-la-argentina-n6273313</t>
+          <t>https://www.ambito.com/economia/arca-podran-las-pymes-acceder-al-blanqueo-laboral-la-caida-ventas-n6274617</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1366,24 +1366,24 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>La decisión llega en un contexto de alta volatilidad global y puede incidir directamente en precios internos y dinámica cambiaria.</t>
+          <t>Referentes del sector advirtieron que las empresas están teniendo dificultades para afrontar pagos corrientes y saldar planes previos. Alertan sobre riesgo de embargos.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Leve rebote de la actividad, inflación que no cede y un dólar bajo presión marcan el pulso: qué se espera para la economía en mayo</t>
+          <t>José Luis Daza prometió una "avalancha de dólares" y dijo que no habrá medidas para estimular la economía en 2027</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/leve-rebote-la-actividad-inflacion-alta-y-dolar-presion-marcan-el-pulso-que-se-espera-la-mayo-n6273310</t>
+          <t>https://www.ambito.com/economia/jose-luis-daza-prometio-una-avalancha-dolares-y-dijo-que-no-habra-medidas-estimular-la-2027-n6274513</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1398,24 +1398,24 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Marzo mostró señales de recuperación impulsadas por sectores transables, pero el repunte aún es frágil frente a una inflación que sigue elevada y expectativas cambiarias que anticipan mayor tensión en mayo.</t>
+          <t>El vice de Luis Caputo aseguró que la Argentina atraviesa un "cambio estructural" y prometió una masiva llegada de divisas por la energía y la minería. También afirmó que el programa financiero de 2026 ya está cerrado y se prepara el de 2027, donde pesará lo electoral.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>El peso argentino vive su mejor cuatrimestre en décadas, pero la fiesta tiene fecha de vencimiento</t>
+          <t>El Gobierno aprobó el Presupuesto Consolidado 2026 y lo enviará al Congreso: las claves</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/el-peso-argentino-vive-su-mejor-cuatrimestre-decadas-pero-la-fiesta-tiene-fecha-vencimiento-n6273279</t>
+          <t>https://www.ambito.com/economia/el-gobierno-aprobo-el-presupuesto-consolidado-2026-y-lo-enviara-al-congreso-las-claves-n6274393</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1430,24 +1430,24 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Un superávit extraordinario de divisas —cosecha récord, petróleo patagónico y deuda corporativa— sostuvo una apreciación nominal del 4,9% mientras la inflación acumulaba 9,4% en el primer trimestre. El Banco Central compró USD 7.000 millones. Los inversores celebran el carry; los exportadores indust</t>
+          <t>La decisión administrativa oficializó el esquema que integra a todo el sector público nacional. Aclaran que no modifica los presupuestos vigentes y proyecta superávit financiero.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>El origen primero de nuestro malestar económico</t>
+          <t>Plazo fijo: así operan los principales bancos hoy, miércoles 6 de mayo</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/el-origen-primero-nuestro-malestar-economico-n6273076</t>
+          <t>https://www.ambito.com/economia/plazo-fijo-asi-operan-los-principales-bancos-hoy-miercoles-6-mayo-n6274487</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1462,24 +1462,24 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Los mecanismos de fijación de precios que rigen en nuestro país continúan siendo un conflicto para el crecimiento económico estable.</t>
+          <t>Relevamiento reciente muestra diferencias en rendimientos según entidad y canal digital; qué conviene mirar antes de invertir pesos.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Al 90% de los hogares le quedan menos de $60.000 diarios tras cubrir gastos fijos, según informe</t>
+          <t>ARCA aplicó cambios y digitaliza el reintegro de IVA a turistas extranjeros: cómo es el trámite para agilizar devoluciones y controles</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/al-90-los-hogares-le-quedan-menos-60000-diarios-cubrir-gastos-fijos-segun-informe-n6273252</t>
+          <t>https://www.ambito.com/economia/arca-aplico-cambios-y-digitaliza-el-reintegro-iva-turistas-como-es-el-tramite-agilizar-devoluciones-y-controles-n6274390</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1494,24 +1494,24 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Un relevamiento advirtió que el ingreso disponible de las familias cayó del 53% en 2015 al 36% en febrero. El estudio marca el peso creciente de vivienda, servicios, transporte, educación y salud sobre los presupuestos familiares.</t>
+          <t>El nuevo sistema exige comprobantes electrónicos y validación online. El reembolso se gestionará con control digital en la salida del país.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Daniel Artana afirmó que hay margen para una recuperación salarial, aunque siguen rezagados frente a la inflación</t>
+          <t>Rebajas de aportes, beneficios a empresas y más: las claves del RIFL, el nuevo régimen de la reforma laboral para impulsar el empleo formal</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/daniel-artana-afirmo-que-hay-margen-una-recuperacion-salarial-aunque-siguen-rezagados-frente-la-inflacion-n6273214</t>
+          <t>https://www.ambito.com/economia/rebajas-aportes-beneficios-empresas-y-mas-las-claves-del-rifl-el-nuevo-regimen-la-reforma-laboral-impulsar-el-empleo-formal-n6274404</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1526,24 +1526,24 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Artana señaló que los ingresos formales todavía se ubican por debajo de los niveles previos en términos reales. También analizó el desempeño de la actividad en el primer trimestre y el posible impacto del conflicto en Medio Oriente.</t>
+          <t>El esquema apunta a incorporar trabajadores no registrados, desempleados y monotributistas, con condiciones y límites para evitar abusos.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Dante Sica pronosticó que "la inflación va a ser más alta que la proyectada"</t>
+          <t>Reforma laboral: el Gobierno reglamentó el RIFL, el régimen de incentivo para formalizar empleo</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/dante-sica-pronostico-que-la-inflacion-va-ser-mas-alta-que-la-proyectada-n6273212</t>
+          <t>https://www.ambito.com/economia/reforma-laboral-el-gobierno-reglamento-el-rifl-el-regimen-incentivo-formalizar-empleo-n6274394</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1558,24 +1558,24 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>El exministro resaltó que habrá crecimiento por el impulso de los sectores más competitivos, aunque señaló el desafío de aquellos que "están volcados al mercado interno".</t>
+          <t>La medida fija condiciones para acceder a la reducción de aportes patronales por nuevas contrataciones. El beneficio podrá extenderse hasta 48 meses.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Mayo de locro: cómo ahorrar con esta billetera virtual para las compras patrias</t>
+          <t>El Gobierno le recorta fondos a las provincias y acude a los ATN como principal instrumento</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/mayo-locro-como-ahorrar-esta-billetera-virtual-las-compras-patrias-n6272233</t>
+          <t>https://www.ambito.com/economia/el-gobierno-le-recorta-fondos-las-provincias-y-acude-los-atn-como-principal-instrumento-n6274236</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1590,24 +1590,24 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Una lista con todos los reintegros y descuentos de esta entidad bancaria que pueden hacerte falta para planear el almuerzo de un feriado.</t>
+          <t>En abril los envíos no automáticos cayeron 53% respecto del mismo mes del año pasado. Los Aportes del Tesoro Nacional a nueve provincias concentraron el 30%.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Plazo fijo en 2026: ¿cuánto hay que invertir para generar $250.000 en 30 días?</t>
+          <t>Fuerte suba interanual en la pesca: creció 31,6% en marzo, aunque cayó en la comparación mensual</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/plazo-fijo-2026-cuanto-hay-que-invertir-generar-250000-30-dias-n6272754</t>
+          <t>https://www.ambito.com/economia/fuerte-suba-interanual-la-pesca-crecio-316-marzo-aunque-cayo-la-comparacion-mensual-n6274375</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1622,24 +1622,24 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Con tasas cercanas al 19%, esta herramienta de inversión requiere capitales altos para alcanzar rendimientos significativos en 30 días.</t>
+          <t>El índice del INDEC mostró un salto interanual en el sector pesquero y un sólido primer trimestre, pese a una baja desestacionalizada respecto a febrero.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>A menos de 45 días: los consejos para viajar al Mundial 2026 sin gastar todos tus ahorros en dólares</t>
+          <t>El Gobierno cruzó a Domingo Cavallo por sus críticas: "Si hay resentimiento, tratá que no se note"</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/a-menos-45-dias-los-consejos-viajar-al-mundial-2026-gastar-todos-tus-ahorros-dolares-n6272036</t>
+          <t>https://www.ambito.com/economia/el-gobierno-cruzo-domingo-cavallo-sus-criticas-si-hay-resentimiento-trata-que-no-se-note-n6274367</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1654,24 +1654,24 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Todo lo que tenés que saber para hacer que cada dólar rinda en tu travesía por los Estados Unidos en esta Copa del Mundo.</t>
+          <t>La polémica escaló tras cuestionamientos del exministro al rumbo económico y derivó en una respuesta directa de Luis Caputo y Javier Milei, que defendieron la gestión y apuntaron contra su legado.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Luis Caputo destacó el impacto del acuerdo con la UE en exportaciones e inversiones</t>
+          <t>Acuerdo Mercosur-UE: Argentina concretó la primera exportación de miel al bloque europeo con arancel cero</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/luis-caputo-destaco-el-impacto-del-acuerdo-la-ue-exportaciones-e-inversiones-n6273039</t>
+          <t>https://www.ambito.com/economia/acuerdo-mercosur-ue-argentina-concreto-la-primera-exportacion-miel-al-bloque-europeo-arancel-cero-n6274365</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>El ministro de Economía aseguró que la entrada en vigencia del pacto con el bloque europeo potenciará las ventas externas, impulsará sectores clave y favorecerá el ingreso de capitales.</t>
+          <t>El primer certificado fue emitido para un cargamento de más de 20.000 kilos despachado desde Concordia, Entre Ríos, con destino a Alemania. El canciller Pablo Quirno destacó que la operación se realizó bajo el nuevo sistema de cuotas del pacto comercial.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Cómo comprar en la Feria del Libro 2026 con descuento</t>
+          <t>La baja de tasas no llega a los créditos personales y dificulta la reactivación económica: qué hay detrás</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/como-comprar-la-feria-del-libro-2026-descuento-n6272113</t>
+          <t>https://www.ambito.com/economia/la-baja-tasas-no-llega-los-creditos-personales-y-dificulta-la-reactivacion-economica-que-hay-detras-n6273896</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1718,24 +1718,24 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Cuenta DNI y tarjetas del Banco Provincia ofrecen beneficios para pagar menos en entradas y compras dentro de La Rural.</t>
+          <t>Mientras las tasas de cauciones, Lecaps, plazos fijos y créditos a empresas ya corren por debajo de la inflación esperada, los préstamos a personas físicas todavía muestran retornos que prácticamente la duplican.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Transferencias automáticas a provincias: cayeron por cuarto mes al hilo y en abril la merma fue de hasta 3,3%</t>
+          <t>Provincias bajo presión: ya perdieron $1,3 billones de coparticipación en lo que va de 2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/transferencias-automaticas-provincias-cayeron-cuarto-mes-al-hilo-y-abril-la-merma-fue-33-n6272985</t>
+          <t>https://www.ambito.com/economia/provincias-presion-ya-perdieron-13-billones-coparticipacion-lo-que-va-2026-n6274308</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1750,24 +1750,24 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>En abril, las transferencias ascendieron a $5,5 billones, una suba nominal del 28% pero una caída real de hasta el 3,3% al descontar la inflación.</t>
+          <t>Los recursos tributarios superaron los $68 billones en el primer cuatrimestre, aunque apenas el 32% del total fue coparticipado a las provincias. Medidas a precios constantes, las transferencias automáticas registraron una caída real anual del 5,6% en lo que va del año.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Para un frigorífico tradicional "el precio de la carne llegó a un techo"</t>
+          <t>Cuidado con tus ahorros en dólares: las 5 estafas virtuales más comunes</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/para-un-frigorifico-tradicional-el-precio-la-carne-llego-un-techo-n6272977</t>
+          <t>https://www.ambito.com/economia/cuidado-tus-ahorros-dolares-las-5-estafas-virtuales-mas-comunes-n6274125</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1782,24 +1782,24 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>El aumento en los valores de la carne vacunaes uno de los principales ejes de preocupación de los últimos meses. Esto devino en una marcada caída del consumo.</t>
+          <t>Con las nuevas formas de engaño, los usuarios deben prestar atención a los métodos que pueden vaciar sus cuentas en cuestión de minutos.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>¿Rebote de la actividad económica en marzo? Fuerte tracción de los bienes transables y energía</t>
+          <t>Chau plazo fijo: cuánto gano a 30 días si deposito hoy $500.000</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/rebote-la-actividad-economica-marzo-fuerte-traccion-los-bienes-transables-y-energia-n6272966</t>
+          <t>https://www.ambito.com/economia/chau-plazo-fijo-cuanto-gano-30-dias-si-deposito-hoy-500000-n6274049</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1814,24 +1814,24 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>La actividad económica sigue a "dos velocidades", el sector transable y la energía lideran los avances. La molienda de soja pegó un salto del 32,7%.</t>
+          <t>Esta herramienta sigue siendo una de las opciones más elegidas por los ahorristas para invertir. Cuánto puede rendir, cómo constituir uno y las tasas de interés.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Dólar: Domingo Cavallo redobló críticas al cepo a empresas y alertó que la desinflación puede "empantanarse"</t>
+          <t>La inflación se desaceleró en abril, pero más de la mitad de las familias no logró cubrir la canasta alimentaria</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/dolar-domingo-cavallo-redoblo-criticas-al-cepo-empresas-y-alerto-que-la-desinflacion-puede-empantanarse-n6272872</t>
+          <t>https://www.ambito.com/economia/la-inflacion-se-desacelero-abril-pero-mas-la-mitad-las-familias-no-logro-cubrir-la-canasta-alimentaria-n6274222</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1846,24 +1846,24 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>El exministro cuestionó las restricciones cambiarias y sostuvo que sin una reforma monetaria la baja de la inflación podría frenarse. Planteó que liberar el mercado de divisas es clave para reactivar la economía y atraer inversiones.</t>
+          <t>De acuerdo con un trabajo del IETSE, entre quienes sí pudieron cubrir la canasta básica de alimentos, el 71,4% necesitó asistencia estatal.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Entró en vigencia el acuerdo Mercosur-UE: qué implica para Argentina</t>
+          <t>Consumo estancado: los datos del primer cuatrimestre del IVA confirman la tendencia</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/entro-vigencia-el-acuerdo-mercosur-ue-que-implica-argentina-n6272954</t>
+          <t>https://www.ambito.com/economia/consumo-estancado-los-datos-del-primer-cuatrimestre-del-iva-confirman-la-tendencia-n6274086</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1878,24 +1878,24 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>La UE y el Mercosur representan el 30% del PIB mundial y 700 millones de consumidores. El pacto elimina aranceles en el 90% del comercio entre ambas partes.</t>
+          <t>El componente impositivo del impuesto relacionado con el mercado interno marca que la mejora de la actividad todavía está lejos. Baja 2% entre enero y abril. El componente aduanero cae 23%.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Plazo fijo: cuál es la diferencia de ganancia entre el depósito en home banking y sucursal</t>
+          <t>Ingresos y desigualdad entre provincias: hay argentinos que viven con apenas u$s8 por día</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/plazo-fijo-cual-es-la-diferencia-ganancia-el-deposito-home-banking-y-sucursal-n6272279</t>
+          <t>https://www.ambito.com/economia/ingresos-y-desigualdad-provincias-hay-argentinos-que-viven-apenas-us8-dia-n6274062</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1910,24 +1910,24 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>La diferencia entre constituir esta herramienta en sucursal o de forma electrónica impacta directamente en la ganancia final.</t>
+          <t>Un informe privado expone la fuerte brecha de ingresos entre provincias: mientras en CABA se perciben más de u$s25 diarios, en el norte no se alcanzan los u$s9.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Uno a uno: los aumentos de mayo que golpearán el bolsillo y presionarán a la inflación</t>
+          <t>Plazo fijo: así operan los principales bancos hoy, martes 5 de mayo</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/uno-uno-los-aumentos-mayo-que-golpearan-el-bolsillo-y-presionaran-la-inflacion-n6271686</t>
+          <t>https://www.ambito.com/economia/plazo-fijo-asi-operan-los-principales-bancos-hoy-martes-5-mayo-n6274018</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1942,24 +1942,24 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>A la espera del dato de inflación de abril, el Gobierno topeó el incremento mensual en las boletas de AySA.</t>
+          <t>Cuánto pagan hoy las entidades por depósitos a 30 días y qué variables influyen en los rendimientos en el sistema financiero local.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Supermercados liquidan televisores desde $199.000: cuáles son las mejores ofertas y cómo aprovecharlas</t>
+          <t>FMI: confirmaron que el Gobierno le compró a EEUU u$s819 millones en DEGs para pagar el vencimiento de mayo</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/supermercados-liquidan-televisores-199000-cuales-son-las-mejores-ofertas-y-como-aprovecharlas-n6272309</t>
+          <t>https://www.ambito.com/economia/fmi-se-confirmo-que-el-gobierno-le-compro-eeuu-us819-millones-degs-pagar-el-vencimiento-mayo-n6274013</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1974,24 +1974,24 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Las cadenas buscan incentivar el consumo con cuotas sin interés y promociones bancarias. Televisores de gama media y alta, las promociones más fuertes.</t>
+          <t>La Argentina volvió a recurrir a Estados Unidos para cumplir con un vencimiento de deuda. La operación se concretó mientras el país aguarda la aprobación de fondos frescos por parte del FMI.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Advierten que el programa del Gobierno mutó hacia la inversa del "punto Anker": qué implica</t>
+          <t>Oficializaron los aumentos de gas tras aplicar una bonificación del 25% a usuarios: cómo quedaron los cuadros tarifarios</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/advierten-que-el-programa-del-gobierno-muto-la-inversa-del-punto-anker-que-implica-n6272728</t>
+          <t>https://www.ambito.com/economia/oficializaron-los-aumentos-gas-aplicar-una-bonificacion-del-25-usuarios-como-quedaron-los-cuadros-tarifarios-n6273940</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2006,24 +2006,24 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Se trata de ese momento en el que el Estado deja de demandar la mayor parte del dinero disponible en el mercado y se allana espacio a los privados. Al inicio de la gestión estaba en boca de todos los funcionarios de Economía.</t>
+          <t>La medida del ENARGAS obliga a distribuidoras a reflejar nuevos valores y descuentos en las facturas. Alcanza a usuarios de CABA y el conurbano.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Salarios: uno por uno, cuáles son los aumentos confirmados en mayo para todos los trabajadores</t>
+          <t>Cómo acceder a los descuentos en carnicería y ahorrar hasta $18.000 en mayo 2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/salarios-uno-uno-cuales-son-los-aumentos-confirmados-mayo-todos-los-trabajadores-n6272576</t>
+          <t>https://www.ambito.com/economia/como-acceder-los-descuentos-carniceria-y-ahorrar-18000-mayo-2026-n6273635</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2038,24 +2038,24 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Con una inflación acumulada superior al 9% en el primer trimestre, los acuerdos salariales muestran una marcada heterogeneidad, pero con un denominador común: la mayoría de los aumentos corre por detrás o apenas empata la suba de precios.</t>
+          <t>Conocé cuál es la billetera virtual que te permite reducir tus gastos diarios y cómo organizar tus compras de la semana para maximizar el ahorro, aprovechando todos los beneficios.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Más que un ahorro en dólares: la guía para hacer voluntariados en Estados Unidos y viajar casi gratis</t>
+          <t>Superávit fiscal: crecen las dudas sobre su sostenibilidad y lo ven "real en lo contable, pero artificial en lo económico"</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/mas-que-un-ahorro-dolares-la-guia-hacer-voluntariados-estados-unidos-y-viajar-casi-gratis-n6271527</t>
+          <t>https://www.ambito.com/economia/superavit-fiscal-crecen-las-dudas-su-sostenibilidad-y-lo-ven-real-lo-contable-pero-artificial-lo-economico-n6273872</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2070,24 +2070,24 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Esta alternativa distinta te permite explorar el país por menos dinero y vivir una experiencia que te va a cambiar para siempre.</t>
+          <t xml:space="preserve">El superávit fiscal se apoya en los recortes: el ministro Luis Caputo ordenó que todos los ministerios recorten el 2% de sus gastos corrientes y el 20% de sus gastos de capital, a la par de que la recaudación cae en términos reales. "El ajuste que se muerde la cola", afirman desde una consultora de </t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>El ladrillo como inversión líquida: lanzan el primer REIT de la Argentina, ¿qué es y cómo genera rendimientos?</t>
+          <t>Plazo fijo: cuánto se gana al invertir $400.000 a 30 días</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/el-ladrillo-como-inversion-liquida-lanzan-el-primer-reit-la-argentina-que-es-y-como-genera-rendimientos-n6272331</t>
+          <t>https://www.ambito.com/economia/plazo-fijo-cuanto-se-gana-al-invertir-400000-30-dias-n6273757</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2102,24 +2102,24 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>El nuevo instrumento ofrece fraccionamiento, liquidez y retornos atractivos, junto con una operatoria de entrada y salida simple, tanto para inversores retail como corporativos.</t>
+          <t>Las tasas actuales se mantienen en niveles bajos en mayo y condicionan el rendimiento real de las inversiones en pesos.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>El Gobierno anunció aumentos para empleadas domésticas y una nueva revisión en julio</t>
+          <t>El secreto mejor guardado para evitar compras impulsivas y cuidar tu dólares: la regla de las 72 horas</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/el-gobierno-anuncio-aumentos-empleadas-domesticas-y-una-nueva-revision-julio-n6272756</t>
+          <t>https://www.ambito.com/economia/el-secreto-mejor-guardado-evitar-compras-impulsivas-y-cuidar-tu-dolares-la-regla-las-72-horas-n6273746</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>El acuerdo establece subas acumulativas de 1,8% en abril, 1,6% en mayo, 1,5% en junio y 1,4% en julio. Además, se incorporará a los básicos la suma no remunerativa de marzo y se actualizará el adicional por zona desfavorable.</t>
+          <t>Este método es muy simple y propone cambiar la relación con la manera de consumir en tiempos de incertidumbre econpomica.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Un estudio de la UBA advierte que la morosidad de las familias ya supera los niveles de la pandemia</t>
+          <t>Kevin Warsh llega a una Fed más reacia a bajar las tasas y con Jerome Powell como gran opositor interno</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/un-estudio-la-uba-advierte-que-la-morosidad-las-familias-ya-supera-los-niveles-la-pandemia-n6272738</t>
+          <t>https://www.ambito.com/economia/kevin-warsh-llega-una-fed-mas-reacia-bajar-las-tasas-y-jerome-powell-como-gran-opositor-interno-n6273675</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2166,24 +2166,24 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>El informe del Centro RA de la Facultad de Ciencias Económicas señaló que el crédito al consumo creció 57% desde el inicio de la gestión de Javier Milei. También detectó un fuerte avance del uso de tarjetas para sostener compras básicas.</t>
+          <t>El cadidato nominado por Donald Trump asumirá su cargo como titular de la Fed el próximo 15 de mayo. Sin embargo, no la tendrá fácil a la hora de cumplir su pretensión de bajar las tasas, ya que deberá convencer a una Junta Directiva cada vez más convencida de lo contrario.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Cuenta DNI oficializó los beneficios de mayo 2026 y el descuento en carnicerías sigue de lunes a viernes</t>
+          <t>Pirámide social: el 6% más acaudalado concentra el 34% de la riqueza y redefine el consumo en la Argentina</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/cuenta-dni-oficializo-los-beneficios-mayo-2026-y-el-descuento-carnicerias-sigue-lunes-viernes-n6272721</t>
+          <t>https://www.ambito.com/economia/piramide-social-el-6-mas-rico-concentra-el-34-la-riqueza-y-redefine-el-consumo-la-argentina-n6273639</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2198,24 +2198,24 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>La billetera digital de Banco Provincia continua con una amplia variedad de promociones en distintos rubros.</t>
+          <t>Un análisis revela cómo vive y gasta el segmento de mayores ingresos. Viajes, bienestar y experiencias premium conviven con una tendencia general a optimizar el gasto.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Impuesto a las Ganancias: los trabajadores que pagan el tributo recibirán una devolución en mayo</t>
+          <t>Plazo fijo en mayo 2026: así operan los principales bancos hoy, lunes 4</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/impuesto-las-ganancias-los-trabajadores-que-pagan-el-tributo-recibiran-una-devolucion-mayo-n6272562</t>
+          <t>https://www.ambito.com/economia/plazo-fijo-mayo-2026-asi-operan-los-principales-bancos-hoy-lunes-4-n6273585</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2230,24 +2230,24 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>La mayoría de las empresas retiene de más el impuesto a las Ganancias en los salarios de sus empleados en la primera mitad del año fiscal. Luego se ajustan las escalas en el segundo semestre. En abril del año siguiente, se reintegran los saldos a favor.</t>
+          <t>Tasas actualizadas banco por banco y claves para entender cuánto rinde hoy un depósito a 30 días en un contexto económico cambiante.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>La inversión real bajó 0,8% anual en marzo, según Orlando Ferreres</t>
+          <t>Cuáles son los trabajos más afectados y los más beneficiados por la Inteligencia Artificial</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/la-inversion-real-08-anual-marzo-segun-orlando-ferreres-n6272610</t>
+          <t>https://www.ambito.com/economia/cuales-son-los-trabajos-mas-afectados-y-los-mas-beneficiados-la-inteligencia-artificial-n6273580</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2262,24 +2262,24 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>La baja en la inversión muestra un contraste con la caída de 11,1% de febrero y la merma de enero, pero advierten que el "repunte es mínimo".</t>
+          <t>Un estudio reveló qué trabajos enfrentan mayor riesgo de automatización y en contraste, aquellos que crecerán gracias al uso de la inteligencia artificial.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>La inflación esperada por la población sigue alta: se ubicó en el 3,9% para abril</t>
+          <t>Salarios de empleadas domésticas: acuerdan una suba del 6,5 % y la actualización de escalas hasta julio</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/la-inflacion-esperada-la-poblacion-sigue-alta-se-ubico-el-39-abril-n6272584</t>
+          <t>https://www.ambito.com/economia/el-gobierno-anuncio-aumentos-empleadas-domesticas-y-una-nueva-revision-julio-n6272756</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2294,24 +2294,24 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Para los próximos 30 días, la inflación esperada en abril se ubicó en 3,93% en promedio y 3% de mediana.</t>
+          <t>El acuerdo establece subas acumulativas de 1,8% en abril, 1,6% en mayo, 1,5% en junio y 1,4% en julio. Además, se incorporará a los básicos la suma no remunerativa de marzo y se actualizará el adicional por zona desfavorable.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Últimos días de abril para invertir en plazo fijo: cuánto gano a 30 días si deposito $150.000 hoy</t>
+          <t>El gobierno de Javier Milei reglamentó un capítulo clave de la reforma laboral: cuál es</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/ultimos-dias-abril-invertir-plazo-fijo-cuanto-gano-30-dias-si-deposito-150000-hoy-n6271757</t>
+          <t>https://www.ambito.com/economia/el-gobierno-javier-milei-reglamento-un-capitulo-clave-la-reforma-laboral-cual-es-n6273503</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2326,24 +2326,24 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Conocé los valores porcentuales de acuerdo a cada entidad bancaria y analizá el método más conveniente para poder realizar la operatoria.</t>
+          <t>A través del Decreto 315/2026, se puso en marcha el Régimen de Incentivo a la Formalización Laboral. Las claves de la norma en vigencia.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Chau plazo fijo: las tasas siguen a la baja y así operan los principales bancos hoy, jueves 30 de abril</t>
+          <t>Recaudación: el IVA y el Impuesto a las Ganancias siguen en caída, aunque se desacelera el ritmo de la baja</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/chau-plazo-fijo-las-tasas-siguen-la-baja-y-asi-operan-los-principales-bancos-hoy-jueves-30-abril-n6272537</t>
+          <t>https://www.ambito.com/economia/recaudacion-el-iva-y-el-impuesto-las-ganancias-siguen-caida-aunque-se-desacelera-el-ritmo-la-baja-n6273516</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2358,24 +2358,24 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Las entidades mantienen rendimientos similares y crece la cautela entre ahorristas frente a inflación y expectativas cambiarias.</t>
+          <t>Se trata de estimaciones de consultores. En el IVA aduanero se comenzaron a igualar condiciones por la suspensión de certificados de exclusión que regían anteriormente.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Así funciona el nuevo sistema de ARBA para pymes que alivia la carga financiera de Ingresos Brutos</t>
+          <t>Dólares del agro: la liquidación cayó 1,2% interanual en abril, en el comienzo de la cosecha gruesa</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/asi-funciona-el-nuevo-sistema-arba-pymes-que-alivia-la-carga-financiera-ingresos-brutos-n6272519</t>
+          <t>https://www.ambito.com/economia/dolares-del-agro-la-liquidacion-cayo-11-interanual-el-comienzo-la-cosecha-gruesa-n6273525</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2390,24 +2390,24 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Más de 12.000 empresas ya operan bajo el esquema "Riesgo 0, SAF 0" que ajusta automáticamente las retenciones para evitar saldos a favor acumulados.</t>
+          <t>CIARA-CEC, la cámara que agrupa a las empresas agroexportadoras, informó los números de abril. En el primer cuatrimestre, ingresaron u$s7.667 millones, 11% menos que en 2025.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Comercio exterior: el Puerto de Mar del Plata lanza incentivos para exportar y busca frenar la salida de cargas a otros puertos</t>
+          <t>Aumentan los boletos de colectivos en la Provincia de Buenos Aires: cuánto costará viajar en mayo</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/comercio-exterior-el-puerto-mar-del-plata-lanza-incentivos-exportar-y-busca-frenar-la-salida-cargas-otros-puertos-n6272447</t>
+          <t>https://www.ambito.com/economia/aumentan-los-boletos-colectivos-la-provincia-buenos-aires-cuanto-costara-viajar-mayo-n6273514</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2422,24 +2422,24 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>El Consorcio Portuario Regional aprobó beneficios de hasta el 100% en cánones y aplicará recargos para desalentar desvíos logísticos.</t>
+          <t>Las tarifas del transporte público bonaerense registraron un incremento del 11,6% desde mayo. El valor mínimo del pasaje supera los $1.050 y varía según el trayecto.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Inflación de abril: proyectan que marcará su primera desaceleración en 10 meses, ¿más cerca del 2% o 3%?</t>
+          <t>La economía enfrenta fuertes contrastes en el consumo</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/inflacion-abril-proyectan-que-marcara-su-primera-desaceleracion-10-meses-mas-cerca-del-2-o-3-n6272360</t>
+          <t>https://www.ambito.com/economia/la-enfrenta-fuertes-contrastes-el-consumo-n6273469</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2454,24 +2454,24 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>El IPC se dirige a interrumpir una secuencia de diez meses consecutivos sin caídas, luego de alcanzar el 3,4% en marzo y se prevé que perfore el nivel clave del 3%. Pese al congelamiento de las naftas, el combustible tiene un arrastre mayor al 10%.</t>
+          <t>La caída del poder adquisitivo de los salarios. El peso de las tarifas: en marzo las familias último destinan más del 29% de los ingresos a gastos ineludibles. La carga de los intereses de las deudas con relación a los salarios (registrados) subió de 9% en 2024 a 25% en la actualidad. Caen ventas de</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Estufas y caloventores: conocé cómo conseguirlos desde $35.999 y con hasta 25% de descuento</t>
+          <t>La Bolsa quiebra récords empujada por la efervescencia de los balances</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/estufas-y-caloventores-conoce-como-conseguirlos-35999-y-25-descuento-n6271818</t>
+          <t>https://www.ambito.com/economia/la-bolsa-quiebra-records-empujada-la-efervescencia-los-balances-n6273430</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2486,24 +2486,24 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>En busca de anticiparse al invierno, Carrefour y Jumbo lanzan promociones en calefacción con descuentos y cuotas sin interés.</t>
+          <t>El impulso de Wall Street desafía tensiones geopolíticas, suba de tasas y crisis energética. La clave pasa por los resultados corporativos, que sostienen el optimismo y empujan al mercado a nuevos máximos.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Referentes de la economía del conocimiento destacaron el potencial de Argentina en IA: "Siempre se diferencia por calidad"</t>
+          <t>Reservas: el BCRA compró dólares, pero el alza se explicó casi en su totalidad por el oro</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/referentes-la-del-conocimiento-destacaron-el-potencial-argentina-ia-siempre-se-diferencia-calidad-n6272370</t>
+          <t>https://www.ambito.com/economia/reservas-el-bcra-compro-dolares-pero-el-alza-se-explico-casi-su-totalidad-el-oro-n6273383</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -2518,24 +2518,24 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>En el marco de la Expo EFI, representantes del sector destacaron las ventajas comparativas que tiene el país y expusieron las habilidades que solicitará el mercado laboral: "No vamos a necesitar meros contadores, sino contadores tecnológicos".</t>
+          <t>Un informe privado reveló que el 99% del incremento de reservas en el primer trimestre respondió a la revalorización de activos. El saldo por intervenciones cambiarias fue prácticamente nulo.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Cómo obtener el reintegro en transporte con esta billetera virtual</t>
+          <t>Dólares fuera del sistema: Bloomberg advierte que pese a los incentivos, persiste la desconfianza</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/como-obtener-el-reintegro-transporte-esta-billetera-virtual-n6271706</t>
+          <t>https://www.ambito.com/economia/dolares-fuera-del-sistema-bloomberg-advierte-que-pese-los-incentivos-persiste-la-desconfianza-n6273362</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -2550,24 +2550,24 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Conocé todos los descuentos que ofrece la aplicación del Banco Ciudad hasta mitad de año, para pagos con QR o NFC, en comercios adheridos.</t>
+          <t>Aunque el Gobierno busca captar los dólares fuera del circuito formal, la mayoría de los argentinos sigue optando por el efectivo. El recuerdo del corralito y la falta de confianza continúan condicionando el comportamiento de los ahorristas.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Claudio Zuchovicki: "Por primera vez en mis 40 años de mercado, la Argentina no discute el rumbo económico"</t>
+          <t>Feriado del Día del Trabajador: viajaron 1,1 millones de turistas y gastaron $235.000 millones, pero con caída real del consumo</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/claudio-zuchovicki-por-primera-vez-mis-40-anos-mercado-la-argentina-no-discute-el-rumbo-economico-n6272247</t>
+          <t>https://www.ambito.com/economia/feriado-del-dia-del-trabajador-viajaron-11-millones-turistas-y-gastaron-235000-millones-pero-caida-real-del-consumo-n6273337</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2582,24 +2582,24 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>El presidente de BYMA destacó que gran parte del los agentes económicos argentinos comparte el rumbo del Gobierno, y que también apoya la velocidad de los cambios.</t>
+          <t>Durante el fin de semana largo viajaron más de un millón de personas y se generaron $235.000 millones, pero el consumo fue más moderado, con escapadas breves y fuerte foco en gastos básicos.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Guillermo Pérez: "El impuesto a las Ganancias Simplificado es una especie de blanqueo encubierto"</t>
+          <t>Petróleo y dólares: el efecto de la suba de producción de la OPEP+ en la economía de la Argentina</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/guillermo-perez-el-impuesto-las-ganancias-simplificado-es-una-especie-blanqueo-encubierto-n6272293</t>
+          <t>https://www.ambito.com/economia/petroleo-y-dolares-el-efecto-la-suba-produccion-la-opep-la-la-argentina-n6273313</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -2614,24 +2614,24 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>El CEO del Grupo GNP destacó que la ley de Inocencia Fiscal ofrece ventajas a quienes tienen bienes sin declarar. El plazo para adherir por el período 2025 vence en junio.</t>
+          <t>La decisión llega en un contexto de alta volatilidad global y puede incidir directamente en precios internos y dinámica cambiaria.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Paritarias de bancarios: cuánto cobrarán en mayo de 2026 tras el último acuerdo</t>
+          <t>Leve rebote de la actividad, inflación que no cede y un dólar bajo presión marcan el pulso: qué se espera para la economía en mayo</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/paritarias-bancarios-cuanto-cobraran-mayo-2026-el-ultimo-acuerdo-n6272171</t>
+          <t>https://www.ambito.com/economia/leve-rebote-la-actividad-inflacion-alta-y-dolar-presion-marcan-el-pulso-que-se-espera-la-mayo-n6273310</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2646,24 +2646,24 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Los salarios del sector bancario se incrementarán nuevamente, según afirma la Asociación Bancaria. Se trata de un aumento que acompaña la inflación.</t>
+          <t>Marzo mostró señales de recuperación impulsadas por sectores transables, pero el repunte aún es frágil frente a una inflación que sigue elevada y expectativas cambiarias que anticipan mayor tensión en mayo.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Plazo fijo en 2026: cuánto hay que invertir para generar $50.000 en 30 días</t>
+          <t>El peso argentino vive su mejor cuatrimestre en décadas, pero la fiesta tiene fecha de vencimiento</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/plazo-fijo-2026-cuanto-hay-que-invertir-generar-50000-30-dias-n6271803</t>
+          <t>https://www.ambito.com/economia/el-peso-argentino-vive-su-mejor-cuatrimestre-decadas-pero-la-fiesta-tiene-fecha-vencimiento-n6273279</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2678,24 +2678,24 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Actualmente, con tasas cercanas al 18%-19%, el plazo fijo sigue siendo una opción estable para generar ingresos mensuales.</t>
+          <t>Un superávit extraordinario de divisas —cosecha récord, petróleo patagónico y deuda corporativa— sostuvo una apreciación nominal del 4,9% mientras la inflación acumulaba 9,4% en el primer trimestre. El Banco Central compró USD 7.000 millones. Los inversores celebran el carry; los exportadores indust</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>¿Repunta el plazo fijo? Así operan los principales bancos hoy, miércoles 29 de abril</t>
+          <t>Al 90% de los hogares le quedan menos de $60.000 diarios tras cubrir gastos fijos, según informe</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/repunta-el-plazo-fijo-asi-operan-los-principales-bancos-hoy-miercoles-29-abril-n6272059</t>
+          <t>https://www.ambito.com/economia/al-90-los-hogares-le-quedan-menos-60000-diarios-cubrir-gastos-fijos-segun-informe-n6273252</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -2710,24 +2710,24 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Las entidades muestran rendimientos distintos y los ahorristas vuelven a mirar esta opción para resguardar ingresos mensuales.</t>
+          <t>Un relevamiento advirtió que el ingreso disponible de las familias cayó del 53% en 2015 al 36% en febrero. El estudio marca el peso creciente de vivienda, servicios, transporte, educación y salud sobre los presupuestos familiares.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Comercio exterior: habilitan nueva herramienta para importadores que permitirá conocer de antemano el origen y tratamiento de mercaderías</t>
+          <t>Daniel Artana afirmó que hay margen para una recuperación salarial, aunque siguen rezagados frente a la inflación</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/comercio-exterior-habilitan-nueva-herramienta-importadores-que-permitira-conocer-antemano-el-origen-y-tratamiento-mercaderias-n6271991</t>
+          <t>https://www.ambito.com/economia/daniel-artana-afirmo-que-hay-margen-una-recuperacion-salarial-aunque-siguen-rezagados-frente-la-inflacion-n6273214</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2742,24 +2742,24 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>La medida de la Secretaría de Industria, Comercio y de la Pequeña y Mediana Empresa fija plazos y procedimientos para consultas vinculantes antes del ingreso de mercaderías.</t>
+          <t>Artana señaló que los ingresos formales todavía se ubican por debajo de los niveles previos en términos reales. También analizó el desempeño de la actividad en el primer trimestre y el posible impacto del conflicto en Medio Oriente.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Salarios de empleadas domésticas: el Gobierno convocó a reunión para discutir nuevos aumentos a partir de mayo</t>
+          <t>Dante Sica pronosticó que "la inflación va a ser más alta que la proyectada"</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/salarios-empleadas-domesticas-el-gobierno-convoco-reunion-discutir-nuevos-aumentos-n6271988</t>
+          <t>https://www.ambito.com/economia/dante-sica-pronostico-que-la-inflacion-va-ser-mas-alta-que-la-proyectada-n6273212</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -2774,24 +2774,24 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>La reunión de la Comisión Nacional de Trabajo en Casas Particulares será virtual y buscará actualizar remuneraciones en un contexto sin bono extraordinario.</t>
+          <t>El exministro resaltó que habrá crecimiento por el impulso de los sectores más competitivos, aunque señaló el desafío de aquellos que "están volcados al mercado interno".</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Empresarios de sectores clave respaldaron el rumbo económico de Milei, pero alertaron que el proceso "requerirá de dolor"</t>
+          <t>Plazo fijo en 2026: ¿cuánto hay que invertir para generar $250.000 en 30 días?</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/empresarios-sectores-clave-respaldaron-el-rumbo-economico-milei-pero-alertaron-que-el-proceso-requerira-dolor-n6271865</t>
+          <t>https://www.ambito.com/economia/plazo-fijo-2026-cuanto-hay-que-invertir-generar-250000-30-dias-n6272754</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>En el marco de la Expo EFI, representantes relevantes del empresariado destacaron los avances del Gobierno en el orden macro o en medidas como el RIGI. Sin embargo, marcaron algunas cuestiones en el "debe".</t>
+          <t>Con tasas cercanas al 19%, esta herramienta de inversión requiere capitales altos para alcanzar rendimientos significativos en 30 días.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Paritarias de Comercio: cuánto cobrarán en mayo de 2026 tras la homologación del acuerdo</t>
+          <t>Plazo fijo en 2026: ¿cuánto rinde invertir $500.000?</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/paritarias-comercio-cuanto-cobraran-mayo-2026-la-homologacion-del-acuerdo-n6271948</t>
+          <t>https://www.ambito.com/economia/plazo-fijo-2026-cuanto-rinde-invertir-500000-n6272319</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -2838,24 +2838,24 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>El Ministerio de Capital Humano convalidó sin modificaciones el entendimiento firmado por FAECyS y las cámaras empresarias. En el quinto mes del año se activa el segundo tramo de la suba trimestral, junto con las sumas extraordinarias previstas para el sector.</t>
+          <t>Con tasas por debajo del 20% anual, esta herramienta sigue generando rendimientos mensuales acotados, pero previsibles.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Paritarias de la construcción: cuánto cobrarán los trabajadores en mayo 2026</t>
+          <t>Luis Caputo destacó el impacto del acuerdo con la UE en exportaciones e inversiones</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/paritarias-la-construccion-cuanto-cobraran-los-trabajadores-mayo-2026-n6271953</t>
+          <t>https://www.ambito.com/economia/luis-caputo-destaco-el-impacto-del-acuerdo-la-ue-exportaciones-e-inversiones-n6273039</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -2870,24 +2870,24 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>El acuerdo entre la UOCRA y las cámaras empresarias fijó nuevos valores para abril, que se perciben en mayo. Incluye subas acumulativas y sumas no remunerativas.</t>
+          <t>El ministro de Economía aseguró que la entrada en vigencia del pacto con el bloque europeo potenciará las ventas externas, impulsará sectores clave y favorecerá el ingreso de capitales.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Federico Sturzenegger impulsa una ley para que existan empresas gestionadas 100% por inteligencia artificial</t>
+          <t>Cómo comprar en la Feria del Libro 2026 con descuento</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/federico-sturzenegger-impulsa-una-ley-que-existan-empresas-gestionadas-100-inteligenciaaartificial-n6271805</t>
+          <t>https://www.ambito.com/economia/como-comprar-la-feria-del-libro-2026-descuento-n6272113</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -2902,24 +2902,24 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Durante su discurso, el ministro de Desregulación y Transformación del Estado adelantó seis nuevas leyes que planea enviar al Congreso Nacional.</t>
+          <t>Cuenta DNI y tarjetas del Banco Provincia ofrecen beneficios para pagar menos en entradas y compras dentro de La Rural.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>El mercado empieza a preguntarse si las elecciones de 2027 volverán a generar inestabilidad económica</t>
+          <t>Transferencias automáticas a provincias: cayeron por cuarto mes al hilo y en abril la merma fue de hasta 3,3%</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/el-mercado-empieza-preguntarse-si-las-elecciones-2027-volveran-generar-inestabilidad-economica-n6271734</t>
+          <t>https://www.ambito.com/economia/transferencias-automaticas-provincias-cayeron-cuarto-mes-al-hilo-y-abril-la-merma-fue-33-n6272985</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -2934,24 +2934,24 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Si bien prima una mirada optimista para los próximos meses respecto de la actividad, luego de los recientes malos datos, persisten dudas sobre el clima social, la inflación y los armados políticos de cara al año que viene.</t>
+          <t>En abril, las transferencias ascendieron a $5,5 billones, una suba nominal del 28% pero una caída real de hasta el 3,3% al descontar la inflación.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Últimos días de abril 2026 con descuentos de Cuenta DNI</t>
+          <t>Para un frigorífico tradicional "el precio de la carne llegó a un techo"</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/ultimos-dias-abril-2026-descuentos-cuenta-dni-n6271234</t>
+          <t>https://www.ambito.com/economia/para-un-frigorifico-tradicional-el-precio-la-carne-llego-un-techo-n6272977</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -2966,24 +2966,24 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Todo lo que tenés que saber para aprevechar al máximo todas las ofertas y reintegros que brinda la billetera virtual del Banco Provincia durante esta última semana del mes.</t>
+          <t>El aumento en los valores de la carne vacunaes uno de los principales ejes de preocupación de los últimos meses. Esto devino en una marcada caída del consumo.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>El empleo autopartista cayó 7,7% y crece la preocupación por 2026</t>
+          <t>¿Rebote de la actividad económica en marzo? Fuerte tracción de los bienes transables y energía</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/el-empleo-autopartista-cayo-77-y-crece-la-preocupacion-2026-n6271712</t>
+          <t>https://www.ambito.com/economia/rebote-la-actividad-economica-marzo-fuerte-traccion-los-bienes-transables-y-energia-n6272966</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>El sector perdió más de 4.000 puestos en un año y enfrenta un escenario desafiante marcado por menor producción local y mayor ingreso de importaciones.</t>
+          <t>La actividad económica sigue a "dos velocidades", el sector transable y la energía lideran los avances. La molienda de soja pegó un salto del 32,7%.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Chau plazo fijo: todo lo que hay que invertir para ganar más de $10.000 a 30 días</t>
+          <t>Dólar: Domingo Cavallo redobló críticas al cepo a empresas y alertó que la desinflación puede "empantanarse"</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/chau-plazo-fijo-todo-lo-que-hay-que-invertir-ganar-mas-10000-30-dias-n6271629</t>
+          <t>https://www.ambito.com/economia/dolar-domingo-cavallo-redoblo-criticas-al-cepo-empresas-y-alerto-que-la-desinflacion-puede-empantanarse-n6272872</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -3030,24 +3030,24 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Esta inversión vuelve a posicionarse como una de las alternativas más elegidas por los argentinos que buscan rendimientos previsibles y sin riesgos.</t>
+          <t>El exministro cuestionó las restricciones cambiarias y sostuvo que sin una reforma monetaria la baja de la inflación podría frenarse. Planteó que liberar el mercado de divisas es clave para reactivar la economía y atraer inversiones.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Plazo fijo: así operan los principales bancos hoy, martes 28 de abril</t>
+          <t>Entró en vigencia el acuerdo Mercosur-UE: qué implica para Argentina</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/plazo-fijo-asi-operan-los-principales-bancos-hoy-martes-28-abril-n6271609</t>
+          <t>https://www.ambito.com/economia/entro-vigencia-el-acuerdo-mercosur-ue-que-implica-argentina-n6272954</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3062,24 +3062,24 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Las entidades ajustan rendimientos y el ahorrista vuelve a mirar cuánto paga cada depósito a 30 días.</t>
+          <t>La UE y el Mercosur representan el 30% del PIB mundial y 700 millones de consumidores. El pacto elimina aranceles en el 90% del comercio entre ambas partes.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Crece la preocupación en Europa: consumidores disparan sus expectativas de inflación antes de la reunión del BCE</t>
+          <t>Plazo fijo: cuál es la diferencia de ganancia entre el depósito en home banking y sucursal</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/crece-la-preocupacion-europa-consumidores-disparan-sus-expectativas-inflacion-antes-la-reunion-del-bce-n6271548</t>
+          <t>https://www.ambito.com/economia/plazo-fijo-cual-es-la-diferencia-ganancia-el-deposito-home-banking-y-sucursal-n6272279</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -3094,24 +3094,24 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Una encuesta del Banco Central Europeo mostró un fuerte salto en las proyecciones de inflación para el próximo año y un mayor pesimismo sobre la economía. El dato refuerza la presión sobre la autoridad monetaria en medio del shock energético por la guerra en Ucrania.</t>
+          <t>La diferencia entre constituir esta herramienta en sucursal o de forma electrónica impacta directamente en la ganancia final.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Privatización del Belgrano Cargas: oficializan esquema para licitar vías, material rodante y uso de fondos</t>
+          <t>Uno a uno: los aumentos de mayo que golpearán el bolsillo y presionarán a la inflación</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/privatizacion-del-belgrano-cargas-oficializan-esquema-licitar-vias-material-rodante-y-uso-fondos-n6271528</t>
+          <t>https://www.ambito.com/economia/uno-uno-los-aumentos-mayo-que-golpearan-el-bolsillo-y-presionaran-la-inflacion-n6271686</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -3126,24 +3126,24 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>A través de un decreto, el Ministerio De Economía dispuso que lo recaudado por la venta de material rodante se canalice a un fideicomiso para financiar infraestructura en las vías concesionadas.</t>
+          <t>A la espera del dato de inflación de abril, el Gobierno topeó el incremento mensual en las boletas de AySA.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Avanza la privatización de AySA: el Gobierno aprobó el nuevo contrato de concesión</t>
+          <t>Supermercados liquidan televisores desde $199.000: cuáles son las mejores ofertas y cómo aprovecharlas</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/avanza-la-privatizacion-aysa-el-gobierno-aprobo-el-nuevo-contrato-concesion-n6271530</t>
+          <t>https://www.ambito.com/economia/supermercados-liquidan-televisores-199000-cuales-son-las-mejores-ofertas-y-como-aprovecharlas-n6272309</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -3158,24 +3158,24 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>La medida del Ministerio de Economía formaliza el contrato que regirá el servicio de agua y cloacas y fija las bases para la venta de la empresa con participación privada.</t>
+          <t>Las cadenas buscan incentivar el consumo con cuotas sin interés y promociones bancarias. Televisores de gama media y alta, las promociones más fuertes.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Reservas: el déficit de servicios cayó 35% interanual en marzo</t>
+          <t>Advierten que el programa del Gobierno mutó hacia la inversa del "punto Anker": qué implica</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/reservas-el-deficit-servicios-cayo-35-interanual-marzo-n6271484</t>
+          <t>https://www.ambito.com/economia/advierten-que-el-programa-del-gobierno-muto-la-inversa-del-punto-anker-que-implica-n6272728</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -3190,24 +3190,24 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Turismo y compras al exterior sigue gravitando. Fue un mes de bajo pago de intereses pero empezaron a jugar en contra el giro de dividendos al exterior.</t>
+          <t>Se trata de ese momento en el que el Estado deja de demandar la mayor parte del dinero disponible en el mercado y se allana espacio a los privados. Al inicio de la gestión estaba en boca de todos los funcionarios de Economía.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Empleo: el cuentapropismo ya se ubica cerca del nivel de la pandemia y se agrava la precarización</t>
+          <t>Lo que se dice en las mesas: "Toto" Caputo negocia repo, mientras el riesgo país sigue jaqueado por los fantasmas de siempre</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/empleo-el-cuentapropismo-ya-se-ubica-cerca-del-nivel-la-pandemia-y-se-agrava-la-precarizacion-n6271403</t>
+          <t>https://www.ambito.com/economia/lo-que-se-dice-las-mesas-luis-caputo-sigue-negociando-repo-la-espera-comprar-mas-reservas-n6272859</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -3222,24 +3222,24 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>El mercado laboral ajusta por calidad y cantidad: si bien el cuentapropismo crece, no llega a compensar la pérdida de empleo privado. Además, la precarización se profundiza en los tejidos urbanos donde el mercado es más débil.</t>
+          <t>Un riesgo país jaqueado por los fantasmas de siempre no cede. El “Toto” sigue negociando repo a la espera de comprar más reservas. Gestores reajustan carteras pero el apetito por el riesgo no aparece.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>El Gobierno homologó la paritaria de Comercio sin cambios y ratificó el aumento del 5%</t>
+          <t>Salarios: uno por uno, cuáles son los aumentos confirmados en mayo para todos los trabajadores</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/el-gobierno-homologo-la-paritaria-comercio-cambios-y-ratifico-el-aumento-del-5-n6271473</t>
+          <t>https://www.ambito.com/economia/salarios-uno-uno-cuales-son-los-aumentos-confirmados-mayo-todos-los-trabajadores-n6272576</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -3254,24 +3254,24 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>El Ministerio de Capital Humano convalidó el acuerdo firmado entre el gremio y las cámaras empresarias. Se prevé un aumento en tres tramos, un bono de $120.000 y sumas no remunerativas.</t>
+          <t>Con una inflación acumulada superior al 9% en el primer trimestre, los acuerdos salariales muestran una marcada heterogeneidad, pero con un denominador común: la mayoría de los aumentos corre por detrás o apenas empata la suba de precios.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Países del G7 definen tasas de interés ante el shock inflacionario por la guerra</t>
+          <t>Más que un ahorro en dólares: la guía para hacer voluntariados en Estados Unidos y viajar casi gratis</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/paises-del-g7-definen-tasas-interes-el-shock-inflacionario-la-guerra-n6271474</t>
+          <t>https://www.ambito.com/economia/mas-que-un-ahorro-dolares-la-guia-hacer-voluntariados-estados-unidos-y-viajar-casi-gratis-n6271527</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -3286,24 +3286,24 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Los principales bancos centrales del mundo, en conjunto con Brasil, enfrentan una semana clave de decisiones sobre tasas de interés en un contexto cada vez más desafiante. El riesgo de un escenario de estanflación vuelve al centro de la escena y condiciona la estrategia de política monetaria.</t>
+          <t>Esta alternativa distinta te permite explorar el país por menos dinero y vivir una experiencia que te va a cambiar para siempre.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>El precio de exportación de la carne alcanzó en el primer trimestre un récord histórico</t>
+          <t>El ladrillo como inversión líquida: lanzan el primer REIT de la Argentina, ¿qué es y cómo genera rendimientos?</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/el-precio-exportacion-la-carne-alcanzo-el-primer-trimestre-un-record-historico-n6271397</t>
+          <t>https://www.ambito.com/economia/el-ladrillo-como-inversion-liquida-lanzan-el-primer-reit-la-argentina-que-es-y-como-genera-rendimientos-n6272331</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -3318,24 +3318,24 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Pese a la suba en los precios de las exportaciones durante el primer trimestre, los términos de intercambio no mejoraron ya que en las importaciones se verificó un alza similar. La mejora del superávit comercial se dio por el efecto cantidades.</t>
+          <t>El nuevo instrumento ofrece fraccionamiento, liquidez y retornos atractivos, junto con una operatoria de entrada y salida simple, tanto para inversores retail como corporativos.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Cerca de la mitad de las pymes prevé reducir personal en los próximos meses</t>
+          <t>Un estudio de la UBA advierte que la morosidad de las familias ya supera los niveles de la pandemia</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/cerca-la-mitad-las-pymes-preve-reducir-personal-los-proximos-meses-n6271467</t>
+          <t>https://www.ambito.com/economia/un-estudio-la-uba-advierte-que-la-morosidad-las-familias-ya-supera-los-niveles-la-pandemia-n6272738</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -3350,24 +3350,24 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Las pymes que “probablemente” reducirán su plantilla (31%) con aquellas que ya lo tienen decidido (18,5%) alcanzan el 50%, de acuerdo al informe de la IAE. Aumenta el pesimismo respecto al futuro.</t>
+          <t>El informe del Centro RA de la Facultad de Ciencias Económicas señaló que el crédito al consumo creció 57% desde el inicio de la gestión de Javier Milei. También detectó un fuerte avance del uso de tarjetas para sostener compras básicas.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>No pierdas tus dólares: qué hacer si no te llegó tu pedido de Shein o Temu</t>
+          <t>Cuenta DNI oficializó los beneficios de mayo 2026 y el descuento en carnicerías sigue de lunes a viernes</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/no-pierdas-tus-dolares-que-hacer-si-no-te-llego-tu-pedido-shein-o-temu-n6271127</t>
+          <t>https://www.ambito.com/economia/cuenta-dni-oficializo-los-beneficios-mayo-2026-y-el-descuento-carnicerias-sigue-lunes-viernes-n6272721</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -3382,24 +3382,24 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Conociendo las opciones que existen para recuperar el dinero en cada caso, así es como tenés que actuar ante demoras en tu entrega.</t>
+          <t>La billetera digital de Banco Provincia continua con una amplia variedad de promociones en distintos rubros.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>La industria de China aumentó sus ganancias empresarias a pesar de la guerra en Medio Oriente</t>
+          <t>Impuesto a las Ganancias: los trabajadores que pagan el tributo recibirán una devolución en mayo</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/la-industria-china-aumento-sus-ganancias-empresarias-pesar-la-guerra-medio-oriente-n6271308</t>
+          <t>https://www.ambito.com/economia/impuesto-las-ganancias-los-trabajadores-que-pagan-el-tributo-recibiran-una-devolucion-mayo-n6272562</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -3414,24 +3414,24 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Los datos oficiales mostraron que las ganas industriales crecieron a su mejor ritmo en seis meses. Sin embargo, el riesgo de un impacto de la guerra sobre el entramado productivo chino sigue latente.</t>
+          <t>La mayoría de las empresas retiene de más el impuesto a las Ganancias en los salarios de sus empleados en la primera mitad del año fiscal. Luego se ajustan las escalas en el segundo semestre. En abril del año siguiente, se reintegran los saldos a favor.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Las tasas se desploman en el mercado, pero el costo de los préstamos personales sube en términos reales</t>
+          <t>La inversión real bajó 0,8% anual en marzo, según Orlando Ferreres</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/las-tasas-se-desploman-el-mercado-pero-el-costo-los-prestamos-personales-sube-terminos-reales-n6271213</t>
+          <t>https://www.ambito.com/economia/la-inversion-real-08-anual-marzo-segun-orlando-ferreres-n6272610</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -3446,24 +3446,24 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>A pesar de la caída de las tasas de interés generales, los préstamos personales se mantienen estables en comparación con 2022, afectando a familias endeudadas.</t>
+          <t>La baja en la inversión muestra un contraste con la caída de 11,1% de febrero y la merma de enero, pero advierten que el "repunte es mínimo".</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Chau plazo fijo: así operan los principales bancos hoy, lunes 27 de abril</t>
+          <t>La inflación esperada por la población sigue alta: se ubicó en el 3,9% para abril</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/chau-plazo-fijo-asi-operan-los-principales-bancos-hoy-lunes-27-abril-n6271206</t>
+          <t>https://www.ambito.com/economia/la-inflacion-esperada-la-poblacion-sigue-alta-se-ubico-el-39-abril-n6272584</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -3478,24 +3478,24 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Las entidades mantienen rendimientos moderados y el mapa de tasas sigue mostrando diferencias para quienes buscan cuidar pesos.</t>
+          <t>Para los próximos 30 días, la inflación esperada en abril se ubicó en 3,93% en promedio y 3% de mediana.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Salarios y paritarias de metalúrgicos: cuánto cobrarán en mayo de 2026 tras el último acuerdo</t>
+          <t>Últimos días de abril para invertir en plazo fijo: cuánto gano a 30 días si deposito $150.000 hoy</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/salarios-y-paritarias-metalurgicos-cuanto-cobraran-mayo-2026-el-ultimo-acuerdo-n6271204</t>
+          <t>https://www.ambito.com/economia/ultimos-dias-abril-invertir-plazo-fijo-cuanto-gano-30-dias-si-deposito-150000-hoy-n6271757</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -3510,24 +3510,24 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Los metalúrgicos cobrarán en mayo los sueldos de abril con escalas actualizadas. No es un aumento nuevo, sino la aplicación del último acuerdo vigente.</t>
+          <t>Conocé los valores porcentuales de acuerdo a cada entidad bancaria y analizá el método más conveniente para poder realizar la operatoria.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Lanzan Kit 4.0, el programa del Gobierno para impulsar la transformación tecnológica de las pymes</t>
+          <t>Chau plazo fijo: las tasas siguen a la baja y así operan los principales bancos hoy, jueves 30 de abril</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/lanzan-kit-40-el-programa-del-gobierno-impulsar-impulsa-la-transformacion-tecnologica-las-pymes-n6271132</t>
+          <t>https://www.ambito.com/economia/chau-plazo-fijo-las-tasas-siguen-la-baja-y-asi-operan-los-principales-bancos-hoy-jueves-30-abril-n6272537</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -3542,24 +3542,24 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>La iniciativa del Ministerio De Economía apunta a impulsar la adopción de tecnología e Industria 4.0 mediante aportes del FONPEC y un esquema de cofinanciamiento.</t>
+          <t>Las entidades mantienen rendimientos similares y crece la cautela entre ahorristas frente a inflación y expectativas cambiarias.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Ni Shein ni Temu: la nueva plataforma para compras en el exterior que es furor</t>
+          <t>Así funciona el nuevo sistema de ARBA para pymes que alivia la carga financiera de Ingresos Brutos</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/ni-shein-ni-temu-la-nueva-plataforma-compras-el-exterior-que-es-furor-n6270242</t>
+          <t>https://www.ambito.com/economia/asi-funciona-el-nuevo-sistema-arba-pymes-que-alivia-la-carga-financiera-ingresos-brutos-n6272519</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -3574,24 +3574,24 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>El avance de apps de compras extranjeras cambió los hábitos, brindando una alternativa con beneficios inéditos y precios imbatibles.</t>
+          <t>Más de 12.000 empresas ya operan bajo el esquema "Riesgo 0, SAF 0" que ajusta automáticamente las retenciones para evitar saldos a favor acumulados.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>La guerra en Medio Oriente también impacta en un alimento inesperado: se disparó el precio mundial del pistacho</t>
+          <t>La inflación en la Eurozona repuntó al 3% anual, tras el aumento del costo de la energía</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/la-guerra-medio-oriente-tambien-impacta-un-alimento-inesperado-se-disparo-el-precio-mundial-del-pistacho-n6271007</t>
+          <t>https://www.ambito.com/economia/la-inflacion-la-eurozona-repunto-al-3-anual-el-aumento-del-costo-la-energia-n6272487</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -3606,24 +3606,24 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>El conflicto entre Estados Unidos, Israel e Irán alteró el comercio global del pistacho, cuya producción se concentra en esa región. El valor internacional alcanzó máximos de ocho años y Argentina busca aprovechar la oportunidad con fuerte expansión del cultivo en dos provincias clave.</t>
+          <t>La inflación en la zona euro volvió a acelerarse en abril y alcanzó el 3% anual, impulsada principalmente por el fuerte salto de los precios de la energía.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>La industria repuntó en marzo y cortó racha de ocho meses de caídas interanuales, según Orlando Ferreres</t>
+          <t>Comercio exterior: el Puerto de Mar del Plata lanza incentivos para exportar y busca frenar la salida de cargas a otros puertos</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/la-industria-repunto-marzo-y-corto-racha-ocho-meses-caidas-interanuales-segun-orlando-ferreres-n6271004</t>
+          <t>https://www.ambito.com/economia/comercio-exterior-el-puerto-mar-del-plata-lanza-incentivos-exportar-y-busca-frenar-la-salida-cargas-otros-puertos-n6272447</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -3638,24 +3638,24 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Según el Índice de Producción Industrial, la actividad fabril subió 0,8% mensual desestacionalizado y 0,7% interanual. Pese a la mejora de marzo, el primer trimestre cerró con saldo negativo y persisten dudas sobre la demanda.</t>
+          <t>El Consorcio Portuario Regional aprobó beneficios de hasta el 100% en cánones y aplicará recargos para desalentar desvíos logísticos.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Buepp acepta pagos con NFC: cómo usarlo para obtener los descuentos</t>
+          <t>Suben las tasas aeroportuarias y crecen los costos para las aerolíneas</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/buepp-acepta-pagos-nfc-como-usarlo-obtener-los-descuentos-n6270169</t>
+          <t>https://www.ambito.com/economia/suben-las-tasas-aeroportuarias-y-crecen-los-costos-las-aerolineas-n6272445</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -3670,24 +3670,24 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>La billetera virtual del Banco Provincia establece reintegros en todos los ámbitos del consumo cotidiano con beneficios diarios.</t>
+          <t>La medida de la ANAC fija subas en las tasas de vuelo y aterrizaje y deroga el esquema anterior para adecuarlo a los costos del sistema.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>El Banco Central compró más de US$ 7.000 millones en el primer cuatrimestre - Perfil</t>
+          <t>Informe de Política Monetaria | Abril 2026 - Universidad Nacional de Rosario</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPVThjRG9tNTdFVjNISjN2VnY0QXFETnppdGVUVnVXci1tNTRTRTlKNkl6NHBFYkV3TE04RVBpWFpHdnN6T0ZfWlVpWU1oeDVCU3VUaVpnUDBKVW9sMDhUYzVHTHJ6QXdzWHN5MzdJajdUeVgzUnk0clg3OTNtOWtxX0hxb1pjVUYyd1NxRGtneFdFc3gzZDV3U2swbmg3RDA5MS1lZzktYXdxTmxxZWxuaFZ4bFVzT3dacG1ock130gHDAUFVX3lxTE9ycFFRWkVSWS1pNEh6ZFVORnBObHVJOERrd3pKS1VBaVlQSFhzUEFBaGo4UEtpQlFCZndpREdZOGxaS1M5UXBTMzhXX2VJMU15eFVFdVRzSGNjMDBscEFjNkFmRThTUEtaNXFiMkRVeXNrQVZvY1lHRUdIMUlSZWZrOXllT2dGVVVxa1R6c0pJWE9PRUlJVU9ZWkFBc3ItRENHOFcyRnlaUzExSlhOMnZjdEQxV0tMX2xKYl94TlNWdFMtNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9MV0w5TmNaeTV6VExwZ0xDTi1wcFVzc3NoWlotLS1XUEZNVXZZYzVLTF9mQjJDLXlTd0NYUGVES1RsNWxJYkpBQW1QclFyTWlmR1NWNmtMVGNBUlBCaUhBSWpmS2RlTGg5ald1Qg?oc=5</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -3702,24 +3702,24 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>El Banco Central compró más de US$ 7.000 millones en el primer cuatrimestre    Perfil</t>
+          <t>Informe de Política Monetaria | Abril 2026    Universidad Nacional de Rosario</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>El presidente del BCRA aseguró que los bancos "ya vieron el pico de morosidad" - MinutoUno</t>
+          <t>El Banco Central compró más de US$ 7.000 millones en el primer cuatrimestre - Perfil</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNcnZqcnVkSGhTZ3d5czFHQ2s4UC00MXZuQmdpRkpKb0RCNUtXaTMxdWxnQ25vNFVqN21NZVRiQm51YnFXS29ZRGRCeTBWcWhnLTZhWDlKYVZ2MG5XTmwzNmNHd3FpdzNlUk03X29kTVJ0ZHR3V0lQYnBNczNtTnlmanRmZTBuMXZkWXVKWDZRb2hXeVNZQkN5X1R6VEdaeEZteHRuVldJRlJYYXE4elh0c3N4TFJHNW440gG4AUFVX3lxTE1ydmpydWRIaFNnd3lzMUdDazhQLTQxdm5CZ2lGSkpvREI1S1dpMzF1bGdDbm80VWo3bU1lVGJCbnVicVdLb1lEZEJ5MFZxaGctNmFYOUphVnYwbldObDM2Y0d3cWl3M2VSTTdfb2RNUnRkdHdXSVBicE1zM21OeWZqdGZlMG4xdmRZdUpYNlFvaFd5U1lCQ3lfVHpUR1p4Rm14dG5WV0lGUlhhcTh6WHRzc3hMUkc1bjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPVThjRG9tNTdFVjNISjN2VnY0QXFETnppdGVUVnVXci1tNTRTRTlKNkl6NHBFYkV3TE04RVBpWFpHdnN6T0ZfWlVpWU1oeDVCU3VUaVpnUDBKVW9sMDhUYzVHTHJ6QXdzWHN5MzdJajdUeVgzUnk0clg3OTNtOWtxX0hxb1pjVUYyd1NxRGtneFdFc3gzZDV3U2swbmg3RDA5MS1lZzktYXdxTmxxZWxuaFZ4bFVzT3dacG1ock130gHDAUFVX3lxTE9ycFFRWkVSWS1pNEh6ZFVORnBObHVJOERrd3pKS1VBaVlQSFhzUEFBaGo4UEtpQlFCZndpREdZOGxaS1M5UXBTMzhXX2VJMU15eFVFdVRzSGNjMDBscEFjNkFmRThTUEtaNXFiMkRVeXNrQVZvY1lHRUdIMUlSZWZrOXllT2dGVVVxa1R6c0pJWE9PRUlJVU9ZWkFBc3ItRENHOFcyRnlaUzExSlhOMnZjdEQxV0tMX2xKYl94TlNWdFMtNA?oc=5</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -3734,88 +3734,88 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>El presidente del BCRA aseguró que los bancos "ya vieron el pico de morosidad"    MinutoUno</t>
+          <t>El Banco Central compró más de US$ 7.000 millones en el primer cuatrimestre    Perfil</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>El BCRA reconoció presión inflacionaria, pero confía en una baja en los próximos meses - Diario Mendoza</t>
+          <t>Dólar blue hoy: a cuánto opera este jueves 7 de mayo</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOYlJwcGxycmdoQWo4allRYk04N09wY3EzOXVfVGhtSVdNNVcwenEydUtSMXo0ajZqNmxDaEg5QVlxNUN3VXZoOVNQS3NKU2RKcmdSTnZnZWY2bVNFZnR5eGdoZUY5WHVBWWl4dERma1VVQ21oNC10enBSenpIN1Y4Q2VyLW1zcFdJYU5xU25HVnhicmZWclVBVEZPRHZNaVpiOTFSckY5WUFyc1R5SDRmRkg5QUlLSEVGLU92eGpkZl9HQ0XSAcgBQVVfeXFMT19mQW9UemljUDJiZnJLd2Q0X2I1Z2F5NnotRzFucFphQm1FTWRld3lKTFJNaFBKS1JQY01lelVRUlJmV0tRdlRSb2ptcjJHNkJXQmd2VWM5eUFXZmVMN1VCXzFPbTRNRENQNl9SUTVfeHVWZjBJRlBKaGJPMHlRaENfXzRsWnh1MFZEYTZ5VmV4cGh3U204ZkpDVERId01TaEVzTzlLNmZjNjNaZ1NWUXZfbF93X3E0Vl9EV3F4NENFTVZLcWFzNWE?oc=5</t>
+          <t>https://www.ambito.com/finanzas/dolar-blue-hoy-cuanto-opera-este-jueves-7-mayo-n6274862</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Google News - BCRA</t>
+          <t>Ambito - Finanzas</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Macro &amp; Policy</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>El BCRA reconoció presión inflacionaria, pero confía en una baja en los próximos meses    Diario Mendoza</t>
+          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Paro en el BCRA: impacto en la actividad financiera - Vive La Plata</t>
+          <t>Dólar hoy: a cuánto cotiza este jueves 7 de mayo</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNcXFTTXdza3UxdHk1QWxPNDNWcktfUTJRb2R6Wk5PUEVvczc2cExQYTV2STBJdm02eC1ZNzh5aExjZmJlaElsUHZnNi10QU5UbVdLbUo5cTR4ZXNmcTg5SGdiMWpVV3QzVGU0WVVjQk94eVZVVERnc3V0N2VPMDRGOXdYRmI?oc=5</t>
+          <t>https://www.ambito.com/finanzas/dolar-hoy-cuanto-cotiza-este-jueves-7-mayo-n6274861</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Google News - BCRA</t>
+          <t>Ambito - Finanzas</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Macro &amp; Policy</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Paro en el BCRA: impacto en la actividad financiera    Vive La Plata</t>
+          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Dólar hoy: a cuánto cotiza este lunes 4 de mayo</t>
+          <t>Euro hoy y Euro blue hoy: a cuánto cotiza este jueves 7 de mayo</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/dolar-hoy-cuanto-cotiza-este-lunes-4-mayo-n6273493</t>
+          <t>https://www.ambito.com/finanzas/euro-hoy-y-euro-blue-hoy-cuanto-cotiza-este-jueves-7-mayo-n6274797</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -3830,24 +3830,24 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
+          <t>Mirá a cuánto cotizan el euro oficial y el euro blue.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Dólar blue hoy: a cuánto opera este lunes 4 de mayo</t>
+          <t>Real blue: a cuánto opera este jueves 7 de mayo</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/dolar-blue-hoy-cuanto-opera-este-lunes-4-mayo-n6273494</t>
+          <t>https://www.ambito.com/finanzas/real-blue-cuanto-opera-este-jueves-7-mayo-n6274800</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -3862,24 +3862,24 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
+          <t>La cotización minuto a minuto para la compra y venta de la divisa brasileña en nuestro país.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Dólar blue hoy: a cuánto opera este lunes 4 de mayo</t>
+          <t>Rally de acciones y bonos: los ADRs treparon hasta 11% y el riesgo país se hundió 7% tras la mejora de la nota soberana</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/dolar-blue-hoy-cuanto-opera-este-lunes-4-mayo-n6273494</t>
+          <t>https://www.ambito.com/finanzas/los-bonos-dolares-rebotan-fuerza-impulsados-el-optimismo-los-mercados-globales-n6274482</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -3894,24 +3894,24 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
+          <t>Los bonos soberanos en dólares rebotaron con fuerza en la jornada, liderados por los Globales de mayor plazo, luego de que la deuda argentina recibiera una mejora de calificación. En Wall Street, los bancos encabezaron las subas, mientras que las energéticas retrocedieron por la baja del petróleo.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Euro hoy y Euro blue hoy: a cuánto cotiza este lunes 4 de mayo</t>
+          <t>Bitcoin anota su sexta suba en siete ruedas y toca un nuevo máximo en más de 3 meses</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/euro-hoy-y-euro-blue-hoy-cuanto-cotiza-este-lunes-4-mayo-n6273457</t>
+          <t>https://www.ambito.com/finanzas/bitcoin-consolida-la-tendencia-alcista-la-expectativa-un-acuerdo-paz-eeuu-e-iran-n6274525</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Mirá a cuánto cotizan el euro oficial y el euro blue.</t>
+          <t>Además de las crecientes expectativas de que el conflicto en Medio Oriente llegue a su fin, los inversores cripto siguen de cerca dos elementos clave en EEUU: el avance de la Ley Clarity y el dato de empleo que se conocerá el viernes.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Real blue: a cuánto opera este lunes 4 de mayo</t>
+          <t>Real blue: a cuánto operó este miércoles 6 de mayo</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/real-blue-cuanto-opera-este-lunes-4-mayo-n6273466</t>
+          <t>https://www.ambito.com/finanzas/real-blue-cuanto-opero-este-miercoles-6-mayo-n6274339</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -3970,12 +3970,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Mientras el mercado ya mira el 2027, llegan 15 balances de empresas argentinas: los datos clave a seguir en la semana</t>
+          <t>Euro hoy y Euro blue hoy: a cuánto cotizó este miércoles 6 de mayo</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/mientras-el-mercado-ya-mira-el-2027-llegan-15-balances-empresas-argentinas-los-datos-clave-seguir-la-semana-n6273394</t>
+          <t>https://www.ambito.com/finanzas/euro-hoy-y-euro-blue-hoy-cuanto-cotiza-este-miercoles-6-mayo-n6274337</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -3990,24 +3990,24 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>El deterioro en la actividad, la inflación y los salarios empieza a impactar en las expectativas. Mientras el Gobierno sostiene el frente financiero sin sobresaltos, los inversores exigen mejor tasa a 2028 y analizan las opciones en pesos.</t>
+          <t>Mirá a cuánto cotizan el euro oficial y el euro blue.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Dólar hoy: a cuánto cotiza este domingo 3 de mayo</t>
+          <t>Wall Street quebró nuevos récords ante un posible acuerdo de paz entre EEUU e Irán</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/dolar-hoy-cuanto-cotiza-este-domingo-3-mayo-n6273285</t>
+          <t>https://www.ambito.com/finanzas/el-petroleo-cae-debajo-los-us100-y-los-mercados-celebran-un-posible-acuerdo-paz-medio-oriente-n6274413</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -4022,24 +4022,24 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
+          <t>La Casa Blanca cree estar cerca de firmar un memorándum para poner fin a la guerra con Teherán, lo que hizo disparar las acciones en los principales mercados del mundo. El crudo retrocedió cerca de los u$s100 por barril.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Dólar blue hoy: a cuánto opera este domingo 3 de mayo</t>
+          <t>El dólar blue retrocedió y tocó mínimos de casi un mes</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/dolar-blue-hoy-cuanto-opera-este-domingo-3-mayo-n6273286</t>
+          <t>https://www.ambito.com/finanzas/el-dolar-blue-retrocedio-y-toco-minimos-casi-un-mes-n6274751</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -4054,24 +4054,24 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
+          <t>El billete paralelo bajó $15 y dejó atrás la suba mensual acumulada. La brecha con el tipo de cambio oficial descendió a menos de 1%.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Dólar hoy: a cuánto cotiza este sábado 2 de mayo</t>
+          <t>Dólar hoy y dólar blue hoy minuto a minuto: a cuánto opera este miércoles 6 de mayo</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/dolar-hoy-cuanto-cotiza-este-sabado-2-mayo-n6273106</t>
+          <t>https://www.ambito.com/finanzas/dolar-hoy-y-dolar-blue-hoy-minuto-minuto-cuanto-opera-este-miercoles-6-mayo-n6274397</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -4098,12 +4098,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Dólar blue hoy: a cuánto opera este sábado 2 de mayo</t>
+          <t>Dólar blue hoy: a cuánto cerró este miércoles 6 de mayo</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/dolar-blue-hoy-cuanto-opera-este-sabado-2-mayo-n6273107</t>
+          <t>https://www.ambito.com/finanzas/dolar-blue-hoy-cuanto-cerro-este-miercoles-6-mayo-n6274703</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -4130,12 +4130,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Morosidad: alerta por el nivel del GBA, mientras que el BCRA y los bancos aseguran que el pico ya pasó</t>
+          <t>Dólar hoy: a cuánto cerró este miércoles 6 de mayo</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/morosidad-alerta-el-nivel-del-gba-mientras-que-el-bcra-y-los-bancos-aseguran-que-el-pico-ya-paso-n6273159</t>
+          <t>https://www.ambito.com/finanzas/dolar-hoy-cuanto-cerro-este-miercoles-6-mayo-n6274702</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -4150,24 +4150,24 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>En las últimas semanas, creció la preocupación por el nivel de morosidad, que en el Gran Buenos Aires ya se cuadruplicó durante el último año, según datos que se desprenden de un informe del BCRA. Mientras tanto, distintos actores del sistema financiero aseguran que el "pico ya pasó".</t>
+          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Deuda: Economía enfrenta vencimientos por $6,9 billones en mayo y seguirá con la política de estirar plazos</t>
+          <t>Avanza la ley de regulación cripto en EEUU pero aún no se disipa la "guerra" entre bancos y exchanges</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/deuda-economia-enfrenta-vencimientos-69-billones-mayo-y-seguira-la-politica-estirar-plazos-n6272821</t>
+          <t>https://www.ambito.com/finanzas/avanza-la-ley-regulacion-cripto-eeuu-pero-aun-no-se-disipa-la-guerra-bancos-y-exchanges-n6274662</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -4182,24 +4182,24 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Se espera que el Tesoro trate de ir nuevamente por niveles de rollover por encima del 100%. Las colocaciones hard dollar ya superan los u$s2.250 millones.</t>
+          <t>El nuevo borrador del proyecto que busca regular a las stablecoins logró un acuerdo bipartidario en el Senado de EEUU. Los bancos destacaron los cambios, pero aún no están conformes con el texto, mientras que las empresas cripto cuestionaron los argumentos del sector financiero tradicional.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Mercado de capitales: más comitentes, nuevos instrumentos y el impulso de las nuevas generaciones</t>
+          <t>Dólar hoy: a cuánto cotiza este miércoles 6 de mayo</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/mercado-capitales-mas-comitentes-nuevos-instrumentos-y-el-impulso-las-nuevas-generaciones-n6272341</t>
+          <t>https://www.ambito.com/finanzas/dolar-hoy-cuanto-cotiza-este-miercoles-6-mayo-n6274379</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -4214,24 +4214,24 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Los actores del sistema financiero celebran el aumento del volumen de las operatorias y la canalización del ahorro a una función productiva.</t>
+          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Cambios en los pagos digitales: cómo deben adecuarse las fintech a la nueva norma del BCRA</t>
+          <t>Dólar blue hoy: a cuánto opera este miércoles 6 de mayo</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/cambios-los-pagos-digitales-como-deben-adecuarse-las-fintech-la-nueva-norma-del-bcra-n6272979</t>
+          <t>https://www.ambito.com/finanzas/dolar-blue-hoy-cuanto-opera-este-miercoles-6-mayo-n6274380</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -4246,24 +4246,24 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>La nueva normativa del BCRA pone fin a los grises legales al regular a las fintech que operan bajo la modalidad de servicio en pagos digitales.</t>
+          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Dólar hoy: a cuánto cotiza este viernes 1 de mayo</t>
+          <t>El FGS de ANSES salió a comprar acciones y aumentó su participación en empresas: en qué invierte y cuál es el impacto</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/dolar-hoy-cuanto-cotiza-este-viernes-1-mayo-n6272879</t>
+          <t>https://www.ambito.com/finanzas/el-fgs-salio-comprar-acciones-y-aumento-su-participacion-empresas-que-invierte-y-cual-es-el-impacto-n6274661</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -4278,24 +4278,24 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
+          <t>Se trata de una reconstrucción de Ámbito en base a los últimos datos disponibles a abril de 2025. ANSES no detalla la composición específica de las inversiones del FGS. En sectores clave como energía y servicios financieros, el incremento derivó en la designación de directores en asambleas. Desde la</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Dólar blue hoy: a cuánto opera este viernes 1 de mayo</t>
+          <t>El dólar oficial volvió a ceder y registró un mínimo de dos semanas</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/dolar-blue-hoy-cuanto-opera-este-viernes-1-mayo-n6272880</t>
+          <t>https://www.ambito.com/finanzas/el-dolar-oficial-se-mantiene-debajo-los-1400-y-continua-su-alejamiento-del-techo-la-banda-n6274457</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -4310,29 +4310,29 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
+          <t>La cotización del tipo de cambio estiró la brecha con la banda cambiaria, algo que le otorga más margen al Banco Central para intervenir en el MLC sin necesidad de vender.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Qué está pasando en el Congreso: elecciones presidenciales y falta de quórum frenan la agenda legislativa</t>
+          <t>Las acciones de Disney saltaron en Wall Street tras el reporte de un sólido balance</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/04/que-esta-pasando-en-el-congreso-elecciones-presidenciales-y-falta-de-quorum-frenan-la-agenda-legislativa/</t>
+          <t>https://www.ambito.com/finanzas/las-acciones-disney-saltaron-wall-street-el-reporte-un-solido-balance-n6274555</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Ambito - Finanzas</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -4342,29 +4342,29 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>El avance de la agenda legislativa se ha visto interrumpido por sesiones que no logran continuar con el orden del día, lo que ha impedido la discusión y votación de varios proyectos. A esto se suman tensiones entre bancadas y cruces de señalamientos sobre la responsabilidad del estancamiento</t>
+          <t>Disney reportó ingresos por unos u$s25.200 millones en su segundo trimestre fiscal de 2026, lo que representa un aumento interanual cercano al 7%.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Del frío a la ciclogénesis: cómo estará el tiempo en el AMBA esta semana</t>
+          <t>Qué implica la mejora de la calificadora de riesgo Fitch a la deuda argentina</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/sociedad/2026/05/04/del-frio-a-la-ciclogenesis-como-estara-el-tiempo-en-el-amba-esta-semana/</t>
+          <t>https://www.ambito.com/finanzas/que-implica-la-mejora-la-calificadora-riesgo-fitch-la-deuda-argentina-n6274509</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Ambito - Finanzas</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -4374,29 +4374,29 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>La segunda mitad de la semana estará marcada por vientos extremos, tormentas y lluvias abundantes que afectarían algunas zonas de la provincia durante al menos 72 horas</t>
+          <t>Tras conocerse la recalificación de la deuda por parte de Fitch se abre un universo de posibilidades.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Cómo impacta en los bonos en dólares de Argentina el calendario electoral 2027 - Bloomberg Línea</t>
+          <t>Se elimina la reelección inmediata y nepotismo en el Edomex: normas entrarán en vigor en 2030</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOcWIyRXJBNEFncnpkbkt5QWlSTlJya28tRGRuM3NRQnpNSWhaNE9qWV9OZUFVQlJmNjRrWjlBWXE4QXlndmJtN3RoblMtbGZwV1Q3TW1wZ0d2dzN1cWRfYTBsYnV5NmhFMU1aNmRIcmtlMlJ6Vk9tNFBQUUdYcWo2eEF3Wksta2dqZFNIN2FycF83cnNDRU1RT0N5WC1sM0IwMXNRTW54M2k4YTZSa2ZtV1hBeU4ydnJnaWhaRjhqQmIzbjFwS3N6Qi10MFN0dDjSAeMBQVVfeXFMT2dhSlh5QUw3d3M1d0RmMXJmWk9VNG83V0lXMnNpeEJLSEhSb0ZXa3BIWmhnZXdpVzVGa2VGRy0tQXZkS0FOMzlfRnI5RFpUVVUyZGF5WUhoZDBmei16ZkV2TVM5Qzhac0ZESXRJN2paUzZoWGQxN0xnM19VUlg3VnNoeU9tWnROLTQ2Nm1nblJKZzYwV05OcEZ2Ti1ub3hLTjZIREMzNXZfNkxGVkM4akl5ZFVYQmNsM2FEZWl6c1RJVHZFcjlDdWhWSHZOelc1V0tOU0RGWkcwY21aQ0oxdnlIZkE?oc=5</t>
+          <t>https://www.infobae.com/mexico/2026/05/07/se-elimina-la-reeleccion-inmediata-y-nepotismo-en-el-edomex-normas-entraran-en-vigor-en-2030/</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Google News - Mercados</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -4406,618 +4406,4242 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Cómo impacta en los bonos en dólares de Argentina el calendario electoral 2027    Bloomberg Línea</t>
+          <t>Se aprueba el “Plan B” de la reforma electoral de la presidenta Claudia Sheinabaum</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>El Gobierno se apoyó en el Tesoro de los EEUU para pagarle al FMI: cómo fue la operación - Infobae</t>
+          <t>Inundaciones, granizo y vientos: continúa la alerta naranja por fuertes tormentas en Buenos Aires</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQY3ZmRDA1Qmx6UHBXM0xfN1Vna3Z2VmU5YlpiV29FRE5VTk1UVGJadl9RRGx6OS1NN1d5Q0syelp1LUJ5S0tidUw3MkwzcXZ6RGFOMDlYdjhWUy1ZbmM3OF9KUFV0RUhnSGkxeUNkd0VLOEVHS0FXYVRtNFJhQjBzbXhTNEpJOG1rdzc2YXB4M1JKTlhRRjhKb3N2eWV6OUZFNkh3MUhBV2Zsa1Vua3VyVk9ScE9tOWJLNWppU0hYVF9nQ0VCdERSbWFWdGbSAecBQVVfeXFMTm12VUNIaTMzQ1pDNGpBUndLZXlBNlFqbFhJd0w0QjR0TDRjRkdSTTNBU2tTNDE3ZlFwZGN2dGpDcXY1QjZoNHgtUG1aSjVJT0FmY1JET0F3c2hMd3Ewcl8zcVh2RU41aWl6WExQY3EwV3BkcWhUaWQ5MjVfNTFmN2xvZVBmVlBMZUZWTllPMDQwbW5QVHdDenhJcFZHRzJlUVNmc3NITml4NUpia2Qza0RxR1Rrdmd3MEpRbkhCcjlGSU4yQmREWHhKZ1FPWmVvRzZ2UFZ3X1o5Q091b0E0T0FFQ25lXzNZ?oc=5</t>
+          <t>https://www.infobae.com/sociedad/2026/05/07/inundaciones-granizo-y-vientos-continua-la-alerta-naranja-por-fuertes-tormentas-en-buenos-aires/</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Google News - FMI</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>International Impact</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>El Gobierno se apoyó en el Tesoro de los EEUU para pagarle al FMI: cómo fue la operación    Infobae</t>
+          <t>El SMN advierte que las alertas siguen vigentes por tormentas y fuertes vientos que y afectó a varias zonas durante la medianoche del jueves. Además, advierten sobre el fenómeno de ciclogénesis</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>La deuda externa es la más alta de la historia y se multiplicaron por cuatro los vencimientos de corto plazo - La Política Online</t>
+          <t>Hantavirus, última hora del crucero MV Hondius y su llegada a Canarias, en directo | Países Bajos informa de un nuevo posible contagio de una azafata de vuelo</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPU1NIUmZsQ3M2LWktOUVlZlM4bGZBQ1NxQzJWZmdfYTVXZ2s2T1Y3QUNTZV82T2ZGeXZSWDhKUEZBUjM5WVd3V3I5MERuX1B6ekZLM29qUTdITlI3cUg3amV2T3RUazkybXYyZVNFUVpDNGRPQ21JcmcyX2ludWk5elp3bzd0ZDZtWnFwSGtqTVR1REFRNlRyOFZQb044bWh6Zm1FZkVyUlRWWjY1RHVEMUViSlF5Y19Lbktnc9IB6AFBVV95cUxPYmRyRzhJRkhEN3JtM1hiOFAtTmY0d3FzNmRHWjBwenVObEQ1amFfNGpGZmxoOXI1WFJrS2RzdUZaeGtDbkl0SGI5b2ZSMi1WYXdQOTZ3b3lqVUFzNkFyTkhxMzNxdHkyY3VRV01sNGVwa2ViMXB5UUY5YkM4QXQwTlpLOERqZENEQl8yNVA2eDR3SjhkUlFfUkVVaHBHM2t5MnpGNjhLWEQ1UERRVzUtZllKUmhwOC1DRjRobjhiX0FUa1VQMXZlbE1LX2tsUnFBTFNyX3RvWTBnREtMWGM2bE8yUWtIOEgt?oc=5</t>
+          <t>https://www.infobae.com/espana/2026/05/07/hantavirus-ultima-hora-del-crucero-mv-hondius-y-su-llegada-a-canarias-en-directo-se-preve-que-la-embarcacion-llegue-el-sabado-a-tenerife/</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Google News - FMI</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>International Impact</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>La deuda externa es la más alta de la historia y se multiplicaron por cuatro los vencimientos de corto plazo    La Política Online</t>
+          <t>El brote vírico, que corresponde a la cepa de los Andes, ha causado tres muertes y varios contagios confirmados por laboratorio</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>La deuda externa más alta de la historia: cuánto endeudaron al Estado los últimos gobiernos - Enterate Noticias</t>
+          <t>Magaly Medina expone dramático caso contra el doctor Hoshe Joo tras muerte de ingeniero de 40 años</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNNVF4UFVaY3AxdEphcWRsZldPbElSUW14b0haYVBzWjR3eGVTM3B6REdHN0pvOW5hZEJ2M00ySDdMZF9vVW9VOWpvY2VUcTJWMnl5YVpoN1pGSm50VEd0YXc3bUJvbmpYQ0E0ZTBiNksyWnByNHA3Y1dQdkkwODRzUGpsOEFtd29NQW9HMFU0QmQxOXdBNm1Rb1lTTTRtdkN3allTcC1fQ1FwWGVaTi1STnoyUzRKcFB2ZUp6VzlRUdIBuAFBVV95cUxQMVh5RWNDak5fTmYzUi16dGxXQnVERVJYQnNpSTMyNU1HUUlGcXBoQ0JYWGxFY1dJX3lYNTdacU9rQXpIV2E5dkN5UWZxMEJIal92UFBNaHRLeU55QVBSaGFLMUpYUnFMcGZJOFE3R3I1cHBLUnF2d0VaWW5GUFdSeVU3a2hyMmRYVWJUS2xUcXhtVmZRd0dyTUd6cjdGWkNIUXpwT0pORDZIOXg2UnBGQllBcnYxenJr?oc=5</t>
+          <t>https://www.infobae.com/peru/2026/05/07/magaly-medina-expone-dramatico-caso-contra-el-doctor-hoshe-joo-tras-muerte-de-ingeniero-de-40-anos/</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Google News - FMI</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>International Impact</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>La deuda externa más alta de la historia: cuánto endeudaron al Estado los últimos gobiernos    Enterate Noticias</t>
+          <t>La periodista presentó el caso de Cristian Maldonado, un ingeniero de 40 años que falleció tras someterse a un procedimiento bariátrico en una clínica de San Isidro</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>La Argentina le compró DEG a Estados Unidos por US$819 millones para pagarle intereses al FMI - La Nación</t>
+          <t>Este es el ejercicio ideal para que las mujeres mayores de 50 años pierdan grasa abdominal</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPUHQ2SDRDSnJLdzZfUGR2RjhidU42QWtHX1FZV2pDaDBIWVFkQ05SV3hYSUhnbDJEeHdicVlkWjgxVEU1b0xaZzY0c0UzQjc0cktVVEE4ZDkwSFZkc3d3MERyY3FIOU1NMnFqcTVYcHB1c0Zkd0F0NWNMQkNhZUZFU0hqd2dteFQ2NEVJVmZyX04yM1JFUjlNT1ZjdXB3T1JXTHluY0EtWnRrQXdUUzRkTWMteTRZdENXLUx5NDgtM2NIck5QT25wQ2RoRFJVYWZVcjdNaVEtWExyZw?oc=5</t>
+          <t>https://www.infobae.com/espana/2026/05/07/este-es-el-ejercicio-ideal-para-que-las-mujeres-mayores-de-50-anos-pierdan-grasa-abdominal/</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Google News - FMI</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>International Impact</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>La Argentina le compró DEG a Estados Unidos por US$819 millones para pagarle intereses al FMI    La Nación</t>
+          <t>La entrenadora Andrea Marcellus recomienda una actividad para eliminar la grasa localizada</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>El Gobierno concretó un nuevo DEG con el Tesoro de Estados Unidos por US$ 819 millones para pagar deuda al FMI - Diario Río Negro</t>
+          <t>Cristina Boscá y Karin Herrero hacen oficial su relación: “Estoy saliendo con una compañera de trabajo 12 años mayor”</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQc2FQT3A3eVVmbWNhaDFMNEpYd19BM3BPRm1EaTZmSkdMeUZ2RDZEMDZRWjhDakV2eF9sRFVTc05HSWNRSGY2TmpQWExPZFVMaUdPRWhtTGJUek02ekJsUHg3ZTM3aVZGa1hGMThNTW11UjZxNnY2ektqdFBVaTJfeU5sTWJPdnBPZGYzTWVfTUJGQjU0cTZXem1lMC10cF9xRjhxcUFhVXRpUTFMQ2xzMW1SRV9iMWFTT2ZzaUtaUEFUMzRrSkw4Z1hiY1VqVE9lekNfcdIB3AFBVV95cUxPaE10VXJmSHVjWlFRVmE3RXJsc2lUcWZTMFJOSnVCX3VON3dOZS1sSjhYTG5PZE5PVWhKSExYTkVTYUpEMkVIOFdwUUlmaTJNU2Z5WUowV1NVcjBQZmtyMUw2MG85cEhRdUNPUE9NNGdLUW1tUGk1V0lJYW5xLXd2Q1paTmVFTlVJTmlTaVkxX0hNVTFXX1lQNGRVRURSX1NvQlpFNU1fVUpJa1JfTWprZm9hOXVmRDV3WVA1bkNCNkVma3hSWTgxX0tMdnVKZjYxRkJiWld1TGY4blN0?oc=5</t>
+          <t>https://www.infobae.com/espana/2026/05/07/cristina-bosca-y-karin-herrero-hacen-oficial-su-relacion-estoy-saliendo-con-una-companera-de-trabajo-12-anos-mayor/</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Google News - FMI</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>International Impact</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>El Gobierno concretó un nuevo DEG con el Tesoro de Estados Unidos por US$ 819 millones para pagar deuda al FMI    Diario Río Negro</t>
+          <t>Los locutores de ‘Anda Ya’, el programa estrella de Los 40, han sorprendido a sus seguidores al confirmar su historia de amor durante un viaje a Nueva York</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Deuda con el FMI: el Gobierno concretó una operación financiera con EEUU para pagar más de U$S800 millones - La Gaceta</t>
+          <t>La población de España crece en 97.021 personas y se sitúa en 49,6 millones</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPdG12TW5FbUpBYjZxWjB3eEQ4RVVtWkl1NXY3TU9tQVFrRlJiRHlSR3c1aENNQXNteFRVOGZOLTg1UHpPWVhNSTdSWGNvZEVCLVhkNEhIcEdzQWxWZGJwWDBCd3B3S2tPemgtMnM3WHYtOUJzWjVRUXlvZk9mWTAtYjZ4cmVhcUJBQTIzeS1HcGYtMlFKcC1kSWxpUzJjOTRWT1pZYjNBbW5rWnM0b0ZuUDNFblY3a1VBbklGY3gwM1lGWmVoN3o0aU1YVmJCU0hCaDlITdIB2gFBVV95cUxQd29NcDE4V3dTbW9tX19VUTdJaGxXQzA3OERQYUZsSC0yY2VPV2xzdG9iRmd1d1JfNlJqMFpuYlZGQkVVdXhRdmtrcXpCYnZqXzdQc1Y4ZkRnMmhURzdBYXhRV3hwUVduSW50Z01CNlZ6bmhJNDhPWjk3OGlUZ3hFZmxmaXUzd1hTUWV3Z2dqcUs2aFkweE8yN1RXRVROVjNaLTJNTEhFU0RoQXJjdWxkeWtTRVdPUk9UMUdYUVRUOUZBX1djZ1NtcDMwNDZPcmRobmIwNXdjMUZtUQ?oc=5</t>
+          <t>https://www.infobae.com/espana/agencias/2026/05/07/la-poblacion-de-espana-crece-en-97021-personas-y-se-situa-en-496-millones/</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Google News - FMI</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>International Impact</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>Deuda con el FMI: el Gobierno concretó una operación financiera con EEUU para pagar más de U$S800 millones    La Gaceta</t>
-        </is>
-      </c>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Exdirector del FMI ve acceso al mercado como llave para resolver la deuda argentina con el organismo - Bloomberg Línea</t>
+          <t>Gordon Ramsay, chef británico: “Para un pescado rebozado de escándalo utilizo media lata de cerveza, una cucharadita de levadura y curry”</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxOeXRqcVlXUm9pelRfRTc5WXN4eEhSa3RmLUhYZTRJODdOTHhYVmM3OUxkaFRpaGxlV0dqdG5PUTFNbVFNdmN1RlJzUVFTUmc0ZVZUbFBkdklSZUQydm1WQUlyV1VJbVJyWEtXczRDdnpHcllHMTNHNllzSnJlbEpzRVU4b0xtMkpRS0laYkczRll0bTdYOHVwcFpLcUV5SDM1elAxX2tTQ3FqUm5Eb0dmUDlWTnpFNnJFRVV3TV9RdFNkcS1vMjEwU0pRWFZHbnNoek9xcTZWYldzX09Wdk1xUGhNeVM3bm1ZZjBybdIBgAJBVV95cUxOdllkZzdGeERqMktHNnRUTGdoSUxreEFZUWhZSkZtZ3lIVW96RzJORWM3aks3Z3JDNURSS0FzTVVCQWs4VVgzcEZENFZpcE1YT1ZtQXJURURWeFIxeEcyU3NkOVRONTVXdUJaRUtObi1YOUpKNXZMRGJGcTB1ZGU5WW1aQVRPU1I2emFzb3ZpMFdfbDRKR2NNdG9VaDMtSnZrVTgycFIwczlQdHZtdkdTMnZJQjJDWmtlQm5DZFdwZkRYZWx2T0VhQ0lpd3JRM0d5Nm5XM1RwVU1QNzRoTUFJbXRvd3JKX1poWDlTcWJPTTBIWkkxdlhGT1Y1T1ZFbVc2?oc=5</t>
+          <t>https://www.infobae.com/espana/2026/05/07/gordon-ramsay-chef-britanico-para-un-pescado-rebozado-de-escandalo-utilizo-media-lata-de-cerveza-una-cucharadita-de-levadura-y-curry/</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Google News - FMI</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>International Impact</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Exdirector del FMI ve acceso al mercado como llave para resolver la deuda argentina con el organismo    Bloomberg Línea</t>
+          <t>El ‘fish and chips’ perfecto es crujiente por fuera y jugoso por dentro, un clásico de la cocina británica que podemos preparar en casa con los consejos del chef y presentador de televisión</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Deuda: el Gobierno volvió a comprarle DEGs a EEUU y le pagó u$s800 millones al FMI - Ambito</t>
+          <t>Cuatro detenidos por cometer estafas manipulando fotos de los rostros de las víctimas</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPX01IRnBJTllEY2RRZlBQYkJMMjRlMFdLcVU5cGFJdTY3WkZaVjNOTVRfNmwxTkpNZHdxWnBpYmJRQzFvWkRyU1hkYk1XRjJ5eWxEZkFSSGFVcnhta0VqeU9nVGRCTTkzODJkcmY1ZEJaekNrWnZXcXhZSHpFVlJJYTdzRWdfcEUtZ0lGWFVFTHI1MzVwalROTGNKcW52QlZibzlsRdIBqgFBVV95cUxOcERfdkJYZS1iOE16TWpjQWZBTkZCekI3N3owR1R5eE9EMlFFcmRUb1pXZUpRWVJHME9VR3FYRThOSXhyTkVsWXdnb2o2S0hjUGRKRXRtelN5Z0pqekJJYlQwN19hMFFvU1VlVk02LVhVVmdxeGRSb3pEaW01SkpNeWs1VERTdVBjQ2JkcnNjYnM4dWMwLXhKeURZNWRLdjJ6RnBXTkRDSjIxdw?oc=5</t>
+          <t>https://www.infobae.com/espana/agencias/2026/05/07/cuatro-detenidos-por-cometer-estafas-manipulando-fotos-de-los-rostros-de-las-victimas/</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Google News - FMI</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>International Impact</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>Deuda: el Gobierno volvió a comprarle DEGs a EEUU y le pagó u$s800 millones al FMI    Ambito</t>
-        </is>
-      </c>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Deuda con el FMI: el Gobierno pagará más de USD 800 millones - Border Periodismo</t>
+          <t>Golpe a una red que logró 500.000 euros con el timo del sicario a clientes de prostitución</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNT09rUTNGUmE5Y0ptdjdHNWR1c05ZUVF5eFhxNHItQUpRY2tjMFhGUVhqeU9kZU1kQjZuWHpldGlQb2tGS2pCVUJzMXpvNnZiLThpbTdOVFJSOWxmcmQ1RXBDTUlER20wYWx6eWY3b2xEVVQwYWRtcm5YQ0loUEZYamFDT3BIT1ZDRk0yQUZkSVpPODc3N1Ztd29FSlBkd0VELVRkM2JKR002dldybVh0SDg0VnoxNTFSQkJVcWRLZThUQ3pXQTJDVW9aRXQ?oc=5</t>
+          <t>https://www.infobae.com/espana/agencias/2026/05/07/golpe-a-una-red-que-logro-500000-euros-con-el-timo-del-sicario-a-clientes-de-prostitucion/</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Google News - FMI</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>International Impact</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>Deuda con el FMI: el Gobierno pagará más de USD 800 millones    Border Periodismo</t>
-        </is>
-      </c>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Deuda récord: supera los USD 483.000 millones y crecen los vencimientos de corto plazo para Nación - NEA HOY</t>
+          <t>El BCE urge a profundizar la integración financiera para apoyar la prosperidad de Europa</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNMWl4TkFWdUsxeEN5eUJ4R2RwSDVSaTNLbGYybTA3WDROb29GZkU5QVo4VVczWVg4eFktdlg4SlZXbnpuX1doWHFnbEt6eHg2ZG9ZVEZiTjdKUjBSdElwXzRhVzJNellqQy1aaGRTN2pab0FQRGtmYVpmVHNoMjMwc3N5THV2RGxrbUozZ0hqRmhwTnUwQXlVZDZGaUNoX19MUjhfZGRfRnBNVnhjS3lZNS12dFRVaXhvT0JMMy1ORHV2ZXhhUm9B?oc=5</t>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/el-bce-urge-a-profundizar-la-integracion-financiera-para-apoyar-la-prosperidad-de-europa/</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Google News - FMI</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>International Impact</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>Deuda récord: supera los USD 483.000 millones y crecen los vencimientos de corto plazo para Nación    NEA HOY</t>
-        </is>
-      </c>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Uno de los negociadores de la deuda con el FMI en 2021 advierte que con Milei hoy es menos pagable - Perfil</t>
+          <t>Australia celebra vigilias en todo el país por la niña aborigen asesinada</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOejUtLVEtb1pLSTM2VXgxUXJGSm1RMFRDenFjRnhhSVU2ajZPMFpvYjI0T2ZBQVBhZTQyZmc2dkY2X3RsNjdDQjI4dDB2V3ZTdVlvM3FqZG5ZYXBLbXBUS2NlOHMxZEpVOXJ4LXlRaUJveUN3NHBMWUJMdjdyRHVZTnhPY2ppbFZYYkp5MmZGZjkwelZRTFg0RmlmVXFIbmpaSXdhQnBoSG1LUVRvUmR3OXRzanF6QmdIUmxlSVVRdWV0aURhTHZuQTdNWFZLUXlOczc2S1FtTUZMcjFickhWQlVZVjFiMmFlVTZKeXFWN3Rpd9IB9wFBVV95cUxQa2M1ekpER0wzTEI3R2VkX1JmbThDWUI0aFdYVEhFVmpteXhXOExwZTNudW51ay1uN1Y4ajhMRnNtNGNoamFZUVZJblJmMGpuR09EWkVfSTJ2eHIxVzNwZDVJRTRRWHAtVnM2Y0pTLXI3SXA2MkUzOHVjakJJd1pLb2lmamVtMWdkajZsX0FwenhHMFlDRDVPN18xOExEbjZUVDV6Rlc3WW42Szk1eGt4X2lWTHJFZVk4bTBWYmZtVVI2WVBtOE9sZnQweTdQc2thZWFIRi1WLVhLcTdYQ1A1aXZyWWVfVHBZU3FyaXQyVjFKUTFuZDhJ?oc=5</t>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/australia-celebra-vigilias-en-todo-el-pais-por-la-nina-aborigen-asesinada/</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Google News - FMI</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>International Impact</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>Uno de los negociadores de la deuda con el FMI en 2021 advierte que con Milei hoy es menos pagable    Perfil</t>
-        </is>
-      </c>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>¿Cuánto endeudaron al Estado los últimos gobiernos y cuál es el saldo parcial de la gestión Milei? - Infobae</t>
+          <t>Ayuso cree que México está "a dos pasos" de ir por el camino de Venezuela y cuestiona el "recibimiento" de Sheinbaum</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNVFB0WTQ2ZG5RZ29lalVNNWwyS0NJdVljTzBSZ2F5MUFUT2tXLXF0ejhSVEJwVS1IWTlGT2Iza1RjYmxUR3daaVo0TXRkaFhuMWtkSjhLbDlNY3p5U2tfd2QtWFAxc0thOF9FYTZvQmQzYzZyWklpemw0SkREeXh6b3hDbGFUaXE5c3VDT2FadHZkbHZ6Z1puMUtNbzE2UzFjLVRkcGprb3R4cE13Z1hBajhNTnp1M09wcWgydGg3UFcxVXR6WEM1aW9XckI0VFlYdldUOFlGNEHSAfMBQVVfeXFMTmZ0LWdWTnJtc09OVWdHcTBRTW5heVJYTldjR3BoOExpZThHNlpUZXZQdXA5VU9nbWYzTlk2OVVzOFFRMk5UTUlTVXhmY2VXc09Wd0hOdnUtZUJQaWZpbnVZdXA2c3VxeW5ZU2I2ZjdkZGhJNUJobEt0RWktOG1VcWVDREoyaFdmTk1KTWlWdnhadVBnWXFxX3pKOFRBQy1Vd1RxYlEwMWZDM3NLNndUX1ZYcVZOaUpyMjFFY2g0UGd1WHFfZzFlbTU4dUkxZHNZVVEtdTNpNG5BQlNBMXV1SjgxMk10Q2cxZVpYdGM3NlJBdVhZ?oc=5</t>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/ayuso-cree-que-mexico-esta-a-dos-pasos-de-ir-por-el-camino-de-venezuela-y-cuestiona-el-recibimiento-de-sheinbaum/</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Google News - FMI</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>International Impact</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>¿Cuánto endeudaron al Estado los últimos gobiernos y cuál es el saldo parcial de la gestión Milei?    Infobae</t>
-        </is>
-      </c>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Qué claves mira Wall Street del programa económico de Milei: entusiasmo y una duda para 2027 - Infobae</t>
+          <t>La Comisión Anti-Violencia propone prohibir la entrada a ultras de Las Palmas y el Alcalá</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQZm1GaEoyTklZZDFxcVNPQldES0FkRXJ1U0RxUHEybUl5MWw2RzhOWVdCY0pYT0N0cGE2b3U1d2lXdnpmMDZFZUJzQ3pqUFRvMkwwRWhJU1VYdnJkOGs2U0ZYMHVoMkR4N0NqZlQ2UkpyTExDeFRhX3lQM0ZOUDJiSXFlQVVLWjJHQlRNMnJuTDJ5ZmJoZnhPSjllTm8xQzhPMG5JVFBoMlpXQU9WY1o3OU5UcUJrcVJWRWFXV3FrUXYyb2JMcHN3OEVFaHhYWXFsaEHSAewBQVVfeXFMTlFNSnctUlozeHIzazNiZE5PTVZ3R3BHdkNnNDh0RDE4eEJ0TURZZWoya2pjNk95cVpzMEljQUtRTWpfbHhEb0ZPdFVQbHRFRU5fSExiMjlGc29FRWdwal9sVTZBS0FVZExKdUdzZDhUWV9wMFIwTGM0cm5HVzExUUNTX00yQm5GTnR4Tk5ObEIwVXJNLTczY24taTc2Qnowa0VoMmo1YTBMbHVuUF9GaGo5Qk9hT0RKUnZidVUyVDktUC0tVS1TMS1xckgzZV9iMmRjdkdyX1FtSmpOWHFwYmVrRFpCZ1NPTjJ6UmE?oc=5</t>
+          <t>https://www.infobae.com/espana/agencias/2026/05/07/la-comision-anti-violencia-propone-prohibir-la-entrada-a-ultras-de-las-palmas-y-el-alcala/</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Google News - FMI</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>International Impact</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t>Qué claves mira Wall Street del programa económico de Milei: entusiasmo y una duda para 2027    Infobae</t>
-        </is>
-      </c>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Qué implica el próximo desembolso de USD 1.000 millones que llegará desde el FMI - Infobae</t>
+          <t>Resultados de la Triplex de la Once: sorteo 1 de las 10:00</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQTFAyeHQxeHRqSy1qX1BLNF9TcDNGeEl5T1N1bGxiV2FWd0U0a01wZWp0a1pmOW04Umw5Y05tcm1BNGJVeE5kMkFnWnVyRHNiVzlJRUtfOHFCVG15Yzd3d1IxNlJPM0FlUnBpUmhlRE5mdldmQXVpbGc5QXB1MWVTb3dTQnJxREFObHM3ZjAxS1JFUFFUcnkwT0FTak16SkdnMkJ4Z3ZETHJDRmczSU9hTmM3TFJGcENfRkJybEczS2PSAdsBQVVfeXFMTmdaeUdaQTZCNUpJNkRfTU14STN4S1NsbFpWS29zSTlsaExsUkE4alo3MDNfenNvUGhTR3hxQWU1X2Q4TW9XQzUtX0hxR2tVdzcxa3EtdF9kWXJTMnNOR21xS1dkRDVUUlZMbFd6b2NuVndCNkNXMDhoMWJLcFVCc21NdjZiXzBDYnRSeF9ScXZqXzdZXzR4ZmltUWxLV2VoeE5aWlVod1oxZEFrQWw0eUsxMlRKZFFKd0U1LVY4QnlXNF9HZ0dzUTl4RG1nYk9udWFiM0pHZnpJZFlz?oc=5</t>
+          <t>https://www.infobae.com/espana/2026/05/07/resultados-de-la-triplex-de-la-once-sorteo-1-de-las-1000/</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Google News - FMI</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>International Impact</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Qué implica el próximo desembolso de USD 1.000 millones que llegará desde el FMI    Infobae</t>
+          <t>Juegos Once anunció la combinación ganadora del Sorteo 1 de las 10:00 horas. Tenemos los números ganadores aquí mismo</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>«¿De qué nos sirvió?»: el furioso tuit de Vanesa Siley por la deuda de 70 mil millones con el FMI - El Intransigente</t>
+          <t>Charly, marido de Lydia Lozano, recibe el alta después de 12 días ingresado</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQbVhNQzV5eXhSdWdvRXZ1NnNzN3ZfSGFTQUtHY2pDZG5ISlV3OEdIVGYyTXJRN2dneVF5UmhOWmxVM1FvWVRIV3JEZkRpTGU4aW5tV2ZnTTVuTlltQkx3TnFNNFdiQTVCNDRBZnRIbjhlVGd0dTZhZ2tUT0I2cWN3U0c5TnNIT1B3VGlrRkQ4cHdtQ3NTbUVNcXN4aEVIbU91Y1pyYnpiOXI5aWlMOTVldEF2Q2dMY1ZuVlgxN1g5dnJHSnJhTEhDMg?oc=5</t>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/charly-marido-de-lydia-lozano-recibe-el-alta-despues-de-12-dias-ingresado/</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Google News - FMI</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>International Impact</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>«¿De qué nos sirvió?»: el furioso tuit de Vanesa Siley por la deuda de 70 mil millones con el FMI    El Intransigente</t>
-        </is>
-      </c>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Top Argentina official resigned after return to markets shelved - Buenos Aires Times</t>
+          <t>El Nikkei se dispara un 5,58 % y marca un nuevo récord gracias al optimismo sobre Irán</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOSmY3Zm02WTlSdEl2WTl3cEc4MXZyT3JFeFpzU2xhTHdRc2ItczFJaWliYkNJOU95NTd6RkNLeGNVbnZRN3ZEdG1Wc1pPVy0zcWw1bXdPZnZBTldnZGdMSlN2aDl4OEV4TUNRcWNIVGIwY0JvQnN5N2xkQlg0Yl83eXBIVS0wbEhXckxHQzZEUm1ESlB6M2Zpa21iQTB0Zms1TGItVThaNDBBb2FNeXfSAbMBQVVfeXFMTWw3TmJrcWNqcnhmbFU3VENPUzhDbjhmUUk2MXB1ekdWNDEyZHNiNzNRbk0yd2NYenVlNWFSZFRNaW90T3hweGtJYXFSYnV5S2tOSlRGa1lSSWUzWnpEcFBaWVQwY1Y5cGNpbU1qQ0I3c2tfNGQwY1hBcWRZRm03Zk16S2YtOTg3NUVUeVF0bl85dUV1WVJmXzFZOVN2X3I0bkxmcmxtOWxQdFlIMy0tWWRpcUE?oc=5</t>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/el-nikkei-se-dispara-un-558-y-marca-un-nuevo-record-gracias-al-optimismo-sobre-iran/</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Google News - Argentina EN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>International Impact</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>Top Argentina official resigned after return to markets shelved    Buenos Aires Times</t>
-        </is>
-      </c>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Argentina’s economy records sharpest monthly contraction under Javier Milei - Financial Times</t>
+          <t>Policía rechaza ataque en Ataco, Tolima tras incineración de vehículo en operativo contra minería ilegal</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPREc1NDM0ZVZyVEM0ODdORmtnV092cXpGQmtsMTB4UjVkTVZkd0NrZlVHalNzNDJwSFJCV19vOWFabTVLSGszVGtHZHlVVWMxd29BWDc3MnJlSEpiUy05elBUWFhuR0NTTGJvUFhnX1ZnWU5vaE5LVmhqMy1LUklyZVZhdks?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/05/07/policia-rechaza-ataque-en-ataco-tolima-tras-incineracion-de-vehiculo-en-operativo-contra-mineria-ilegal/</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Google News - Argentina EN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>International Impact</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Argentina’s economy records sharpest monthly contraction under Javier Milei    Financial Times</t>
+          <t>La institución informó que no se registraron uniformados lesionados durante los hechos y que se adelantan investigaciones para identificar a los responsables</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Argentina - Resources, Power, Economy - Britannica</t>
+          <t>El precio de la vivienda registra su mayor aumento desde 2006 con una subida del 15,4% en abril</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5OaWRwb2M3MHFRX2kzRERsVEhjRnJiNTFnRTBPdXVYSFplUlJ1UGJOWFJocWc1TWxlOU5XUU1Cb3VuSzJBN1lfVUIzanBMSnM3MGdBaEI5NFZwQ193YXI5MUNVR21pbW1SeEZLa1QyNA?oc=5</t>
+          <t>https://www.infobae.com/espana/2026/05/07/el-precio-de-la-vivienda-registra-su-mayor-aumento-desde-2006-con-una-subida-del-154-en-abril/</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Google News - Argentina EN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>International Impact</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Argentina - Resources, Power, Economy    Britannica</t>
+          <t>La tasadora Tinsa estima que el repunto inflacionario por la guerra en Irán ha empujado al alza el coste de los inmuebles nuevos y usados, que se acelera por encima del 20% en las islas y un 15% en grandes ciudades</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>Condenaron a una familia en Mar del Plata por el crimen de un hombre que fue asesinado delante de su hermana</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/sociedad/policiales/2026/05/07/condenaron-a-una-familia-en-mar-del-plata-por-el-crimen-de-un-hombre-que-fue-asesinado-delante-de-su-hermana/</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Walter Bravo murió en abril de 202. Para la Justicia, quedó probada la premeditación. Primero lo apuñalaron y luego le dispararon a quemarropa</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Clima en Washington D. C.: cuál será la temperatura máxima y mínima este 7 de mayo</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/noticias/2026/05/07/clima-en-washington-d-c-cual-sera-la-temperatura-maxima-y-minima-este-7-de-mayo/</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Los fenómenos meteorológicos y análisis de probabilidad permiten dar información sobre la temperatura, lluvias y vientos para las próximas horas</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Familiares de militares en Líbano trasladan a Robles su preocupación por la inseguridad</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/agencias/2026/05/07/familiares-de-militares-en-libano-trasladan-a-robles-su-preocupacion-por-la-inseguridad/</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Carla, la joven que perdió sus manos y pies por una sepsis: "Ahora disfruto y valoro más"</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/agencias/2026/05/07/carla-la-joven-que-perdio-sus-manos-y-pies-por-una-sepsis-ahora-disfruto-y-valoro-mas/</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Clima en Miami: pronóstico de lluvias y ráfagas de viento</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/noticias/2026/05/07/clima-en-miami-pronostico-de-lluvias-y-rafagas-de-viento/</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Para evitar cualquier imprevisto es importante conocer el pronóstico del tiempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Detenido un joven en Jerez de la Frontera por una agresión sexual en la vía pública</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/agencias/2026/05/07/detenido-un-joven-en-jerez-de-la-frontera-por-una-agresion-sexual-en-la-via-publica/</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Colombia: las predicciones del tiempo para Cartagena de Indias este 7 de mayo</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/colombia/2026/05/07/colombia-las-predicciones-del-tiempo-para-cartagena-de-indias-este-7-de-mayo/</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Las costas del Mar Caribe al Norte, la corriente del Océano Pacífico y las cordilleras que atraviesan de norte a sur, son las que definen el tipo de clima en Colombia</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>El koala tiene sed: Australia descubre cómo el calor extremo afecta al icono del país</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/el-koala-tiene-sed-australia-descubre-como-el-calor-extremo-afecta-al-icono-del-pais/</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Ayuso censura "descontrol" y "versiones diferentes" del Gobierno sobre pasajeros que llegarán al Gómez Ulla</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/agencias/2026/05/07/ayuso-censura-descontrol-y-versiones-diferentes-del-gobierno-sobre-pasajeros-que-llegaran-al-gomez-ulla/</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Adiós a la incertidumbre, conoce las condiciones climáticas en Cali</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/colombia/2026/05/07/adios-a-la-incertidumbre-conoce-las-condiciones-climaticas-en-cali/</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>El clima en Colombia se ve afectado debido a su complejidad geográfica como lo son las costas del Mar Caribe al Norte, la corriente del Océano Pacífico, así como las cordilleras que lo atraviesan por el centro de norte a sur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Muere civil en la región fronteriza rusa de Bélgorod tras ataque de dron ucraniano</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/muere-civil-en-la-region-fronteriza-rusa-de-belgorod-tras-ataque-de-dron-ucraniano/</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Investigado en Cantabria el conductor de un camión cisterna por quintuplicar la tasa de alcohol</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/investigado-en-cantabria-el-conductor-de-un-camion-cisterna-por-quintuplicar-la-tasa-de-alcohol/</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Clima en Colombia: el pronóstico del tiempo para Barranquilla este 7 de mayo</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/colombia/2026/05/07/clima-en-colombia-el-pronostico-del-tiempo-para-barranquilla-este-7-de-mayo/</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Las costas del Mar Caribe al Norte, la corriente del Océano Pacífico y las cordilleras que atraviesan de norte a sur, son las que definen el estado del tiempo en Colombia</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Termina la retirada de escombros tras el ataque en Beirut, aún sin balance de víctimas</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/termina-la-retirada-de-escombros-tras-el-ataque-en-beirut-aun-sin-balance-de-victimas/</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>La junta de accionistas de Acerinox aprueba el pago de un dividendo complementario de 0,31 euros</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/la-junta-de-accionistas-de-acerinox-aprueba-el-pago-de-un-dividendo-complementario-de-031-euros/</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Adiós a la incertidumbre, conoce las condiciones climáticas en Bogotá</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/colombia/2026/05/07/adios-a-la-incertidumbre-conoce-las-condiciones-climaticas-en-bogota/</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Las costas del Mar Caribe al Norte, la corriente del Océano Pacífico y las cordilleras que atraviesan de norte a sur, son las que definen el tipo de clima en el país</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>El Studio Ghibli confirma que ha recibido la noticia del Premio Princesa de Asturias</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/el-studio-ghibli-confirma-que-ha-recibido-la-noticia-del-premio-princesa-de-asturias/</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Cae una organización que dejó 500 víctimas de extorsión del sicario mediante anuncios de servicios sexuales</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/cae-una-organizacion-que-dejo-500-victimas-de-extorsion-del-sicario-mediante-anuncios-de-servicios-sexuales/</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>El hantavirus no es el nuevo Covid: investigadores explican por qué el brote del crucero “no supone un riesgo de pandemia ni epidemia”</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/2026/05/07/el-hantavirus-no-es-el-nuevo-covid-investigadores-explican-por-que-el-brote-del-crucero-no-supone-un-riesgo-de-pandemia-ni-epidemia/</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Expertos subrayan que el hantavirus no comparte las características de alta transmisibilidad del coronavirus, ni supone un riesgo poblacional similar</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Pronóstico del clima en Medellín este jueves 7 de mayo: temperatura, lluvias y viento</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/colombia/2026/05/07/pronostico-del-clima-en-medellin-este-jueves-7-de-mayo-temperatura-lluvias-y-viento/</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>El clima en Medellín cambia constantemente, por eso es importante mantenerse actualizado y estar preparado ante las adversidades atmosféricas de este día</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>La UE prohíbe la creación de imágenes sexualizadas generadas con IA</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/la-ue-prohibe-la-creacion-de-imagenes-sexualizadas-generadas-con-ia/</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Heridos cinco militares en un ataque achacado a las disidencias de las FARC en el departamento de Cauca</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/heridos-cinco-militares-en-un-ataque-achacado-a-las-disidencias-de-las-farc-en-el-departamento-de-cauca/</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Preguntas y respuestas sobre los fallecidos y los pacientes con hantavirus para evitar la confusión: ocho casos confirmados y sospechosos</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/2026/05/07/preguntas-y-respuestas-sobre-los-fallecidos-y-los-pacientes-con-hantavirus-para-evitar-la-confusion-ocho-casos-confirmados-y-sospechosos/</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>El crucero MV Hondius ya viaja hacia Canarias, tras la evacuación de tres personas que han sido trasladadas a Países Bajos</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Un tornado azotó a Las Flores, generó destrozos y gran parte de la ciudad quedó a oscuras</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/sociedad/2026/05/07/un-tornado-azoto-a-las-flores-genero-destrozos-y-gran-parte-de-la-ciudad-quedo-a-oscuras/</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Hasta el momento, no hay cifras oficiales de la cantidad de damnificados. Además, continúa activa la alerta naranja por tormentas en la zona</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Uno de los pasajeros del MV Hondius, el crucero con hantavirus, lamenta que la tripulación no se tomó “el problema lo suficientemente en serio”: “Era mucho peor de lo que dijeron”</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/2026/05/07/uno-de-los-pasajeros-del-mv-hondius-el-crucero-con-hantavirus-lamenta-que-la-tripulacion-no-se-tomo-el-problema-lo-suficientemente-en-serio-era-mucho-peor-de-lo-que-dijeron/</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Un brote de hantavirus a bordo del crucero ha dejado tres víctimas mortales y ha provocado el aislamiento de los pasajeros, que se encuentran ya camino de Canarias para ser atendidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Esto es lo que le pasa a tu cerebro si dejas de usar el móvil durante una semana, según un médico</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/2026/05/07/esto-es-lo-que-le-pasa-a-tu-cerebro-si-dejas-de-usar-el-movil-durante-una-semana-segun-un-medico/</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>La mente está acostumbrada a recibir estímulos constantes cada pocos segundos, lo que dificulta la adaptación al silencio y la falta de notificaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>El dron ruso Orion-E visto en ejercicios militares de Argelia en el norte de África</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/2026/05/07/el-dron-ruso-orion-e-visto-en-ejercicios-militares-de-argelia-en-el-norte-de-africa/</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>El 8 de abril, se desarrolló el ejercicio táctico con fuego real denominado “Huracán 2026” en In Guezzam, según ‘Mena Defense’</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Hacienda defiende la legalidad de usar créditos de fondos europeos para pagar pensiones</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/agencias/2026/05/07/hacienda-defiende-la-legalidad-de-usar-creditos-de-fondos-europeos-para-pagar-pensiones/</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>El precio de la vivienda sube al 15,4 % en abril, la tasa más alta desde octubre de 2006</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/agencias/2026/05/07/el-precio-de-la-vivienda-sube-al-154-en-abril-la-tasa-mas-alta-desde-octubre-de-2006/</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>La jueza autoriza el entierro del niño de 4 años asesinado en Garrucha (Almería)</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/agencias/2026/05/07/la-jueza-autoriza-el-entierro-del-nino-de-4-anos-asesinado-en-garrucha-almeria/</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Llega a Países Bajos el tercer evacuado desde el crucero con hantavirus</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/llega-a-paises-bajos-el-tercer-evacuado-desde-el-crucero-con-hantavirus/</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Al menos 3 muertos y más de 400 arrestos en ola de violencia poselectoral en Calcuta</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/al-menos-3-muertos-y-mas-de-400-arrestos-en-ola-de-violencia-poselectoral-en-calcuta/</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Taiwán completa la primera prueba de torpedos de su submarino de fabricación local</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/taiwan-completa-la-primera-prueba-de-torpedos-de-su-submarino-de-fabricacion-local/</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Marruecos despliega "importantes medios" para hallar a dos soldados de EEUU desaparecidos en unas maniobras</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/marruecos-despliega-importantes-medios-para-hallar-a-dos-soldados-de-eeuu-desaparecidos-en-unas-maniobras/</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>La familia de Julio César lo buscó por años, pero su cuerpo había sido donado al IPN: hoy la FGJCDMX les pidió perdón</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/mexico/2026/05/07/la-familia-de-julio-cesar-lo-busco-por-anos-pero-su-cuerpo-habia-sido-donado-al-ipn-hoy-la-fgjcdmx-les-pidio-perdon/</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>Aunque su cuerpo fue localizado por las autoridades, la familia no fue informada y continuó buscándolo por meses hasta encontrarlo en la Facultad de Medicina</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Rusia anuncia un apagón total de internet móvil en Moscú para el 9 de mayo</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/rusia-anuncia-un-apagon-total-de-internet-movil-en-moscu-para-el-9-de-mayo/</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>El Ibex 35 sube un 0,2% en la apertura y mantiene los 18.100 puntos, con el petróleo en 100 dólares</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/el-ibex-35-sube-un-02-en-la-apertura-y-mantiene-los-18100-puntos-con-el-petroleo-en-100-dolares/</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>El presidente de RDC alerta sobre un posible retraso electoral por el conflicto en el este</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/el-presidente-de-rdc-alerta-sobre-un-posible-retraso-electoral-por-el-conflicto-en-el-este/</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Nuevo récord de población en España, con 49.687.120 habitantes en el primer trimestre de 2026, gracias a los extranjeros</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/nuevo-record-de-poblacion-en-espana-con-49687120-habitantes-en-el-primer-trimestre-de-2026-gracias-a-los-extranjeros/</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>El parlamento de Baréin expulsa a 3 diputados tras oponerse a revocación de nacionalidad</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/el-parlamento-de-barein-expulsa-a-3-diputados-tras-oponerse-a-revocacion-de-nacionalidad/</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Mar Flores reflexiona sobre el salto a la fama de Julia Janeiro: "Una vez que lo haces no puedes dar marcha atrás"</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/mar-flores-reflexiona-sobre-el-salto-a-la-fama-de-julia-janeiro-una-vez-que-lo-haces-no-puedes-dar-marcha-atras/</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Dos drones procedentes de Rusia entraron en Letonia y se reportaron dos accidentes</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/dos-drones-procedentes-de-rusia-entraron-en-letonia-y-se-reportaron-dos-accidentes/</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Vingegaard debuta en el Giro con el cartel de favorito</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/agencias/2026/05/07/vingegaard-debuta-en-el-giro-con-el-cartel-de-favorito/</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Desarticularon una banda narco cultivaba su marihuana en un campo de La Rioja</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/sociedad/policiales/2026/05/07/desarticularon-una-banda-narco-cultivaba-su-marihuana-en-un-campo-de-la-rioja/</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Un operativo encabezado por la Policía Federal permitió el secuestro de más de siete kilos de marihuana, 170 plantas, 21 armas de fuego y tres vehículos en un predio rural de Aguadita de Vargas. Cuatro personas quedaron detenidas</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Torre Mohamed VI, el nuevo techo de Marruecos, es obra de un arquitecto español: un cohete de 55 plantas con las mejores vistas de Rabat</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/2026/05/04/torre-mohamed-vi-el-nuevo-techo-de-marruecos-es-obra-de-un-arquitecto-espanol-un-cohete-de-55-plantas-con-las-mejores-vistas-de-rabat/</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>El príncipe heredero inaugura el edificio, con oficinas, apartamentos, hotel y hasta una galería de arte. Su construcción ha llevado ocho años</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Gran Estadio Hassan II, la monstruosa joya para 115.000 espectadores con la que Marruecos amenaza al Bernabéu: “Gradas empinadas y compactas para un ambiente espectacular”</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/deportes/2026/05/07/gran-estadio-hassan-ii-la-monstruosa-joya-para-115000-espectadores-con-la-que-marruecos-amenaza-al-bernabeu-gradas-empinadas-y-compactas-para-un-ambiente-espectacular/</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Marruecos quiere que la final del Mundial de 2030 se celebre en Casablanca, donde levanta un puntero complejo deportivo inspirado por la tradición</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Guille Galván expone su voz al margen de Vetusta Morla:"¿Quién soy yo si todo desaparece?"</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/agencias/2026/05/07/guille-galvan-expone-su-voz-al-margen-de-vetusta-morlaquien-soy-yo-si-todo-desaparece/</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Mensajes tras el cartel electoral: del presidencialismo de Moreno a la sanidad de Montero</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/agencias/2026/05/07/mensajes-tras-el-cartel-electoral-del-presidencialismo-de-moreno-a-la-sanidad-de-montero/</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>El andalucismo impregna el mensaje de los partidos en las elecciones del 17M</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/agencias/2026/05/07/el-andalucismo-impregna-el-mensaje-de-los-partidos-en-las-elecciones-del-17m/</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>El Supremo estudia el 13 de mayo si paraliza la regularización de inmigrantes</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/agencias/2026/05/07/el-supremo-estudia-el-13-de-mayo-si-paraliza-la-regularizacion-de-inmigrantes/</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>La Guardia Civil se une a un programa para combatir la soledad no deseada</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/agencias/2026/05/07/la-guardia-civil-se-une-a-un-programa-para-combatir-la-soledad-no-deseada/</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Dos personas que estuvieron en el crucero MV Hondius se autoaíslan en el Reino Unido</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/dos-personas-que-estuvieron-en-el-crucero-mv-hondius-se-autoaislan-en-el-reino-unido/</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>El festival Womad comienza este jueves en Cáceres con ritmos extremeños, brasileños y soul palestino</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/el-festival-womad-comienza-este-jueves-en-caceres-con-ritmos-extremenos-brasilenos-y-soul-palestino/</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Interpol incauta medicamentos ilegales por valor de 15,5 millones de dólares en 90 países</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/interpol-incauta-medicamentos-ilegales-por-valor-de-155-millones-de-dolares-en-90-paises/</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>La aerolínea Plus Ultra suspenderá los vuelos a Colombia a partir de junio por el aumento del precio del combustible</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/la-aerolinea-plus-ultra-suspendera-los-vuelos-a-colombia-a-partir-de-junio-por-el-aumento-del-precio-del-combustible/</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>El 30 % de sursudaneses consumen drogas, otro problema en aumento para un país en crisis</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/el-30-de-sursudaneses-consumen-drogas-otro-problema-en-aumento-para-un-pais-en-crisis/</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Muere una mujer en un ataque con drones de Ucrania contra la región rusa de Bélgorod</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/muere-una-mujer-en-un-ataque-con-drones-de-ucrania-contra-la-region-rusa-de-belgorod/</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Israel mata en Gaza a otro hijo del líder negociador de Hamás, Jalil al Haya</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/israel-mata-en-gaza-a-otro-hijo-del-lider-negociador-de-hamas-jalil-al-haya/</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>El Tesoro espera colocar este jueves hasta 6.750 millones en bonos y obligaciones del Estado</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/el-tesoro-espera-colocar-este-jueves-hasta-6750-millones-en-bonos-y-obligaciones-del-estado/</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>El abuelo del nene raptado por su padre relató el calvario que vivió su nieto: “Estuvo al borde de la muerte”</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/sociedad/2026/05/07/el-abuelo-del-nene-raptado-por-su-padre-relato-el-calvario-que-vivio-su-nieto-estuvo-al-borde-de-la-muerte/</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>El menor estuvo 48 horas junto a su padre. Frente a su desaparición, la provincia de Corrientes activó una Alerta Sofía para dar con su paradero</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Lilly Téllez responde a Noroña por exhibirla en sala VIP del AICM: “No soy corrupta y estoy limpia”</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/mexico/2026/05/07/lilly-tellez-responde-a-norona-por-exhibirla-en-sala-vip-del-aicm-no-soy-corrupta-y-estoy-limpia/</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>La disputa entre ambos políticos volvió a encender las redes sociales tras un video grabado</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Hacia la regeneración de extremidades: un estudio logra crear hueso, tendones y ligamentos</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/2026/05/07/hacia-la-regeneracion-de-extremidades-un-estudio-logra-crear-hueso-tendones-y-ligamentos/</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>El estudio experimental estadounidense considera que el proceso de curación del cuerpo podría ocultar su capacidad de regenerarse</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Meghan Markle revela dos fotos inéditas de sus hijos por el séptimo cumpleaños de Archie: “Felicidades a nuestro dulce niño”</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/2026/05/07/meghan-markle-revela-dos-fotos-ineditas-de-sus-hijos-por-el-septimo-cumpleanos-de-archie-felicidades-a-nuestro-dulce-nino/</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>La actriz ha sacado a la luz en su cuenta de Instagram una fotografía nunca antes vista del príncipe Harry junto a su hijo recién nacido</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Teletrabajo en Colombia: Consejo de Estado mantiene auxilio por uso de equipos del trabajador</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/colombia/2026/05/07/teletrabajo-en-colombia-consejo-de-estado-mantiene-auxilio-por-uso-de-equipos-del-trabajador/</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>El alto tribunal avaló que empleadores y trabajadores pacten compensaciones por el uso de herramientas y servicios personales en el trabajo remoto, estableciendo que estos acuerdos no vulneran la ley y permiten mayor flexibilidad en la implementación de esta modalidad laboral</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Hacer de tu casa un negocio: hasta 5.000 euros por alquilar tu piscina en un verano que se espera de calor extremo</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/2026/05/07/hacer-de-tu-casa-un-negocio-hasta-5000-euros-por-alquilar-tu-piscina-en-un-verano-que-se-espera-de-calor-extremo/</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>Con más de 1,3 millones de piscinas privadas y escasas opciones públicas en la mayoría de grandes ciudades, algunas plataformas aprovechan la demanda para monetizar por horas el ocio</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>La Corte intimó al máximo tribunal de Santa Cruz a entregar el expediente sobre la designación de nuevos jueces</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/politica/2026/05/07/la-corte-intimo-al-maximo-tribunal-de-santa-cruz-a-entregar-el-expediente-sobre-la-designacion-de-nuevos-jueces/</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>justicia</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>España inicia más viviendas, pero termina un 14,5% menos: el ‘boom’ de la construcción aún no llega al mercado</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/2026/05/07/espana-inicia-mas-viviendas-pero-termina-un-145-menos-el-boom-de-la-construccion-aun-no-llega-al-mercado/</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>La segunda mano concentra el 90% de las compraventas mientras las nuevas promociones tardan en llegar a compradores e inquilinos</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Los expertos fijan el decálogo de deberes digitales para plataformas y administraciones</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/agencias/2026/05/07/los-expertos-fijan-el-decalogo-de-deberes-digitales-para-plataformas-y-administraciones/</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Las denuncias contra el club de rugby de Bizkaia por el impago de lotería suman ya 80</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/agencias/2026/05/07/las-denuncias-contra-el-club-de-rugby-de-bizkaia-por-el-impago-de-loteria-suman-ya-80/</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Jueves, 7 de mayo de 2026 (07.00 GMT)</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/jueves-7-de-mayo-de-2026-0700-gmt/</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>China sitúa Taiwán como clave para buena relación con EE. UU. antes de la visita de Trump</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/china-situa-taiwan-como-clave-para-buena-relacion-con-ee-uu-antes-de-la-visita-de-trump/</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Mónica García y Torres mantienen una reunión hoy con Clavijo tras sus críticas por falta de información</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/agencias/2026/05/07/monica-garcia-y-torres-mantienen-una-reunion-hoy-con-clavijo-tras-sus-criticas-por-falta-de-informacion/</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Dos pacientes de hantavirus abandonan la isla española de Gran Canaria en un segundo avión</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/dos-pacientes-de-hantavirus-abandonan-la-isla-espanola-de-gran-canaria-en-un-segundo-avion/</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Reental supera los 85 millones de euros de inversión tokenizada en el primer trimestre de 2026</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/reental-supera-los-85-millones-de-euros-de-inversion-tokenizada-en-el-primer-trimestre-de-2026/</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Israel lanzó un nuevo ataque contra cuarteles generales, almacenes y sitios estratégicos de Hezbollah en Líbano</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/mundo/2026/05/07/israel-lanzo-un-nuevo-ataque-contra-cuarteles-generales-almacenes-y-sitios-estrategicos-de-hezbollah-en-libano/</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>El Ejército israelí llevó adelante una nueva ofensiva militar para contrarrestar las hostilidades del grupo terrorista en el sur libanés. Hasta el momento, se desconoce el número de combatientes abatidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Studio Ghibli confirma que ha recibido la noticia del Premio Princesa de Asturias</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/studio-ghibli-confirma-que-ha-recibido-la-noticia-del-premio-princesa-de-asturias/</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Chema Martínez, premio Espiga del Deporte 2026: "Tengo casi 55 años y corro cada día, es mi mejor alimento"</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/chema-martinez-premio-espiga-del-deporte-2026-tengo-casi-55-anos-y-corro-cada-dia-es-mi-mejor-alimento/</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Disturbios en París tras la clasificación del PSG para la final: 127 detenidos, 11 heridos</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/agencias/2026/05/07/disturbios-en-paris-tras-la-clasificacion-del-psg-para-la-final-127-detenidos-11-heridos/</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>Aitana Sánchez-Gijón reaparece públicamente tras la muerte de su madre, y guarda silencio sobre Maxi Iglesias</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2026/05/07/aitana-sanchez-gijon-reaparece-publicamente-tras-la-muerte-de-su-madre-y-guarda-silencio-sobre-maxi-iglesias/</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Pablo Torre: "Es el año que más estoy disfrutando"</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/espana/agencias/2026/05/07/pablo-torre-es-el-ano-que-mas-estoy-disfrutando/</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>Majo Aguilar responde a rumores de envidia y aclara comentarios sobre su prima Ángela Aguilar</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/mexico/2026/05/07/majo-aguilar-responde-a-rumores-de-envidia-y-aclara-comentarios-sobre-su-prima-angela-aguilar/</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>Un clip resurgido en redes sociales volvió a encender los rumores de enemistad entre las cantantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Rally de acciones y bonos: los ADRs treparon hasta 11% y el riesgo país se hundió 7% tras la mejora de la nota soberana - Ambito</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNa0ZYU3UtNUU3SDY3RUE1NEFIMF85R0xpM2FGMnNreVpEd0xGRi1nOG5PNnZpTmpSQ2hKZ0QzZEd4bkItV3pKRGk3OHptc3B6MWExejRBV3djRkZPMEw5ZDVLVEdaT3hEUjBkS3p5YjNUWjNRQVpjaFZ3OFVpdEcwM19RUDBVSWRTcFVNdXhWamNnSktCOXl3MkwxQ1RqS0xNZUowZDBKalVTUlN2Y2pDMWpZTVhJUEFiaFU40gHAAUFVX3lxTE5PSF85OE02RW9vT053a3VZMnRGcG8wSTBKTEVhblI3REU4UkNHVGpiNVhGOVlaYV94dE1kRXpZTzFUTVB4NEhHNVJHYm9MeWZ0VEtHd3p0b1ZzNXV6V19qZ19sZ19BRWdqX1FwZEQ4RHFFaXRXS3kwTW8wcFBxTWkzV3hQenZ4YXM5TnlJRlJXQ2tkMk1yYXpSUlZ2a212U1RrNEJQdnNUeUtNWkZoYnBwVXFfTUE0LXhtSkF4Q3E4RQ?oc=5</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>Google News - Mercados</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>Rally de acciones y bonos: los ADRs treparon hasta 11% y el riesgo país se hundió 7% tras la mejora de la nota soberana    Ambito</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Una calificadora de riesgo de Estados Unidos elevó la nota de deuda soberana de la Argentina - Infobae</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQUC1pOUdHX0ppNkFzZ28ycWN4ZnI2c09HQ3hRMHdqZDBHSFNZaV9IbUt4R1hWal9UME1DX3FQNlBWRDYtQ0FkTjd5X1N2SjVTM3JjRUNQZ3Vtb3gyRTJnenduQjcxbldQdjFXNS11VjBnejBMRy1jN2xJbUFwdmNmMFg2bXhWUU1kRFdHYktHYWlkR3N6dGRSZjBUbjBxQl9oc3RXT0JRUzUwUmM1U0NSMWFVaTVfMzM1V01RbkY0NThqVU1Qb0hyNG5IY0hEMVA3bHpF0gHuAUFVX3lxTE4wSWZuemtEVFJDM2dMNUVrajg2R0FPQzdaMk80aElvRXpxaktnNmtrRVZPMEhYMXBkWTRJcGhySEFmLTJFVEFkZnU2SllFVFA3VTlSUHZlWGFVNzVzTEVlTWJ1ck9aQ3ZwQy1EcFItekFhMUp0ck1MRVVZN0hIdkd1d000NmdQT1dIRW9QZ0MxeU8xZTVNN3BjZXZ0TG9WN0tLamZWSkJUTDN5N01KNnFQY2FhTzE5QVd1MXZmVG5NT2p6bU0ySzhYVllLbjVoRmtKa3hGbnBRZFY0V2txU2h4QmxIZ0NmVU9xZnd1ZFE?oc=5</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>Google News - FMI</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>International Impact</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>Una calificadora de riesgo de Estados Unidos elevó la nota de deuda soberana de la Argentina    Infobae</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Argentina recurrió a Estados Unidos para afrontar vencimientos con el FMI - Nueva Rioja</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNNmpoc19CODNGc2pPSTBta0JRWjN2ZXB4RWVBc3RGWDBUZUtWOEZfYVpXMXotV3NUeUE1Q2FOb0FuX3JKckZWR1pncmxSZzhCWTg5QTkwV2lhMTBNOFJ1cFNDSFdfaVdLcVpHTzh3RDZrRFZNRlllTm8xT2Ytd3NWSzdBazl1LUlLd3lvLU5VTDhjN0JneWt0VUJyTHNBN1FCMk84eXBrVUNfSXdBcXRlaE9B?oc=5</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>Google News - FMI</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>International Impact</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>Argentina recurrió a Estados Unidos para afrontar vencimientos con el FMI    Nueva Rioja</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>Exdirector del FMI ve acceso al mercado como llave para resolver la deuda argentina con el organismo - Bloomberg Línea</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxOeXRqcVlXUm9pelRfRTc5WXN4eEhSa3RmLUhYZTRJODdOTHhYVmM3OUxkaFRpaGxlV0dqdG5PUTFNbVFNdmN1RlJzUVFTUmc0ZVZUbFBkdklSZUQydm1WQUlyV1VJbVJyWEtXczRDdnpHcllHMTNHNllzSnJlbEpzRVU4b0xtMkpRS0laYkczRll0bTdYOHVwcFpLcUV5SDM1elAxX2tTQ3FqUm5Eb0dmUDlWTnpFNnJFRVV3TV9RdFNkcS1vMjEwU0pRWFZHbnNoek9xcTZWYldzX09Wdk1xUGhNeVM3bm1ZZjBybdIBgAJBVV95cUxOdllkZzdGeERqMktHNnRUTGdoSUxreEFZUWhZSkZtZ3lIVW96RzJORWM3aks3Z3JDNURSS0FzTVVCQWs4VVgzcEZENFZpcE1YT1ZtQXJURURWeFIxeEcyU3NkOVRONTVXdUJaRUtObi1YOUpKNXZMRGJGcTB1ZGU5WW1aQVRPU1I2emFzb3ZpMFdfbDRKR2NNdG9VaDMtSnZrVTgycFIwczlQdHZtdkdTMnZJQjJDWmtlQm5DZFdwZkRYZWx2T0VhQ0lpd3JRM0d5Nm5XM1RwVU1QNzRoTUFJbXRvd3JKX1poWDlTcWJPTTBIWkkxdlhGT1Y1T1ZFbVc2?oc=5</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>Google News - FMI</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>International Impact</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>Exdirector del FMI ve acceso al mercado como llave para resolver la deuda argentina con el organismo    Bloomberg Línea</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>La deuda externa más alta de la historia: cuánto endeudaron al Estado los últimos gobiernos - Enterate Noticias</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNNVF4UFVaY3AxdEphcWRsZldPbElSUW14b0haYVBzWjR3eGVTM3B6REdHN0pvOW5hZEJ2M00ySDdMZF9vVW9VOWpvY2VUcTJWMnl5YVpoN1pGSm50VEd0YXc3bUJvbmpYQ0E0ZTBiNksyWnByNHA3Y1dQdkkwODRzUGpsOEFtd29NQW9HMFU0QmQxOXdBNm1Rb1lTTTRtdkN3allTcC1fQ1FwWGVaTi1STnoyUzRKcFB2ZUp6VzlRUdIBuAFBVV95cUxQMVh5RWNDak5fTmYzUi16dGxXQnVERVJYQnNpSTMyNU1HUUlGcXBoQ0JYWGxFY1dJX3lYNTdacU9rQXpIV2E5dkN5UWZxMEJIal92UFBNaHRLeU55QVBSaGFLMUpYUnFMcGZJOFE3R3I1cHBLUnF2d0VaWW5GUFdSeVU3a2hyMmRYVWJUS2xUcXhtVmZRd0dyTUd6cjdGWkNIUXpwT0pORDZIOXg2UnBGQllBcnYxenJr?oc=5</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>Google News - FMI</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>International Impact</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>La deuda externa más alta de la historia: cuánto endeudaron al Estado los últimos gobiernos    Enterate Noticias</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>¿Cuánto endeudaron al Estado los últimos gobiernos y cuál es el saldo parcial de la gestión Milei? - Infobae</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNVFB0WTQ2ZG5RZ29lalVNNWwyS0NJdVljTzBSZ2F5MUFUT2tXLXF0ejhSVEJwVS1IWTlGT2Iza1RjYmxUR3daaVo0TXRkaFhuMWtkSjhLbDlNY3p5U2tfd2QtWFAxc0thOF9FYTZvQmQzYzZyWklpemw0SkREeXh6b3hDbGFUaXE5c3VDT2FadHZkbHZ6Z1puMUtNbzE2UzFjLVRkcGprb3R4cE13Z1hBajhNTnp1M09wcWgydGg3UFcxVXR6WEM1aW9XckI0VFlYdldUOFlGNEHSAfMBQVVfeXFMTmZ0LWdWTnJtc09OVWdHcTBRTW5heVJYTldjR3BoOExpZThHNlpUZXZQdXA5VU9nbWYzTlk2OVVzOFFRMk5UTUlTVXhmY2VXc09Wd0hOdnUtZUJQaWZpbnVZdXA2c3VxeW5ZU2I2ZjdkZGhJNUJobEt0RWktOG1VcWVDREoyaFdmTk1KTWlWdnhadVBnWXFxX3pKOFRBQy1Vd1RxYlEwMWZDM3NLNndUX1ZYcVZOaUpyMjFFY2g0UGd1WHFfZzFlbTU4dUkxZHNZVVEtdTNpNG5BQlNBMXV1SjgxMk10Q2cxZVpYdGM3NlJBdVhZ?oc=5</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>Google News - FMI</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>International Impact</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>¿Cuánto endeudaron al Estado los últimos gobiernos y cuál es el saldo parcial de la gestión Milei?    Infobae</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>La Argentina le compró DEG a Estados Unidos por US$819 millones para pagarle intereses al FMI - La Nación</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPUHQ2SDRDSnJLdzZfUGR2RjhidU42QWtHX1FZV2pDaDBIWVFkQ05SV3hYSUhnbDJEeHdicVlkWjgxVEU1b0xaZzY0c0UzQjc0cktVVEE4ZDkwSFZkc3d3MERyY3FIOU1NMnFqcTVYcHB1c0Zkd0F0NWNMQkNhZUZFU0hqd2dteFQ2NEVJVmZyX04yM1JFUjlNT1ZjdXB3T1JXTHluY0EtWnRrQXdUUzRkTWMteTRZdENXLUx5NDgtM2NIck5QT25wQ2RoRFJVYWZVcjdNaVEtWExyZw?oc=5</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>Google News - FMI</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>International Impact</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>La Argentina le compró DEG a Estados Unidos por US$819 millones para pagarle intereses al FMI    La Nación</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Argentina recibirá nuevo desembolso del FMI por USD 1.000 millones: implicancias para el Banco Central y la deuda - MisionesOnline</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1hNE12OUpYRGg3Yk9Rc2VfMDB5SW1JcVV5bFc2aVNfMEhuNDFsellyTmNRd0ktMDkzbEFyd3pvLXBpR3h4NkNRdlFqZWpmcVVyYlNpTm53WnpxOGx0U0RYbjZIbkdPTXc0WFdZc3djdGxjY1FoRmhZVldQZ3E2dw?oc=5</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>Google News - FMI</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>International Impact</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>Argentina recibirá nuevo desembolso del FMI por USD 1.000 millones: implicancias para el Banco Central y la deuda    MisionesOnline</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Deuda: el Gobierno volvió a comprarle DEGs a EEUU y le pagó u$s800 millones al FMI - Ambito</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPX01IRnBJTllEY2RRZlBQYkJMMjRlMFdLcVU5cGFJdTY3WkZaVjNOTVRfNmwxTkpNZHdxWnBpYmJRQzFvWkRyU1hkYk1XRjJ5eWxEZkFSSGFVcnhta0VqeU9nVGRCTTkzODJkcmY1ZEJaekNrWnZXcXhZSHpFVlJJYTdzRWdfcEUtZ0lGWFVFTHI1MzVwalROTGNKcW52QlZibzlsRdIBqgFBVV95cUxOcERfdkJYZS1iOE16TWpjQWZBTkZCekI3N3owR1R5eE9EMlFFcmRUb1pXZUpRWVJHME9VR3FYRThOSXhyTkVsWXdnb2o2S0hjUGRKRXRtelN5Z0pqekJJYlQwN19hMFFvU1VlVk02LVhVVmdxeGRSb3pEaW01SkpNeWs1VERTdVBjQ2JkcnNjYnM4dWMwLXhKeURZNWRLdjJ6RnBXTkRDSjIxdw?oc=5</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>Google News - FMI</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>International Impact</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>Deuda: el Gobierno volvió a comprarle DEGs a EEUU y le pagó u$s800 millones al FMI    Ambito</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Uno de los negociadores de la deuda con el FMI en 2021 advierte que con Milei hoy es menos pagable - Perfil</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOejUtLVEtb1pLSTM2VXgxUXJGSm1RMFRDenFjRnhhSVU2ajZPMFpvYjI0T2ZBQVBhZTQyZmc2dkY2X3RsNjdDQjI4dDB2V3ZTdVlvM3FqZG5ZYXBLbXBUS2NlOHMxZEpVOXJ4LXlRaUJveUN3NHBMWUJMdjdyRHVZTnhPY2ppbFZYYkp5MmZGZjkwelZRTFg0RmlmVXFIbmpaSXdhQnBoSG1LUVRvUmR3OXRzanF6QmdIUmxlSVVRdWV0aURhTHZuQTdNWFZLUXlOczc2S1FtTUZMcjFickhWQlVZVjFiMmFlVTZKeXFWN3Rpd9IB9wFBVV95cUxQa2M1ekpER0wzTEI3R2VkX1JmbThDWUI0aFdYVEhFVmpteXhXOExwZTNudW51ay1uN1Y4ajhMRnNtNGNoamFZUVZJblJmMGpuR09EWkVfSTJ2eHIxVzNwZDVJRTRRWHAtVnM2Y0pTLXI3SXA2MkUzOHVjakJJd1pLb2lmamVtMWdkajZsX0FwenhHMFlDRDVPN18xOExEbjZUVDV6Rlc3WW42Szk1eGt4X2lWTHJFZVk4bTBWYmZtVVI2WVBtOE9sZnQweTdQc2thZWFIRi1WLVhLcTdYQ1A1aXZyWWVfVHBZU3FyaXQyVjFKUTFuZDhJ?oc=5</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>Google News - FMI</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>International Impact</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>Uno de los negociadores de la deuda con el FMI en 2021 advierte que con Milei hoy es menos pagable    Perfil</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Deuda récord: supera los USD 483.000 millones y crecen los vencimientos de corto plazo para Nación - NEA HOY</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNMWl4TkFWdUsxeEN5eUJ4R2RwSDVSaTNLbGYybTA3WDROb29GZkU5QVo4VVczWVg4eFktdlg4SlZXbnpuX1doWHFnbEt6eHg2ZG9ZVEZiTjdKUjBSdElwXzRhVzJNellqQy1aaGRTN2pab0FQRGtmYVpmVHNoMjMwc3N5THV2RGxrbUozZ0hqRmhwTnUwQXlVZDZGaUNoX19MUjhfZGRfRnBNVnhjS3lZNS12dFRVaXhvT0JMMy1ORHV2ZXhhUm9B?oc=5</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>Google News - FMI</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>International Impact</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>Deuda récord: supera los USD 483.000 millones y crecen los vencimientos de corto plazo para Nación    NEA HOY</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Argentina’s Javier Milei battered by scandals and slowing economy - Financial Times</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOLVlHVUJrTVQ4MFNhYWNsMHBDdWR3dHdWdDBnMHowdUdqS0wzRXoxUmIyQVlBOHYyTzF4LV9XNVVOcTE2V3J4TjZfSHI0TGgtalh4VG8tOGZNa3lYM3lyd1J0NXF3alFfaWY2OEtsNmpCZFBJQU9PNzhhYW1oWFpYamo3YVk?oc=5</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>Google News - Argentina EN</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>International Impact</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>Argentina’s Javier Milei battered by scandals and slowing economy    Financial Times</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
           <t>Tether leads $14M Series A in Argentine crypto fintech belo to scale stablecoins across LatAm - Tech Funding News</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B228" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQMWFFUjl1bmZpczFnU3dpUXQwckpsZWFmRFR5RkFVR2RxTmlrWjZVX2NIWFA0M1lUSnF0QWVRLXl1Zm5KUktOVXhib19LalgwUEdtdjRSR29xZVpHblg0ZW9YX2IwSEZCZXpfVUlaWkJWUmFJZGdNRXJkbnhSOURVSWJn?oc=5</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
+      <c r="C228" s="2" t="inlineStr">
         <is>
           <t>Google News - LatAm Fintech</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>Fintech &amp; Innovation</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>Tether leads $14M Series A in Argentine crypto fintech belo to scale stablecoins across LatAm    Tech Funding News</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Euro hoy y Euro blue hoy: a cuánto cotiza este jueves 7 de mayo</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ambito.com/finanzas/euro-hoy-y-euro-blue-hoy-cuanto-cotiza-este-jueves-7-mayo-n6274797</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>Ambito - Finanzas</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>Mirá a cuánto cotizan el euro oficial y el euro blue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Real blue: a cuánto opera este jueves 7 de mayo</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ambito.com/finanzas/real-blue-cuanto-opera-este-jueves-7-mayo-n6274800</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>Ambito - Finanzas</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>La cotización minuto a minuto para la compra y venta de la divisa brasileña en nuestro país.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>Rally de acciones y bonos: los ADRs treparon hasta 11% y el riesgo país se hundió 7% tras la mejora de la nota soberana</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ambito.com/finanzas/los-bonos-dolares-rebotan-fuerza-impulsados-el-optimismo-los-mercados-globales-n6274482</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>Ambito - Finanzas</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>Los bonos soberanos en dólares rebotaron con fuerza en la jornada, liderados por los Globales de mayor plazo, luego de que la deuda argentina recibiera una mejora de calificación. En Wall Street, los bancos encabezaron las subas, mientras que las energéticas retrocedieron por la baja del petróleo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Real blue: a cuánto operó este miércoles 6 de mayo</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ambito.com/finanzas/real-blue-cuanto-opero-este-miercoles-6-mayo-n6274339</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>Ambito - Finanzas</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>La cotización minuto a minuto para la compra y venta de la divisa brasileña en nuestro país.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Euro hoy y Euro blue hoy: a cuánto cotizó este miércoles 6 de mayo</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ambito.com/finanzas/euro-hoy-y-euro-blue-hoy-cuanto-cotiza-este-miercoles-6-mayo-n6274337</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>Ambito - Finanzas</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>Mirá a cuánto cotizan el euro oficial y el euro blue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>El dólar blue retrocedió y tocó mínimos de casi un mes</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ambito.com/finanzas/el-dolar-blue-retrocedio-y-toco-minimos-casi-un-mes-n6274751</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>Ambito - Finanzas</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>El billete paralelo bajó $15 y dejó atrás la suba mensual acumulada. La brecha con el tipo de cambio oficial descendió a menos de 1%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>Dólar hoy y dólar blue hoy minuto a minuto: a cuánto opera este miércoles 6 de mayo</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ambito.com/finanzas/dolar-hoy-y-dolar-blue-hoy-minuto-minuto-cuanto-opera-este-miercoles-6-mayo-n6274397</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>Ambito - Finanzas</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>Dólar blue hoy: a cuánto cerró este miércoles 6 de mayo</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ambito.com/finanzas/dolar-blue-hoy-cuanto-cerro-este-miercoles-6-mayo-n6274703</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>Ambito - Finanzas</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>Dólar hoy: a cuánto cerró este miércoles 6 de mayo</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ambito.com/finanzas/dolar-hoy-cuanto-cerro-este-miercoles-6-mayo-n6274702</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>Ambito - Finanzas</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>Dólar hoy: a cuánto cotiza este miércoles 6 de mayo</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ambito.com/finanzas/dolar-hoy-cuanto-cotiza-este-miercoles-6-mayo-n6274379</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>Ambito - Finanzas</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>Dólar blue hoy: a cuánto opera este miércoles 6 de mayo</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ambito.com/finanzas/dolar-blue-hoy-cuanto-opera-este-miercoles-6-mayo-n6274380</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>Ambito - Finanzas</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>El FGS de ANSES salió a comprar acciones y aumentó su participación en empresas: en qué invierte y cuál es el impacto</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ambito.com/finanzas/el-fgs-salio-comprar-acciones-y-aumento-su-participacion-empresas-que-invierte-y-cual-es-el-impacto-n6274661</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>Ambito - Finanzas</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>Se trata de una reconstrucción de Ámbito en base a los últimos datos disponibles a abril de 2025. ANSES no detalla la composición específica de las inversiones del FGS. En sectores clave como energía y servicios financieros, el incremento derivó en la designación de directores en asambleas. Desde la</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>El dólar oficial volvió a ceder y registró un mínimo de dos semanas</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ambito.com/finanzas/el-dolar-oficial-se-mantiene-debajo-los-1400-y-continua-su-alejamiento-del-techo-la-banda-n6274457</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>Ambito - Finanzas</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>La cotización del tipo de cambio estiró la brecha con la banda cambiaria, algo que le otorga más margen al Banco Central para intervenir en el MLC sin necesidad de vender.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>Qué implica la mejora de la calificadora de riesgo Fitch a la deuda argentina</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ambito.com/finanzas/que-implica-la-mejora-la-calificadora-riesgo-fitch-la-deuda-argentina-n6274509</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>Ambito - Finanzas</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>Tras conocerse la recalificación de la deuda por parte de Fitch se abre un universo de posibilidades.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Majo Aguilar responde a rumores de envidia y aclara comentarios sobre su prima Ángela Aguilar</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/mexico/2026/05/07/majo-aguilar-responde-a-rumores-de-envidia-y-aclara-comentarios-sobre-su-prima-angela-aguilar/</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>Un clip resurgido en redes sociales volvió a encender los rumores de enemistad entre las cantantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>Rally de acciones y bonos: los ADRs treparon hasta 11% y el riesgo país se hundió 7% tras la mejora de la nota soberana - Ambito</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNa0ZYU3UtNUU3SDY3RUE1NEFIMF85R0xpM2FGMnNreVpEd0xGRi1nOG5PNnZpTmpSQ2hKZ0QzZEd4bkItV3pKRGk3OHptc3B6MWExejRBV3djRkZPMEw5ZDVLVEdaT3hEUjBkS3p5YjNUWjNRQVpjaFZ3OFVpdEcwM19RUDBVSWRTcFVNdXhWamNnSktCOXl3MkwxQ1RqS0xNZUowZDBKalVTUlN2Y2pDMWpZTVhJUEFiaFU40gHAAUFVX3lxTE5PSF85OE02RW9vT053a3VZMnRGcG8wSTBKTEVhblI3REU4UkNHVGpiNVhGOVlaYV94dE1kRXpZTzFUTVB4NEhHNVJHYm9MeWZ0VEtHd3p0b1ZzNXV6V19qZ19sZ19BRWdqX1FwZEQ4RHFFaXRXS3kwTW8wcFBxTWkzV3hQenZ4YXM5TnlJRlJXQ2tkMk1yYXpSUlZ2a212U1RrNEJQdnNUeUtNWkZoYnBwVXFfTUE0LXhtSkF4Q3E4RQ?oc=5</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>Google News - Mercados</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>Financial Markets</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>Rally de acciones y bonos: los ADRs treparon hasta 11% y el riesgo país se hundió 7% tras la mejora de la nota soberana    Ambito</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>Una calificadora de riesgo de Estados Unidos elevó la nota de deuda soberana de la Argentina - Infobae</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQUC1pOUdHX0ppNkFzZ28ycWN4ZnI2c09HQ3hRMHdqZDBHSFNZaV9IbUt4R1hWal9UME1DX3FQNlBWRDYtQ0FkTjd5X1N2SjVTM3JjRUNQZ3Vtb3gyRTJnenduQjcxbldQdjFXNS11VjBnejBMRy1jN2xJbUFwdmNmMFg2bXhWUU1kRFdHYktHYWlkR3N6dGRSZjBUbjBxQl9oc3RXT0JRUzUwUmM1U0NSMWFVaTVfMzM1V01RbkY0NThqVU1Qb0hyNG5IY0hEMVA3bHpF0gHuAUFVX3lxTE4wSWZuemtEVFJDM2dMNUVrajg2R0FPQzdaMk80aElvRXpxaktnNmtrRVZPMEhYMXBkWTRJcGhySEFmLTJFVEFkZnU2SllFVFA3VTlSUHZlWGFVNzVzTEVlTWJ1ck9aQ3ZwQy1EcFItekFhMUp0ck1MRVVZN0hIdkd1d000NmdQT1dIRW9QZ0MxeU8xZTVNN3BjZXZ0TG9WN0tLamZWSkJUTDN5N01KNnFQY2FhTzE5QVd1MXZmVG5NT2p6bU0ySzhYVllLbjVoRmtKa3hGbnBRZFY0V2txU2h4QmxIZ0NmVU9xZnd1ZFE?oc=5</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>Google News - FMI</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>International Impact</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>Una calificadora de riesgo de Estados Unidos elevó la nota de deuda soberana de la Argentina    Infobae</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>Argentina recurrió a Estados Unidos para afrontar vencimientos con el FMI - Nueva Rioja</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNNmpoc19CODNGc2pPSTBta0JRWjN2ZXB4RWVBc3RGWDBUZUtWOEZfYVpXMXotV3NUeUE1Q2FOb0FuX3JKckZWR1pncmxSZzhCWTg5QTkwV2lhMTBNOFJ1cFNDSFdfaVdLcVpHTzh3RDZrRFZNRlllTm8xT2Ytd3NWSzdBazl1LUlLd3lvLU5VTDhjN0JneWt0VUJyTHNBN1FCMk84eXBrVUNfSXdBcXRlaE9B?oc=5</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>Google News - FMI</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>International Impact</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>Argentina recurrió a Estados Unidos para afrontar vencimientos con el FMI    Nueva Rioja</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>Exdirector del FMI ve acceso al mercado como llave para resolver la deuda argentina con el organismo - Bloomberg Línea</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxOeXRqcVlXUm9pelRfRTc5WXN4eEhSa3RmLUhYZTRJODdOTHhYVmM3OUxkaFRpaGxlV0dqdG5PUTFNbVFNdmN1RlJzUVFTUmc0ZVZUbFBkdklSZUQydm1WQUlyV1VJbVJyWEtXczRDdnpHcllHMTNHNllzSnJlbEpzRVU4b0xtMkpRS0laYkczRll0bTdYOHVwcFpLcUV5SDM1elAxX2tTQ3FqUm5Eb0dmUDlWTnpFNnJFRVV3TV9RdFNkcS1vMjEwU0pRWFZHbnNoek9xcTZWYldzX09Wdk1xUGhNeVM3bm1ZZjBybdIBgAJBVV95cUxOdllkZzdGeERqMktHNnRUTGdoSUxreEFZUWhZSkZtZ3lIVW96RzJORWM3aks3Z3JDNURSS0FzTVVCQWs4VVgzcEZENFZpcE1YT1ZtQXJURURWeFIxeEcyU3NkOVRONTVXdUJaRUtObi1YOUpKNXZMRGJGcTB1ZGU5WW1aQVRPU1I2emFzb3ZpMFdfbDRKR2NNdG9VaDMtSnZrVTgycFIwczlQdHZtdkdTMnZJQjJDWmtlQm5DZFdwZkRYZWx2T0VhQ0lpd3JRM0d5Nm5XM1RwVU1QNzRoTUFJbXRvd3JKX1poWDlTcWJPTTBIWkkxdlhGT1Y1T1ZFbVc2?oc=5</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>Google News - FMI</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>International Impact</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>Exdirector del FMI ve acceso al mercado como llave para resolver la deuda argentina con el organismo    Bloomberg Línea</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>La deuda externa más alta de la historia: cuánto endeudaron al Estado los últimos gobiernos - Enterate Noticias</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNNVF4UFVaY3AxdEphcWRsZldPbElSUW14b0haYVBzWjR3eGVTM3B6REdHN0pvOW5hZEJ2M00ySDdMZF9vVW9VOWpvY2VUcTJWMnl5YVpoN1pGSm50VEd0YXc3bUJvbmpYQ0E0ZTBiNksyWnByNHA3Y1dQdkkwODRzUGpsOEFtd29NQW9HMFU0QmQxOXdBNm1Rb1lTTTRtdkN3allTcC1fQ1FwWGVaTi1STnoyUzRKcFB2ZUp6VzlRUdIBuAFBVV95cUxQMVh5RWNDak5fTmYzUi16dGxXQnVERVJYQnNpSTMyNU1HUUlGcXBoQ0JYWGxFY1dJX3lYNTdacU9rQXpIV2E5dkN5UWZxMEJIal92UFBNaHRLeU55QVBSaGFLMUpYUnFMcGZJOFE3R3I1cHBLUnF2d0VaWW5GUFdSeVU3a2hyMmRYVWJUS2xUcXhtVmZRd0dyTUd6cjdGWkNIUXpwT0pORDZIOXg2UnBGQllBcnYxenJr?oc=5</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>Google News - FMI</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>International Impact</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>La deuda externa más alta de la historia: cuánto endeudaron al Estado los últimos gobiernos    Enterate Noticias</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>¿Cuánto endeudaron al Estado los últimos gobiernos y cuál es el saldo parcial de la gestión Milei? - Infobae</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNVFB0WTQ2ZG5RZ29lalVNNWwyS0NJdVljTzBSZ2F5MUFUT2tXLXF0ejhSVEJwVS1IWTlGT2Iza1RjYmxUR3daaVo0TXRkaFhuMWtkSjhLbDlNY3p5U2tfd2QtWFAxc0thOF9FYTZvQmQzYzZyWklpemw0SkREeXh6b3hDbGFUaXE5c3VDT2FadHZkbHZ6Z1puMUtNbzE2UzFjLVRkcGprb3R4cE13Z1hBajhNTnp1M09wcWgydGg3UFcxVXR6WEM1aW9XckI0VFlYdldUOFlGNEHSAfMBQVVfeXFMTmZ0LWdWTnJtc09OVWdHcTBRTW5heVJYTldjR3BoOExpZThHNlpUZXZQdXA5VU9nbWYzTlk2OVVzOFFRMk5UTUlTVXhmY2VXc09Wd0hOdnUtZUJQaWZpbnVZdXA2c3VxeW5ZU2I2ZjdkZGhJNUJobEt0RWktOG1VcWVDREoyaFdmTk1KTWlWdnhadVBnWXFxX3pKOFRBQy1Vd1RxYlEwMWZDM3NLNndUX1ZYcVZOaUpyMjFFY2g0UGd1WHFfZzFlbTU4dUkxZHNZVVEtdTNpNG5BQlNBMXV1SjgxMk10Q2cxZVpYdGM3NlJBdVhZ?oc=5</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>Google News - FMI</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>International Impact</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>¿Cuánto endeudaron al Estado los últimos gobiernos y cuál es el saldo parcial de la gestión Milei?    Infobae</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>La Argentina le compró DEG a Estados Unidos por US$819 millones para pagarle intereses al FMI - La Nación</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPUHQ2SDRDSnJLdzZfUGR2RjhidU42QWtHX1FZV2pDaDBIWVFkQ05SV3hYSUhnbDJEeHdicVlkWjgxVEU1b0xaZzY0c0UzQjc0cktVVEE4ZDkwSFZkc3d3MERyY3FIOU1NMnFqcTVYcHB1c0Zkd0F0NWNMQkNhZUZFU0hqd2dteFQ2NEVJVmZyX04yM1JFUjlNT1ZjdXB3T1JXTHluY0EtWnRrQXdUUzRkTWMteTRZdENXLUx5NDgtM2NIck5QT25wQ2RoRFJVYWZVcjdNaVEtWExyZw?oc=5</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>Google News - FMI</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>International Impact</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>La Argentina le compró DEG a Estados Unidos por US$819 millones para pagarle intereses al FMI    La Nación</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>Argentina recibirá nuevo desembolso del FMI por USD 1.000 millones: implicancias para el Banco Central y la deuda - MisionesOnline</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1hNE12OUpYRGg3Yk9Rc2VfMDB5SW1JcVV5bFc2aVNfMEhuNDFsellyTmNRd0ktMDkzbEFyd3pvLXBpR3h4NkNRdlFqZWpmcVVyYlNpTm53WnpxOGx0U0RYbjZIbkdPTXc0WFdZc3djdGxjY1FoRmhZVldQZ3E2dw?oc=5</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>Google News - FMI</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>International Impact</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>Argentina recibirá nuevo desembolso del FMI por USD 1.000 millones: implicancias para el Banco Central y la deuda    MisionesOnline</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>Deuda: el Gobierno volvió a comprarle DEGs a EEUU y le pagó u$s800 millones al FMI - Ambito</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPX01IRnBJTllEY2RRZlBQYkJMMjRlMFdLcVU5cGFJdTY3WkZaVjNOTVRfNmwxTkpNZHdxWnBpYmJRQzFvWkRyU1hkYk1XRjJ5eWxEZkFSSGFVcnhta0VqeU9nVGRCTTkzODJkcmY1ZEJaekNrWnZXcXhZSHpFVlJJYTdzRWdfcEUtZ0lGWFVFTHI1MzVwalROTGNKcW52QlZibzlsRdIBqgFBVV95cUxOcERfdkJYZS1iOE16TWpjQWZBTkZCekI3N3owR1R5eE9EMlFFcmRUb1pXZUpRWVJHME9VR3FYRThOSXhyTkVsWXdnb2o2S0hjUGRKRXRtelN5Z0pqekJJYlQwN19hMFFvU1VlVk02LVhVVmdxeGRSb3pEaW01SkpNeWs1VERTdVBjQ2JkcnNjYnM4dWMwLXhKeURZNWRLdjJ6RnBXTkRDSjIxdw?oc=5</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>Google News - FMI</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>International Impact</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>Deuda: el Gobierno volvió a comprarle DEGs a EEUU y le pagó u$s800 millones al FMI    Ambito</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>Uno de los negociadores de la deuda con el FMI en 2021 advierte que con Milei hoy es menos pagable - Perfil</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOejUtLVEtb1pLSTM2VXgxUXJGSm1RMFRDenFjRnhhSVU2ajZPMFpvYjI0T2ZBQVBhZTQyZmc2dkY2X3RsNjdDQjI4dDB2V3ZTdVlvM3FqZG5ZYXBLbXBUS2NlOHMxZEpVOXJ4LXlRaUJveUN3NHBMWUJMdjdyRHVZTnhPY2ppbFZYYkp5MmZGZjkwelZRTFg0RmlmVXFIbmpaSXdhQnBoSG1LUVRvUmR3OXRzanF6QmdIUmxlSVVRdWV0aURhTHZuQTdNWFZLUXlOczc2S1FtTUZMcjFickhWQlVZVjFiMmFlVTZKeXFWN3Rpd9IB9wFBVV95cUxQa2M1ekpER0wzTEI3R2VkX1JmbThDWUI0aFdYVEhFVmpteXhXOExwZTNudW51ay1uN1Y4ajhMRnNtNGNoamFZUVZJblJmMGpuR09EWkVfSTJ2eHIxVzNwZDVJRTRRWHAtVnM2Y0pTLXI3SXA2MkUzOHVjakJJd1pLb2lmamVtMWdkajZsX0FwenhHMFlDRDVPN18xOExEbjZUVDV6Rlc3WW42Szk1eGt4X2lWTHJFZVk4bTBWYmZtVVI2WVBtOE9sZnQweTdQc2thZWFIRi1WLVhLcTdYQ1A1aXZyWWVfVHBZU3FyaXQyVjFKUTFuZDhJ?oc=5</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>Google News - FMI</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>International Impact</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>Uno de los negociadores de la deuda con el FMI en 2021 advierte que con Milei hoy es menos pagable    Perfil</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>Deuda récord: supera los USD 483.000 millones y crecen los vencimientos de corto plazo para Nación - NEA HOY</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNMWl4TkFWdUsxeEN5eUJ4R2RwSDVSaTNLbGYybTA3WDROb29GZkU5QVo4VVczWVg4eFktdlg4SlZXbnpuX1doWHFnbEt6eHg2ZG9ZVEZiTjdKUjBSdElwXzRhVzJNellqQy1aaGRTN2pab0FQRGtmYVpmVHNoMjMwc3N5THV2RGxrbUozZ0hqRmhwTnUwQXlVZDZGaUNoX19MUjhfZGRfRnBNVnhjS3lZNS12dFRVaXhvT0JMMy1ORHV2ZXhhUm9B?oc=5</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>Google News - FMI</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>International Impact</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>Deuda récord: supera los USD 483.000 millones y crecen los vencimientos de corto plazo para Nación    NEA HOY</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>Argentina’s Javier Milei battered by scandals and slowing economy - Financial Times</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOLVlHVUJrTVQ4MFNhYWNsMHBDdWR3dHdWdDBnMHowdUdqS0wzRXoxUmIyQVlBOHYyTzF4LV9XNVVOcTE2V3J4TjZfSHI0TGgtalh4VG8tOGZNa3lYM3lyd1J0NXF3alFfaWY2OEtsNmpCZFBJQU9PNzhhYW1oWFpYamo3YVk?oc=5</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>Google News - Argentina EN</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>International Impact</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>Argentina’s Javier Milei battered by scandals and slowing economy    Financial Times</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>Tether leads $14M Series A in Argentine crypto fintech belo to scale stablecoins across LatAm - Tech Funding News</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQMWFFUjl1bmZpczFnU3dpUXQwckpsZWFmRFR5RkFVR2RxTmlrWjZVX2NIWFA0M1lUSnF0QWVRLXl1Zm5KUktOVXhib19LalgwUEdtdjRSR29xZVpHblg0ZW9YX2IwSEZCZXpfVUlaWkJWUmFJZGdNRXJkbnhSOURVSWJn?oc=5</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>Google News - LatAm Fintech</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>Fintech &amp; Innovation</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
         <is>
           <t>Tether leads $14M Series A in Argentine crypto fintech belo to scale stablecoins across LatAm    Tech Funding News</t>
         </is>

--- a/source_status.xlsx
+++ b/source_status.xlsx
@@ -692,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -802,12 +802,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Solo en Off | Sandra Pettovello y un viaje al Vaticano que despierta aplausos y celos en el Gabinete</t>
+          <t>“Se nos ocurrió probar”: fue sensación en Siberia y su llegada a la Patagonia cambió una historia</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/politica/solo-en-off-sandra-pettovello-y-un-viaje-al-vaticano-que-despierta-aplausos-y-celos-en-el-gabinete-nid11052026/</t>
+          <t>https://www.lanacion.com.ar/economia/campo/se-nos-ocurrio-probar-fue-sensacion-en-siberia-y-su-llegada-a-la-patagonia-cambio-una-historia-nid10052026/</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -827,19 +827,19 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Macri apunta a recuperar Boca; el rabino Wahnish tiene nueva discípula y la madre de Pinedo volvió al Partido Demócrata</t>
+          <t>Se trata de genética de maíz que hoy ensaya la firma Lilab SA en diversos puntos del sur; los híbridos lograron completar el ciclo y alcanzar rindes de hasta 10.000 kilos por hectárea</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>“Se nos ocurrió probar”: fue sensación en Siberia y su llegada a la Patagonia cambió una historia</t>
+          <t>Créditos hipotecarios: el dilema de los bancos para prestar a 20 o 30 años con los depósitos que captan a 30 días</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/economia/campo/se-nos-ocurrio-probar-fue-sensacion-en-siberia-y-su-llegada-a-la-patagonia-cambio-una-historia-nid10052026/</t>
+          <t>https://www.lanacion.com.ar/propiedades/casas-y-departamentos/creditos-hipotecarios-buscan-que-los-bancos-presten-a-20-o-30-anos-con-los-depositos-que-captan-a-30-nid10052026/</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,19 +859,19 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Se trata de genética de maíz que hoy ensaya la firma Lilab SA en diversos puntos del sur; los híbridos lograron completar el ciclo y alcanzar rindes de hasta 10.000 kilos por hectárea</t>
+          <t>Miguel Kiguel, Martín Redrado y Federico González Rouco coinciden en que la clave no pasa solo por estabilizar la macro, sino por destrabar el crédito hipotecario, un factor clave para cualquier país</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Créditos hipotecarios: el dilema de los bancos para prestar a 20 o 30 años con los depósitos que captan a 30 días</t>
+          <t>“De mayor escala del mundo”: Molinos Agro presentó un anteproyecto para invertir US$800 millones en un gigantesco complejo portuario e industrial</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/propiedades/casas-y-departamentos/creditos-hipotecarios-buscan-que-los-bancos-presten-a-20-o-30-anos-con-los-depositos-que-captan-a-30-nid10052026/</t>
+          <t>https://www.lanacion.com.ar/economia/campo/de-mayor-escala-del-mundo-molinos-agro-presento-un-anteproyecto-para-invertir-us800-millones-en-un-nid10052026/</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Miguel Kiguel, Martín Redrado y Federico González Rouco coinciden en que la clave no pasa solo por estabilizar la macro, sino por destrabar el crédito hipotecario, un factor clave para cualquier país</t>
+          <t>Se trata de un emprendimiento en Timbúes, Santa Fe, con tres líneas de procesamiento y molienda de oleaginosas con capacidad individual de 12.000 a 15.000 toneladas diarias, capacidad de almacenamiento de aproximadamente un millón de toneladas de granos y oleaginosas y dos muelles, entre otras carac</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>“De mayor escala del mundo”: Molinos Agro presentó un anteproyecto para invertir US$800 millones en un gigantesco complejo portuario e industrial</t>
+          <t>El Gobierno detectó sobreprecios de hasta 4239% en compras de andadores, sillas de ruedas y prótesis en el área de Discapacidad</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/economia/campo/de-mayor-escala-del-mundo-molinos-agro-presento-un-anteproyecto-para-invertir-us800-millones-en-un-nid10052026/</t>
+          <t>https://www.lanacion.com.ar/politica/el-gobierno-detecto-sobreprecios-de-hasta-4239-en-compras-de-andadores-sillas-de-ruedas-y-protesis-nid10052026/</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Se trata de un emprendimiento en Timbúes, Santa Fe, con tres líneas de procesamiento y molienda de oleaginosas con capacidad individual de 12.000 a 15.000 toneladas diarias, capacidad de almacenamiento de aproximadamente un millón de toneladas de granos y oleaginosas y dos muelles, entre otras carac</t>
+          <t>Un informe técnico del Ministerio de Salud, en manos de la Justicia, comparó facturas emitidas al Estado con otros precios de mercado y observó diferencias “injustificables”; el sistema que habría sido vulnerado</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Andrés Malamud y Astrid Pikielny presentaron “Operación Argentina”: una lectura de la democracia desde Alfonsín hasta Milei</t>
+          <t>Desconcierto y nuevas tensiones internas en el Gabinete tras la continuidad de Adorni</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/cultura/andres-malamud-y-astrid-pikielny-presentaron-operacion-argentina-una-lectura-de-la-democracia-desde-nid10052026/</t>
+          <t>https://www.lanacion.com.ar/politica/desconcierto-y-nuevas-tensiones-internas-en-el-gabinete-tras-la-continuidad-de-adorni-nid10052026/</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -982,29 +982,29 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>En la sala Pizarnik de la Feria del Libro, los autores analizaron las tensiones, contradicciones y desafíos que atravesó el país en las últimas décadas, junto a los periodistas Martín Rodríguez Yebra, Hinde Pomeraniec y Ernesto Tenembaum</t>
+          <t>En el Gobierno se acumulan incertidumbre, problemas de gestión y focos de conflicto; Milei bajó línea a favor de su funcionario y Bullrich mantuvo la postura díscola</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Desconcierto y nuevas tensiones internas en el Gabinete tras la continuidad de Adorni</t>
+          <t>Las importaciones de bienes de capital cayeron 7,8% en el primer trimestre</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/politica/desconcierto-y-nuevas-tensiones-internas-en-el-gabinete-tras-la-continuidad-de-adorni-nid10052026/</t>
+          <t>https://www.ambito.com/economia/las-importaciones-bienes-capital-cayeron-78-el-primer-trimestre-n6276012</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>LA NACION</t>
+          <t>Ambito - Economia</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1019,19 +1019,19 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>En el Gobierno se acumulan incertidumbre, problemas de gestión y focos de conflicto; Milei bajó línea a favor de su funcionario y Bullrich mantuvo la postura díscola</t>
+          <t>Las compras destinadas a inversión productiva sumaron u$s2.764 millones entre enero y marzo, con retrocesos en maquinaria y equipos, aunque crecieron los bienes vinculados al transporte.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>La venta de autos usados cayó 2,6% en abril y el sector apunta a las tasas de financiación</t>
+          <t>Orlando Ferreres estimó una inflación de 2,6% en abril y anticipó un posible rebote en mayo</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/la-venta-autos-usados-cayo-26-abril-y-el-sector-apunta-las-tasas-financiacion-n6275924</t>
+          <t>https://www.ambito.com/economia/orlando-ferreres-estimo-una-inflacion-26-abril-y-anticipo-un-posible-rebote-mayo-n6276010</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1051,19 +1051,19 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>En abril se comercializaron casi 155.000 vehículos usados, con una baja interanual del 2,62%. Desde el sector advirtieron que la financiación sigue siendo insuficiente y alertaron por la fuerte distorsión de precios en el mercado.</t>
+          <t>El economista señaló que la desaceleración estuvo impulsada por una menor suba en alimentos, aunque advirtió que los aumentos en tarifas, combustibles y transporte podrían volver a presionar los precios.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Las ventas minoristas pyme volvieron a caer en abril y acumulan una baja de 3,5% en 2026</t>
+          <t>Pablo Guidotti, exviceministro de Economía: "Domingo Cavallo se equivocó al decir que Luis Caputo es un trader sin teoría"</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/las-ventas-minoristas-pyme-volvieron-caer-abril-y-acumulan-una-baja-35-2026-n6275891</t>
+          <t>https://www.ambito.com/economia/pablo-guidotti-exviceministro-domingo-cavallo-se-equivoco-al-decir-que-luis-caputo-es-un-trader-teoria-n6275874</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1083,19 +1083,19 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>El comercio pyme registró una caída interanual del 3,2% durante abril, con retrocesos en seis de los siete rubros relevados por CAME. Aunque las ventas online mostraron una mejora, el consumo sigue golpeado por la pérdida de poder adquisitivo, el aumento de costos y la cautela de los hogares.</t>
+          <t>Guidotti cuestionó al exminitro de Economía por la caracterización que hizo del actual titular del Palacio de Hacienda. También analizó la mejora de Fitch, pero advirtió que no espera avances inmediatos de Moody’s ni de Standard &amp; Poor’s. Y pidió acelerar el regreso al mercado y acumular reservas.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Boom exportador y efecto "aspiradora": la economía crece, pero no derrama</t>
+          <t>La venta de autos usados cayó 2,6% en abril y el sector apunta a las tasas de financiación</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/boom-exportador-y-efecto-aspiradora-la-crece-pero-no-derrama-n6275770</t>
+          <t>https://www.ambito.com/economia/la-venta-autos-usados-cayo-26-abril-y-el-sector-apunta-las-tasas-financiacion-n6275924</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1115,19 +1115,19 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>El nuevo ciclo exportador mejora las cuentas externas, pero no logra reactivar el bolsillo. En la city ya hablan de un crecimiento concentrado, deterioro laboral y salarios en retroceso.</t>
+          <t>En abril se comercializaron casi 155.000 vehículos usados, con una baja interanual del 2,62%. Desde el sector advirtieron que la financiación sigue siendo insuficiente y alertaron por la fuerte distorsión de precios en el mercado.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Plazo fijo complicado: cuánto hay que invertir para generar una ganancia de $50.000 en 30 días</t>
+          <t>La venta de autos usados cayó 2,6% en abril y el sector apunta a las tasas de financiación</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/plazo-fijo-complicado-cuanto-hay-que-invertir-generar-una-ganancia-50000-30-dias-n6275595</t>
+          <t>https://www.ambito.com/economia/la-venta-autos-usados-cayo-26-abril-y-el-sector-apunta-las-tasas-financiacion-n6275924</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1147,19 +1147,19 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>La baja de tasas obliga a invertir millones para obtener rendimientos, que hace algunos meses se lograban con mucho menos capital.</t>
+          <t>En abril se comercializaron casi 155.000 vehículos usados, con una baja interanual del 2,62%. Desde el sector advirtieron que la financiación sigue siendo insuficiente y alertaron por la fuerte distorsión de precios en el mercado.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>La trampa de la nominalidad: por qué la tasa de los créditos actual es el mayor obstáculo para el rebote de la economía real</t>
+          <t>Las ventas minoristas pyme volvieron a caer en abril y acumulan una baja de 3,5% en 2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/la-trampa-la-nominalidad-que-la-tasa-los-creditos-actual-es-el-mayor-obstaculo-el-rebote-la-real-n6275831</t>
+          <t>https://www.ambito.com/economia/las-ventas-minoristas-pyme-volvieron-caer-abril-y-acumulan-una-baja-35-2026-n6275891</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1174,24 +1174,24 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Con una inflación proyectada del 24%, sostener tasas cercanas al 70% ahoga el consumo, dispara la morosidad y desnuda graves ineficiencias del sistema financiero.</t>
+          <t>El comercio pyme registró una caída interanual del 3,2% durante abril, con retrocesos en seis de los siete rubros relevados por CAME. Aunque las ventas online mostraron una mejora, el consumo sigue golpeado por la pérdida de poder adquisitivo, el aumento de costos y la cautela de los hogares.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>La economista Marina Dal Poggetto alertó por el costo de vida en dólares: "Está subiendo"</t>
+          <t>Boom exportador y efecto "aspiradora": la economía crece, pero no derrama</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/la-economista-marina-dal-poggetto-alerto-el-costo-vida-dolares-esta-subiendo-n6275797</t>
+          <t>https://www.ambito.com/economia/boom-exportador-y-efecto-aspiradora-la-crece-pero-no-derrama-n6275770</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1206,24 +1206,24 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>La directora de EcoGo evaluó el esquema del Gobierno, marcó la presión de los vencimientos de deuda y anticipó una nueva desaceleración de la inflación.</t>
+          <t>El nuevo ciclo exportador mejora las cuentas externas, pero no logra reactivar el bolsillo. En la city ya hablan de un crecimiento concentrado, deterioro laboral y salarios en retroceso.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>El precio de la carne frenó su escalada y no mostró variaciones en abril</t>
+          <t>Plazo fijo complicado: cuánto hay que invertir para generar una ganancia de $50.000 en 30 días</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/el-precio-la-carne-freno-escalada-y-no-mostro-variaciones-abril-n6275764</t>
+          <t>https://www.ambito.com/economia/plazo-fijo-complicado-cuanto-hay-que-invertir-generar-una-ganancia-50000-30-dias-n6275595</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1238,24 +1238,24 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Los incrementos venían acumulando un 10% mensual. No obstante, la carne vacuna sigue siendo la más cara.</t>
+          <t>La baja de tasas obliga a invertir millones para obtener rendimientos, que hace algunos meses se lograban con mucho menos capital.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>¿Rinde el plazo fijo?: cuánto podemos ganar si invertimos $1.000.000 a 30 días</t>
+          <t>La trampa de la nominalidad: por qué la tasa de los créditos actual es el mayor obstáculo para el rebote de la economía real</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/rinde-el-plazo-fijo-cuanto-podemos-ganar-si-invertimos-1000000-30-dias-n6275615</t>
+          <t>https://www.ambito.com/economia/la-trampa-la-nominalidad-que-la-tasa-los-creditos-actual-es-el-mayor-obstaculo-el-rebote-la-real-n6275831</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1275,19 +1275,19 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Las tasas siguen bajas y obligan a recalcular cuánto dinero deja realmente un depósito bancario a corto plazo.</t>
+          <t>Con una inflación proyectada del 24%, sostener tasas cercanas al 70% ahoga el consumo, dispara la morosidad y desnuda graves ineficiencias del sistema financiero.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Luis Caputo podría tener problemas para poner en marcha una medida clave de la reforma laboral</t>
+          <t>La economista Marina Dal Poggetto alertó por el costo de vida en dólares: "Está subiendo"</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/luis-caputo-podria-tener-problemas-poner-marcha-una-medida-clave-la-reforma-laboral-n6275518</t>
+          <t>https://www.ambito.com/economia/la-economista-marina-dal-poggetto-alerto-el-costo-vida-dolares-esta-subiendo-n6275797</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1307,19 +1307,19 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Está obligado a sostener el nivel de gasto en función de la evolución de la recaudación fiscal para llegar a la meta del 1,4% del superávit. En junio deberían arrancar los FAL que tienen costo de 0,37 puntos del PBI.</t>
+          <t>La directora de EcoGo evaluó el esquema del Gobierno, marcó la presión de los vencimientos de deuda y anticipó una nueva desaceleración de la inflación.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Pese a la pax financiera, en la city crecen las alertas por el freno de la economía real y el clima político</t>
+          <t>El precio de la carne frenó su escalada y no mostró variaciones en abril</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/pese-la-pax-financiera-la-city-crecen-las-alertas-el-freno-la-real-y-el-clima-politico-n6275546</t>
+          <t>https://www.ambito.com/economia/el-precio-la-carne-freno-escalada-y-no-mostro-variaciones-abril-n6275764</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1339,24 +1339,24 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Esta semana, la agencia calificadora Fitch mejoró la nota de la deuda soberana. Además el dato del IPI Industrial dio positivo. Pese a ello, en la city lanzan serias advertencias sobre la economía real y la imagen del Gobierno.</t>
+          <t>Los incrementos venían acumulando un 10% mensual. No obstante, la carne vacuna sigue siendo la más cara.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>El Banco Central compró más de US$ 7.000 millones en el primer cuatrimestre - Perfil</t>
+          <t>¿Rinde el plazo fijo?: cuánto podemos ganar si invertimos $1.000.000 a 30 días</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPVThjRG9tNTdFVjNISjN2VnY0QXFETnppdGVUVnVXci1tNTRTRTlKNkl6NHBFYkV3TE04RVBpWFpHdnN6T0ZfWlVpWU1oeDVCU3VUaVpnUDBKVW9sMDhUYzVHTHJ6QXdzWHN5MzdJajdUeVgzUnk0clg3OTNtOWtxX0hxb1pjVUYyd1NxRGtneFdFc3gzZDV3U2swbmg3RDA5MS1lZzktYXdxTmxxZWxuaFZ4bFVzT3dacG1ock130gHDAUFVX3lxTE9ycFFRWkVSWS1pNEh6ZFVORnBObHVJOERrd3pKS1VBaVlQSFhzUEFBaGo4UEtpQlFCZndpREdZOGxaS1M5UXBTMzhXX2VJMU15eFVFdVRzSGNjMDBscEFjNkFmRThTUEtaNXFiMkRVeXNrQVZvY1lHRUdIMUlSZWZrOXllT2dGVVVxa1R6c0pJWE9PRUlJVU9ZWkFBc3ItRENHOFcyRnlaUzExSlhOMnZjdEQxV0tMX2xKYl94TlNWdFMtNA?oc=5</t>
+          <t>https://www.ambito.com/economia/rinde-el-plazo-fijo-cuanto-podemos-ganar-si-invertimos-1000000-30-dias-n6275615</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Google News - BCRA</t>
+          <t>Ambito - Economia</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1366,29 +1366,29 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>El Banco Central compró más de US$ 7.000 millones en el primer cuatrimestre    Perfil</t>
+          <t>Las tasas siguen bajas y obligan a recalcular cuánto dinero deja realmente un depósito bancario a corto plazo.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>El BCRA reconoció presión inflacionaria, pero confía en una baja en los próximos meses - Diario Mendoza</t>
+          <t>Luis Caputo podría tener problemas para poner en marcha una medida clave de la reforma laboral</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOYlJwcGxycmdoQWo4allRYk04N09wY3EzOXVfVGhtSVdNNVcwenEydUtSMXo0ajZqNmxDaEg5QVlxNUN3VXZoOVNQS3NKU2RKcmdSTnZnZWY2bVNFZnR5eGdoZUY5WHVBWWl4dERma1VVQ21oNC10enBSenpIN1Y4Q2VyLW1zcFdJYU5xU25HVnhicmZWclVBVEZPRHZNaVpiOTFSckY5WUFyc1R5SDRmRkg5QUlLSEVGLU92eGpkZl9HQ0XSAcgBQVVfeXFMT19mQW9UemljUDJiZnJLd2Q0X2I1Z2F5NnotRzFucFphQm1FTWRld3lKTFJNaFBKS1JQY01lelVRUlJmV0tRdlRSb2ptcjJHNkJXQmd2VWM5eUFXZmVMN1VCXzFPbTRNRENQNl9SUTVfeHVWZjBJRlBKaGJPMHlRaENfXzRsWnh1MFZEYTZ5VmV4cGh3U204ZkpDVERId01TaEVzTzlLNmZjNjNaZ1NWUXZfbF93X3E0Vl9EV3F4NENFTVZLcWFzNWE?oc=5</t>
+          <t>https://www.ambito.com/economia/luis-caputo-podria-tener-problemas-poner-marcha-una-medida-clave-la-reforma-laboral-n6275518</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Google News - BCRA</t>
+          <t>Ambito - Economia</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1398,120 +1398,120 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>El BCRA reconoció presión inflacionaria, pero confía en una baja en los próximos meses    Diario Mendoza</t>
+          <t>Está obligado a sostener el nivel de gasto en función de la evolución de la recaudación fiscal para llegar a la meta del 1,4% del superávit. En junio deberían arrancar los FAL que tienen costo de 0,37 puntos del PBI.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Dólar blue hoy: a cuánto opera este lunes 11 de mayo</t>
+          <t>Pese a la pax financiera, en la city crecen las alertas por el freno de la economía real y el clima político</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/dolar-blue-hoy-cuanto-opera-este-lunes-11-mayo-n6276074</t>
+          <t>https://www.ambito.com/economia/pese-la-pax-financiera-la-city-crecen-las-alertas-el-freno-la-real-y-el-clima-politico-n6275546</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Ambito - Finanzas</t>
+          <t>Ambito - Economia</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Financial Markets</t>
+          <t>Macro &amp; Policy</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
+          <t>Esta semana, la agencia calificadora Fitch mejoró la nota de la deuda soberana. Además el dato del IPI Industrial dio positivo. Pese a ello, en la city lanzan serias advertencias sobre la economía real y la imagen del Gobierno.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Dólar hoy: a cuánto cotiza este lunes 11 de mayo</t>
+          <t>El Banco Central compró más de US$ 7.000 millones en el primer cuatrimestre - Perfil</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/dolar-hoy-cuanto-cotiza-este-lunes-11-mayo-n6276073</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPVThjRG9tNTdFVjNISjN2VnY0QXFETnppdGVUVnVXci1tNTRTRTlKNkl6NHBFYkV3TE04RVBpWFpHdnN6T0ZfWlVpWU1oeDVCU3VUaVpnUDBKVW9sMDhUYzVHTHJ6QXdzWHN5MzdJajdUeVgzUnk0clg3OTNtOWtxX0hxb1pjVUYyd1NxRGtneFdFc3gzZDV3U2swbmg3RDA5MS1lZzktYXdxTmxxZWxuaFZ4bFVzT3dacG1ock130gHDAUFVX3lxTE9ycFFRWkVSWS1pNEh6ZFVORnBObHVJOERrd3pKS1VBaVlQSFhzUEFBaGo4UEtpQlFCZndpREdZOGxaS1M5UXBTMzhXX2VJMU15eFVFdVRzSGNjMDBscEFjNkFmRThTUEtaNXFiMkRVeXNrQVZvY1lHRUdIMUlSZWZrOXllT2dGVVVxa1R6c0pJWE9PRUlJVU9ZWkFBc3ItRENHOFcyRnlaUzExSlhOMnZjdEQxV0tMX2xKYl94TlNWdFMtNA?oc=5</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Ambito - Finanzas</t>
+          <t>Google News - BCRA</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Financial Markets</t>
+          <t>Macro &amp; Policy</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
+          <t>El Banco Central compró más de US$ 7.000 millones en el primer cuatrimestre    Perfil</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Euro hoy y Euro blue hoy: a cuánto cotiza este lunes 11 de mayo</t>
+          <t>El BCRA reconoció presión inflacionaria, pero confía en una baja en los próximos meses - Diario Mendoza</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/euro-hoy-y-euro-blue-hoy-cuanto-cotiza-este-lunes-11-mayo-n6276023</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOYlJwcGxycmdoQWo4allRYk04N09wY3EzOXVfVGhtSVdNNVcwenEydUtSMXo0ajZqNmxDaEg5QVlxNUN3VXZoOVNQS3NKU2RKcmdSTnZnZWY2bVNFZnR5eGdoZUY5WHVBWWl4dERma1VVQ21oNC10enBSenpIN1Y4Q2VyLW1zcFdJYU5xU25HVnhicmZWclVBVEZPRHZNaVpiOTFSckY5WUFyc1R5SDRmRkg5QUlLSEVGLU92eGpkZl9HQ0XSAcgBQVVfeXFMT19mQW9UemljUDJiZnJLd2Q0X2I1Z2F5NnotRzFucFphQm1FTWRld3lKTFJNaFBKS1JQY01lelVRUlJmV0tRdlRSb2ptcjJHNkJXQmd2VWM5eUFXZmVMN1VCXzFPbTRNRENQNl9SUTVfeHVWZjBJRlBKaGJPMHlRaENfXzRsWnh1MFZEYTZ5VmV4cGh3U204ZkpDVERId01TaEVzTzlLNmZjNjNaZ1NWUXZfbF93X3E0Vl9EV3F4NENFTVZLcWFzNWE?oc=5</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Ambito - Finanzas</t>
+          <t>Google News - BCRA</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Financial Markets</t>
+          <t>Macro &amp; Policy</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Mirá a cuánto cotizan el euro oficial y el euro blue.</t>
+          <t>El BCRA reconoció presión inflacionaria, pero confía en una baja en los próximos meses    Diario Mendoza</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Real blue: a cuánto opera este lunes 11 de mayo</t>
+          <t>Dólar blue hoy: a cuánto opera este lunes 11 de mayo</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/real-blue-cuanto-opera-este-lunes-11-mayo-n6276025</t>
+          <t>https://www.ambito.com/finanzas/dolar-blue-hoy-cuanto-opera-este-lunes-11-mayo-n6276074</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1531,19 +1531,19 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>La cotización minuto a minuto para la compra y venta de la divisa brasileña en nuestro país.</t>
+          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Dólar hoy: a cuánto cotiza este domingo 10 de mayo</t>
+          <t>Dólar hoy: a cuánto cotiza este lunes 11 de mayo</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/dolar-hoy-cuanto-cotiza-este-domingo-10-mayo-n6275870</t>
+          <t>https://www.ambito.com/finanzas/dolar-hoy-cuanto-cotiza-este-lunes-11-mayo-n6276073</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1570,12 +1570,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Dólar blue hoy: a cuánto opera este domingo 10 de mayo</t>
+          <t>Euro hoy y Euro blue hoy: a cuánto cotiza este lunes 11 de mayo</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/dolar-blue-hoy-cuanto-opera-este-domingo-10-mayo-n6275871</t>
+          <t>https://www.ambito.com/finanzas/euro-hoy-y-euro-blue-hoy-cuanto-cotiza-este-lunes-11-mayo-n6276023</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1595,19 +1595,19 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
+          <t>Mirá a cuánto cotizan el euro oficial y el euro blue.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>El mercado se entusiasma tras la mejora de la nota de Fitch y se viene un nuevo dato de inflación: las claves de la semana</t>
+          <t>Real blue: a cuánto opera este lunes 11 de mayo</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/el-mercado-se-entusiasma-la-mejora-la-nota-fitch-y-se-viene-un-nuevo-dato-inflacion-las-claves-la-semana-n6275965</t>
+          <t>https://www.ambito.com/finanzas/real-blue-cuanto-opera-este-lunes-11-mayo-n6276025</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1622,24 +1622,24 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>La calificadora elevó la nota soberana de la Argentina y Moody’s dejó abierta la puerta a una futura mejora, aunque advirtió sobre el riesgo político y la inflación. En junio, el mercado también seguirá de cerca la revisión del MSCI, que podría volver a ubicar al país como “Mercado de Frontera”.</t>
+          <t>La cotización minuto a minuto para la compra y venta de la divisa brasileña en nuestro país.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Dólar blue hoy: a cuánto opera este sábado 9 de mayo</t>
+          <t>Dólar hoy: a cuánto cotiza este domingo 10 de mayo</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/dolar-blue-hoy-cuanto-opera-este-sabado-9-mayo-n6275711</t>
+          <t>https://www.ambito.com/finanzas/dolar-hoy-cuanto-cotiza-este-domingo-10-mayo-n6275870</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1666,12 +1666,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Wall Street cerró en máximos históricos impulsado por semiconductores y datos de empleo mejores a lo esperado</t>
+          <t>Dólar blue hoy: a cuánto opera este domingo 10 de mayo</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/wall-street-anticipa-alzas-la-espera-datos-clave-empleo-eeuu-y-crece-la-volatilidad-el-petroleo-n6275336</t>
+          <t>https://www.ambito.com/finanzas/dolar-blue-hoy-cuanto-opera-este-domingo-10-mayo-n6275871</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Los principales índices avanzaron con fuerza tras un informe laboral que alivió temores sobre la economía estadounidense, mientras las empresas de chips lideraron las subas del día. Aun así, la tensión en el estrecho de Ormuz mantuvo en alerta a los inversores por su impacto sobre el petróleo y la i</t>
+          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Lanzan 13 cedears de empresas vinculadas a la IA, energía y tierras raras: ¿cuáles son los más atractivos?</t>
+          <t>El mercado se entusiasma tras la mejora de la nota de Fitch y se viene un nuevo dato de inflación: las claves de la semana</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/lanzan-13-cedears-empresas-vinculadas-la-ia-energia-y-tierras-raras-cuales-son-los-mas-atractivos-n6275639</t>
+          <t>https://www.ambito.com/finanzas/el-mercado-se-entusiasma-la-mejora-la-nota-fitch-y-se-viene-un-nuevo-dato-inflacion-las-claves-la-semana-n6275965</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1718,24 +1718,24 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>La nueva tanda incorpora 13 compañías extranjeras al mercado local, con perfiles que van desde ciberseguridad, data centers y almacenamiento hasta petróleo, gas, uranio, real estate y pagos digitales.</t>
+          <t>La calificadora elevó la nota soberana de la Argentina y Moody’s dejó abierta la puerta a una futura mejora, aunque advirtió sobre el riesgo político y la inflación. En junio, el mercado también seguirá de cerca la revisión del MSCI, que podría volver a ubicar al país como “Mercado de Frontera”.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Dólar hoy y dólar blue hoy minuto a minuto: a cuánto opera este viernes 8 de mayo</t>
+          <t>Dólar blue hoy: a cuánto opera este sábado 9 de mayo</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/dolar-hoy-y-dolar-blue-hoy-minuto-minuto-cuanto-opera-este-viernes-8-mayo-n6275332</t>
+          <t>https://www.ambito.com/finanzas/dolar-blue-hoy-cuanto-opera-este-sabado-9-mayo-n6275711</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Top 3: los Cedears de acciones que saltaron más de 100% en el año</t>
+          <t>Dólar hoy: a cuánto cotiza este sábado 9 de mayo</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/top-3-los-cedears-acciones-que-saltaron-mas-100-el-ano-n6275476</t>
+          <t>https://www.ambito.com/finanzas/dolar-hoy-cuanto-cotiza-este-sabado-9-mayo-n6275710</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1782,24 +1782,24 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Se trata de Cedears que corresponden a empresas tecnológicas vinculadas a la inteligencia artificial, los chips y la industria espacial.</t>
+          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Acciones argentinas se hundieron hasta 12%, lideradas por Mercado Libre; pero el riesgo país cayó a mínimos de 3 meses</t>
+          <t>Bitcoin lucha por sostenerse arriba de los u$80.000, en medio de la guerra en Medio Oriente</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/las-acciones-y-los-bonos-se-encaminan-cerrar-la-semana-ganancias-n6275380</t>
+          <t>https://www.ambito.com/finanzas/bitcoin-retrocede-medio-la-tension-medio-oriente-pero-se-sostiene-los-u80000-n6275389</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1819,19 +1819,19 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Los bonos soberaros cerraron con firmes avances y el riesgo país cayó a mínimos de tres meses, ante la mejora de la nota de la deuda argentina por parte de la calificadora Fitch.</t>
+          <t>La escalada bélica en el estrecho de Ormuz presionó a la baja al mercado cripto durante la jornada, aunque analistas advierten que la acumulación de posiciones cortas podría desencadenar un rally explosivo hacia los u$s100.000.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Dólar blue planchado: sumó tres ruedas sin subas y quedó abajo del minorista por segunda semana</t>
+          <t>Wall Street cerró en máximos históricos impulsado por semiconductores y datos de empleo mejores a lo esperado</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/dolar-blue-planchado-sumo-tres-ruedas-subas-y-quedo-abajo-del-minorista-segunda-semana-n6275609</t>
+          <t>https://www.ambito.com/finanzas/wall-street-anticipa-alzas-la-espera-datos-clave-empleo-eeuu-y-crece-la-volatilidad-el-petroleo-n6275336</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1851,19 +1851,19 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>El tipo de cambio informal se mantiene sin cambios desde el pasado martes en la city porteña y está $20 por detrás del billete en bancos.</t>
+          <t>Los principales índices avanzaron con fuerza tras un informe laboral que alivió temores sobre la economía estadounidense, mientras las empresas de chips lideraron las subas del día. Aun así, la tensión en el estrecho de Ormuz mantuvo en alerta a los inversores por su impacto sobre el petróleo y la i</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>La morosidad en las familias tocó en marzo otro récord desde 2004, mientras el Gobierno busca contener el problema</t>
+          <t>Lanzan 13 cedears de empresas vinculadas a la IA, energía y tierras raras: ¿cuáles son los más atractivos?</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/la-morosidad-las-familias-toco-marzo-otro-record-2004-mientras-el-gobierno-busca-contener-el-problema-n6275549</t>
+          <t>https://www.ambito.com/finanzas/lanzan-13-cedears-empresas-vinculadas-la-ia-energia-y-tierras-raras-cuales-son-los-mas-atractivos-n6275639</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1883,19 +1883,19 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>La irregularidad de los créditos en los hogares alcanzó el 11,5%, su máximo nivel desde 2004, según 1816. De las 30 entidades más grandes que concentran el 96% del crédito, en 24 subió la mora durante marzo.</t>
+          <t>La nueva tanda incorpora 13 compañías extranjeras al mercado local, con perfiles que van desde ciberseguridad, data centers y almacenamiento hasta petróleo, gas, uranio, real estate y pagos digitales.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>El BCRA registró la mayor compra diaria del mes y las reservas volvieron a superar los u$s46.000 millones</t>
+          <t>Dólar hoy y dólar blue hoy minuto a minuto: a cuánto opera este viernes 8 de mayo</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/economia/el-bcra-sumo-80-ruedas-consecutivas-compradoras-y-las-reservas-aumentaron-us224-millones-n6274272</t>
+          <t>https://www.ambito.com/finanzas/dolar-hoy-y-dolar-blue-hoy-minuto-minuto-cuanto-opera-este-viernes-8-mayo-n6275332</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1915,19 +1915,19 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>La autoridad monetaria adquirió u$s110 millones, el monto más alto en lo que va mayo, y cerró la semana con un saldo comprador de u$s330 millones. Las reservas brutas subieron u$s105 millones, hasta u$s46.056 millones.</t>
+          <t>Conocé las cotizaciones dólar blue, el oficial, el MEP y el CCL.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>La presidenta del BCE cuestionó la emisión de stablecoins atadas al euro: cuál es la razón</t>
+          <t>Top 3: los Cedears de acciones que saltaron más de 100% en el año</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>https://www.ambito.com/finanzas/la-presidenta-del-bce-cuestiono-la-emision-stablecoins-atadas-al-euro-cual-es-la-razon-n6275519</t>
+          <t>https://www.ambito.com/finanzas/top-3-los-cedears-acciones-que-saltaron-mas-100-el-ano-n6275476</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1947,24 +1947,24 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Christine Lagarde, extitular del FMI, indicó que no es necesario esperar a una crisis vinculada al sector para poder prevenirla.</t>
+          <t>Se trata de Cedears que corresponden a empresas tecnológicas vinculadas a la inteligencia artificial, los chips y la industria espacial.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Monserrat Seminario se pronuncia por denuncia de apropiación ilícita de auto de ‘Melcochita’: “Es vengativo y doble cara”</t>
+          <t>Acciones argentinas se hundieron hasta 12%, lideradas por Mercado Libre; pero el riesgo país cayó a mínimos de 3 meses</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/peru/2026/05/11/monserrat-seminario-se-pronuncia-por-denuncia-de-apropiacion-ilicita-de-auto-de-melcochita-es-vengativo-y-doble-cara/</t>
+          <t>https://www.ambito.com/finanzas/las-acciones-y-los-bonos-se-encaminan-cerrar-la-semana-ganancias-n6275380</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Ambito - Finanzas</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1974,29 +1974,29 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>La modelo acusó a ‘Melcochita’ de actuar por venganza y afirmó que lleva más de tres meses sin recibir pensión para sus hijas</t>
+          <t>Los bonos soberaros cerraron con firmes avances y el riesgo país cayó a mínimos de tres meses, ante la mejora de la nota de la deuda argentina por parte de la calificadora Fitch.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>El lupus, una enfermedad invisible que condiciona la vida de quienes lo padecen: “Tu propio cuerpo se vuelve tu enemigo”</t>
+          <t>Dólar blue planchado: sumó tres ruedas sin subas y quedó abajo del minorista por segunda semana</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/espana/2026/05/11/el-lupus-una-enfermedad-invisible-que-condiciona-la-vida-de-quienes-lo-padecen-tu-propio-cuerpo-se-vuelve-tu-enemigo/</t>
+          <t>https://www.ambito.com/finanzas/dolar-blue-planchado-sumo-tres-ruedas-subas-y-quedo-abajo-del-minorista-segunda-semana-n6275609</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Ambito - Finanzas</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2006,29 +2006,29 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Una enfermedad autoinmune con la que miles de personas conviven a diario entre el dolor, el cansancio extremo y la incertidumbre</t>
+          <t>El tipo de cambio informal se mantiene sin cambios desde el pasado martes en la city porteña y está $20 por detrás del billete en bancos.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>El Gobierno modificó el Presupuesto 2026 y recortó casi $3 billones de diferentes partidas</t>
+          <t>La morosidad en las familias tocó en marzo otro récord desde 2004, mientras el Gobierno busca contener el problema</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/economia/2026/05/11/el-gobierno-nacional-modifico-el-prespuesto-2026-para-cumplir-con-el-plan-de-retiro-voluntario-de-la-anses/</t>
+          <t>https://www.ambito.com/finanzas/la-morosidad-las-familias-toco-marzo-otro-record-2004-mientras-el-gobierno-busca-contener-el-problema-n6275549</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Ambito - Finanzas</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2038,29 +2038,29 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Los cambios contemplan también créditos del Consejo de la Magistratura y la redistribución de cargos dentro de diferentes ministerios, y recortes de partidas por más de $2,4 billones</t>
+          <t>La irregularidad de los créditos en los hogares alcanzó el 11,5%, su máximo nivel desde 2004, según 1816. De las 30 entidades más grandes que concentran el 96% del crédito, en 24 subió la mora durante marzo.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Pronóstico del clima en Mazatlán para antes de salir de casa este 11 de mayo</t>
+          <t>El BCRA registró la mayor compra diaria del mes y las reservas volvieron a superar los u$s46.000 millones</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/mexico/2026/05/11/pronostico-del-clima-en-mazatlan-para-antes-de-salir-de-casa-este-11-de-mayo/</t>
+          <t>https://www.ambito.com/economia/el-bcra-sumo-80-ruedas-consecutivas-compradoras-y-las-reservas-aumentaron-us224-millones-n6274272</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Ambito - Finanzas</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2070,29 +2070,29 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>La temperatura más alta registrada en el país fue la del 6 de julio de 1966, cuando el termómetro subió hasta los 58.5 grados</t>
+          <t>La autoridad monetaria adquirió u$s110 millones, el monto más alto en lo que va mayo, y cerró la semana con un saldo comprador de u$s330 millones. Las reservas brutas subieron u$s105 millones, hasta u$s46.056 millones.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Bonos en dólares de Argentina suben tras mejora de calificación de Fitch - Perfil</t>
+          <t>La presidenta del BCE cuestionó la emisión de stablecoins atadas al euro: cuál es la razón</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMDdNb0t5eTJMakhGWk1kbUNBVHQxb2RzUktoRi1kXzRZeVBTS2JUQUo3VzVZdzBiWlBlV3BoVXhsZmFSeVQwTjhOaU1hb1NTNjRGdWloWEFtSDhrVWFaUEhlOWJ5ZlRlc2R3ejh2SWdNbG9ybERlbXMtZkhZSzc2eXhSZ2EyUFhoMXNEcllNdHJiTGlScG5uNFJWVXVZNFlOQWZiVUxibVFVbVFJOUV4UFdzdWFfc3RWdU9VTHlGTDbSAcYBQVVfeXFMTnVTUnhLUGpneGg2ajJLTVF0bndjNXFHWnhQSk9Jc3EzVVFlRkRmdXdNZTFmbWRGb2FaRVJCMjhYQ19hU0thcVlDaU1DdUtqSTQyOWhGWFllcVgxVEFvcGs5T2Z0dUNhZVFoUzlNbmFwTF9EOHl4YXNmY0xNYk8weDVCaFZRUlVTZWdLTTZRVUFRTV9PNWp2UDJBY0tweWFqVlYzX0YzOVdtcF8yYnVfdG1DN1hxaHlZdVpnbnNqQUdaYm5WaDdB?oc=5</t>
+          <t>https://www.ambito.com/finanzas/la-presidenta-del-bce-cuestiono-la-emision-stablecoins-atadas-al-euro-cual-es-la-razon-n6275519</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Google News - Mercados</t>
+          <t>Ambito - Finanzas</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2102,29 +2102,29 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Bonos en dólares de Argentina suben tras mejora de calificación de Fitch    Perfil</t>
+          <t>Christine Lagarde, extitular del FMI, indicó que no es necesario esperar a una crisis vinculada al sector para poder prevenirla.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Bolivia y Ecuador emitieron bonos por u$s 2000 millones: ¿cuándo será el turno de Argentina? - El Cronista</t>
+          <t>El dolor de cabeza en la menopausia: cómo evitarlo, por qué se produce y qué hacer en estos casos</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOR3RwcWJLcmN6UkkyOGRpMUFwVHktSll5UU4tOTl5MnhOX2Q5VXJUVVFNT3pDclVaVzcybmljVkpVYmRwWEg0blZXNUN0bHlkeHRmOXZ2S2VUcEdfWTY4UHhiZzFwMmgwZmNFdkExQm03UDQ0NnZsdlQxdGtJRnFCS1R5NWVzNGRWa2dtODBhQ29wMlNycmh5bjg2c2VOOWNqSjJadFp5cjhPRUhtTHpPTEJsbjh6NUc5MkxQRUpzSkR2VWlpN0NaMVN4cTHSAecBQVVfeXFMTi1MektMV2Z4NlJwdC1ybXJyQnNsdWotS21Zam44MlMxQWg0YURuUTVGNnBtNDNleFRoczRrNjhYeVhCTmdEMmN2bkdDUzF4SllwNHdCTXJwVDVOZExhc2ZlV3BFemR0SnBCUFFRR2dreHg3VEs4RWFZZ1RySVZ2ZTUwMVlSczk3anExV0pwa20wNjJYbXpJbXFnUnJKRkRUem9VckRKWnc0X2FFRC1KU01oX0lDWTBOUVZ3M1A0STE2NkJiN0VZYkxaREdpQ0tLVkxvU3RJeGtJb3MyeUJnVzNhVzluSFBj?oc=5</t>
+          <t>https://www.infobae.com/espana/2026/05/11/el-dolor-de-cabeza-en-la-menopausia-como-evitarlo-por-que-se-produce-y-que-hacer-en-estos-casos/</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Google News - Mercados</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2134,29 +2134,29 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Bolivia y Ecuador emitieron bonos por u$s 2000 millones: ¿cuándo será el turno de Argentina?    El Cronista</t>
+          <t>La migraña asociada a la menopausia responde a una caída abrupta de los estrógenos</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Rally de acciones y bonos: los ADRs treparon hasta 11% y el riesgo país se hundió 7% tras la mejora de la nota soberana - Ambito</t>
+          <t>El misterioso mensaje de Ángela Aguilar en redes sociales tras la polémica del cuarto de la hija de Nodal y Cazzu</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNa0ZYU3UtNUU3SDY3RUE1NEFIMF85R0xpM2FGMnNreVpEd0xGRi1nOG5PNnZpTmpSQ2hKZ0QzZEd4bkItV3pKRGk3OHptc3B6MWExejRBV3djRkZPMEw5ZDVLVEdaT3hEUjBkS3p5YjNUWjNRQVpjaFZ3OFVpdEcwM19RUDBVSWRTcFVNdXhWamNnSktCOXl3MkwxQ1RqS0xNZUowZDBKalVTUlN2Y2pDMWpZTVhJUEFiaFU40gHAAUFVX3lxTE5PSF85OE02RW9vT053a3VZMnRGcG8wSTBKTEVhblI3REU4UkNHVGpiNVhGOVlaYV94dE1kRXpZTzFUTVB4NEhHNVJHYm9MeWZ0VEtHd3p0b1ZzNXV6V19qZ19sZ19BRWdqX1FwZEQ4RHFFaXRXS3kwTW8wcFBxTWkzV3hQenZ4YXM5TnlJRlJXQ2tkMk1yYXpSUlZ2a212U1RrNEJQdnNUeUtNWkZoYnBwVXFfTUE0LXhtSkF4Q3E4RQ?oc=5</t>
+          <t>https://www.infobae.com/mexico/2026/05/11/el-misterioso-mensaje-de-angela-aguilar-en-redes-sociales-tras-la-polemica-del-cuarto-de-la-hija-de-nodal-y-cazzu/</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Google News - Mercados</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2166,268 +2166,396 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Rally de acciones y bonos: los ADRs treparon hasta 11% y el riesgo país se hundió 7% tras la mejora de la nota soberana    Ambito</t>
+          <t>Horas después de que Nodal publicara el cuarto decorado para su hija, la cantante también reactivó su canal de WhatsApp y su Instagram</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>¿Cuánto endeudaron al Estado los últimos gobiernos y cuál es el saldo parcial de la gestión Milei? - Infobae</t>
+          <t>Pumas vence al América por global de 6-6 y se enfrentará a Pachuca en semifinales: así fueron los goles</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNVFB0WTQ2ZG5RZ29lalVNNWwyS0NJdVljTzBSZ2F5MUFUT2tXLXF0ejhSVEJwVS1IWTlGT2Iza1RjYmxUR3daaVo0TXRkaFhuMWtkSjhLbDlNY3p5U2tfd2QtWFAxc0thOF9FYTZvQmQzYzZyWklpemw0SkREeXh6b3hDbGFUaXE5c3VDT2FadHZkbHZ6Z1puMUtNbzE2UzFjLVRkcGprb3R4cE13Z1hBajhNTnp1M09wcWgydGg3UFcxVXR6WEM1aW9XckI0VFlYdldUOFlGNEHSAfMBQVVfeXFMTmZ0LWdWTnJtc09OVWdHcTBRTW5heVJYTldjR3BoOExpZThHNlpUZXZQdXA5VU9nbWYzTlk2OVVzOFFRMk5UTUlTVXhmY2VXc09Wd0hOdnUtZUJQaWZpbnVZdXA2c3VxeW5ZU2I2ZjdkZGhJNUJobEt0RWktOG1VcWVDREoyaFdmTk1KTWlWdnhadVBnWXFxX3pKOFRBQy1Vd1RxYlEwMWZDM3NLNndUX1ZYcVZOaUpyMjFFY2g0UGd1WHFfZzFlbTU4dUkxZHNZVVEtdTNpNG5BQlNBMXV1SjgxMk10Q2cxZVpYdGM3NlJBdVhZ?oc=5</t>
+          <t>https://www.infobae.com/mexico/deportes/2026/05/10/pumas-vs-america-en-vivo-universitarios-y-aguilas-se-enfrentan-en-el-olimpico-universitario-tras-el-3-3-en-la-ida/</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Google News - FMI</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>International Impact</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>¿Cuánto endeudaron al Estado los últimos gobiernos y cuál es el saldo parcial de la gestión Milei?    Infobae</t>
+          <t>Gracias a los goles de Duarte, Nathan y Carrillo, los auriazules ganan encuentro en el Olímpico Universitario</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Argentina - Resources, Power, Economy - Britannica</t>
+          <t>Los nuevos nominados y la despedida de Sandra Barneda a Nagore marcan la noche de ‘Supervivientes’: “Me ha sabido muy mal”</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5OaWRwb2M3MHFRX2kzRERsVEhjRnJiNTFnRTBPdXVYSFplUlJ1UGJOWFJocWc1TWxlOU5XUU1Cb3VuSzJBN1lfVUIzanBMSnM3MGdBaEI5NFZwQ193YXI5MUNVR21pbW1SeEZLa1QyNA?oc=5</t>
+          <t>https://www.infobae.com/espana/2026/05/11/los-nuevos-nominados-y-la-despedida-de-sandra-barneda-a-nagore-marcan-la-noche-de-supervivientes-me-ha-sabido-muy-mal/</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Google News - Argentina EN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>International Impact</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Argentina - Resources, Power, Economy    Britannica</t>
+          <t>La colaboradora televisiva ha sido la última expulsada del programa de supervivencia</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Argentina’s Javier Milei battered by scandals and slowing economy - Financial Times</t>
+          <t>Preocupación de los analistas por el aumento de la morosidad y el futuro electoral: rescatan una mejor calificación de la deuda</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOLVlHVUJrTVQ4MFNhYWNsMHBDdWR3dHdWdDBnMHowdUdqS0wzRXoxUmIyQVlBOHYyTzF4LV9XNVVOcTE2V3J4TjZfSHI0TGgtalh4VG8tOGZNa3lYM3lyd1J0NXF3alFfaWY2OEtsNmpCZFBJQU9PNzhhYW1oWFpYamo3YVk?oc=5</t>
+          <t>https://www.infobae.com/economia/2026/05/11/preocupacion-de-los-analistas-por-el-aumento-de-la-morosidad-y-el-futuro-electoral-rescatan-una-mejor-calificacion-de-la-deuda/</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Google News - Argentina EN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>International Impact</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Argentina’s Javier Milei battered by scandals and slowing economy    Financial Times</t>
+          <t>En la noche del domingo en el frente internacional, el overnite anticipaba otra jornada tensa, puesto que los 3 principales indicadores de Nueva York operaban en rojo</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Buenos Aires - Financial Hub, Trade, Manufacturing - Britannica</t>
+          <t>Autoridades de agricultura advierten pérdidas por sequía y piden cambiar estrategias de siembra en varias regiones de Honduras</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTFBkdDB4SEV3UENlWDZIZnhKUzkyVnYyZ0MzQWNvZExERjZJYjBZQ2dxV3ZhSDBUbFdUV0ZZcDdvcUhjbEEwVkh3WE5MZFhBcTcwamdLTWhXNWlVdHQyUmw2MjJOSQ?oc=5</t>
+          <t>https://www.infobae.com/honduras/2026/05/11/autoridades-de-agricultura-advierten-perdidas-por-sequia-y-piden-cambiar-estrategias-de-siembra-en-varias-regiones-de-honduras/</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Google News - Argentina EN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>International Impact</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Buenos Aires - Financial Hub, Trade, Manufacturing    Britannica</t>
+          <t>El sector agrícola advierte sobre la necesidad de ajustar los ciclos de siembra ante la proyección de lluvias irregulares y temperaturas elevadas, lo que pone en riesgo la producción de granos en varias zonas del país.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Startup argentina impulsa bancos y billeteras: trabaja con YPF y llega a Latinoamérica - iProUP</t>
+          <t>Bonos en dólares de Argentina suben tras mejora de calificación de Fitch - Perfil</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQZmVGTE0wM2wzazBJZER0NlRaYURVdFNaQXoyTkM2WkFIUDAtUVpORmJLOVVNTXkteUNIaWF2X21aU0ZaR2tmcDVjeHFDOVRtMVN0NUtrNW4xWjBFcDNNN2R4cU9OXzZsaE53Ynp3VzRBbHFqTFRvcjlwdVhsZ0dTMmIzZlRrcldCeU84eEQxdkFNY2NMLTh0Q3NBTDUxTFduXzBrSVpDV0hWU18xVFpjZdIBtgFBVV95cUxNel9pZHE3WFNaWlNQYjhjZlZwZUxLaE01czRzYU5Rd2pBWFpEY044dU5DelJaSkpoazgtV21pNnRTenl6bWdkSzl0WlJIZE5udmlUdEZIaHNCRUhXODJYN0pfYnVsR0JJRlBjb0psTGdaR0VpVDlBbVBFdS10RktFR0xXdDMtMFhKQnhQSlQ4dHpOMlVhcHpYSl9LWVFrbzBqamFoYkJsSnBXOVZYSEhLaW1HTE1RZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMDdNb0t5eTJMakhGWk1kbUNBVHQxb2RzUktoRi1kXzRZeVBTS2JUQUo3VzVZdzBiWlBlV3BoVXhsZmFSeVQwTjhOaU1hb1NTNjRGdWloWEFtSDhrVWFaUEhlOWJ5ZlRlc2R3ejh2SWdNbG9ybERlbXMtZkhZSzc2eXhSZ2EyUFhoMXNEcllNdHJiTGlScG5uNFJWVXVZNFlOQWZiVUxibVFVbVFJOUV4UFdzdWFfc3RWdU9VTHlGTDbSAcYBQVVfeXFMTnVTUnhLUGpneGg2ajJLTVF0bndjNXFHWnhQSk9Jc3EzVVFlRkRmdXdNZTFmbWRGb2FaRVJCMjhYQ19hU0thcVlDaU1DdUtqSTQyOWhGWFllcVgxVEFvcGs5T2Z0dUNhZVFoUzlNbmFwTF9EOHl4YXNmY0xNYk8weDVCaFZRUlVTZWdLTTZRVUFRTV9PNWp2UDJBY0tweWFqVlYzX0YzOVdtcF8yYnVfdG1DN1hxaHlZdVpnbnNqQUdaYm5WaDdB?oc=5</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Google News - Fintech AR</t>
+          <t>Google News - Mercados</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Fintech &amp; Innovation</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Startup argentina impulsa bancos y billeteras: trabaja con YPF y llega a Latinoamérica    iProUP</t>
+          <t>Bonos en dólares de Argentina suben tras mejora de calificación de Fitch    Perfil</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Tether leads $14M Series A in Argentine crypto fintech belo to scale stablecoins across LatAm - Tech Funding News</t>
+          <t>Bolivia y Ecuador emitieron bonos por u$s 2000 millones: ¿cuándo será el turno de Argentina? - El Cronista</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQMWFFUjl1bmZpczFnU3dpUXQwckpsZWFmRFR5RkFVR2RxTmlrWjZVX2NIWFA0M1lUSnF0QWVRLXl1Zm5KUktOVXhib19LalgwUEdtdjRSR29xZVpHblg0ZW9YX2IwSEZCZXpfVUlaWkJWUmFJZGdNRXJkbnhSOURVSWJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOR3RwcWJLcmN6UkkyOGRpMUFwVHktSll5UU4tOTl5MnhOX2Q5VXJUVVFNT3pDclVaVzcybmljVkpVYmRwWEg0blZXNUN0bHlkeHRmOXZ2S2VUcEdfWTY4UHhiZzFwMmgwZmNFdkExQm03UDQ0NnZsdlQxdGtJRnFCS1R5NWVzNGRWa2dtODBhQ29wMlNycmh5bjg2c2VOOWNqSjJadFp5cjhPRUhtTHpPTEJsbjh6NUc5MkxQRUpzSkR2VWlpN0NaMVN4cTHSAecBQVVfeXFMTi1MektMV2Z4NlJwdC1ybXJyQnNsdWotS21Zam44MlMxQWg0YURuUTVGNnBtNDNleFRoczRrNjhYeVhCTmdEMmN2bkdDUzF4SllwNHdCTXJwVDVOZExhc2ZlV3BFemR0SnBCUFFRR2dreHg3VEs4RWFZZ1RySVZ2ZTUwMVlSczk3anExV0pwa20wNjJYbXpJbXFnUnJKRkRUem9VckRKWnc0X2FFRC1KU01oX0lDWTBOUVZ3M1A0STE2NkJiN0VZYkxaREdpQ0tLVkxvU3RJeGtJb3MyeUJnVzNhVzluSFBj?oc=5</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Google News - LatAm Fintech</t>
+          <t>Google News - Mercados</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Fintech &amp; Innovation</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Tether leads $14M Series A in Argentine crypto fintech belo to scale stablecoins across LatAm    Tech Funding News</t>
+          <t>Bolivia y Ecuador emitieron bonos por u$s 2000 millones: ¿cuándo será el turno de Argentina?    El Cronista</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Tether backs Argentine fintech belo in bid to expand Latin America stablecoin payments - Trade Finance Global</t>
+          <t>Rally de acciones y bonos: los ADRs treparon hasta 11% y el riesgo país se hundió 7% tras la mejora de la nota soberana - Ambito</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeWFLWGNwU2RmeTJrVlg4NjR2SE5CZXhYam5Lb2MtZzRTR1U0ck9EOURkTDhYQVVzcml3TFo4TDA2ZmltSzFUSVY4Z3c3Mm1NY1BMdmhNaGlRYUVNc2d0NDJKOC14dWJGVnVET21LUEctbVFhc3dSbVdiVDU1dmZIRDhuclZtWGs5VnFOWUFVUXNpeEhVSE9rOG8xdFQ3ak9fZmk2OUpJWXZ6Yng5YTVxUlpBN0tBOUdBT1F1LU41TQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNa0ZYU3UtNUU3SDY3RUE1NEFIMF85R0xpM2FGMnNreVpEd0xGRi1nOG5PNnZpTmpSQ2hKZ0QzZEd4bkItV3pKRGk3OHptc3B6MWExejRBV3djRkZPMEw5ZDVLVEdaT3hEUjBkS3p5YjNUWjNRQVpjaFZ3OFVpdEcwM19RUDBVSWRTcFVNdXhWamNnSktCOXl3MkwxQ1RqS0xNZUowZDBKalVTUlN2Y2pDMWpZTVhJUEFiaFU40gHAAUFVX3lxTE5PSF85OE02RW9vT053a3VZMnRGcG8wSTBKTEVhblI3REU4UkNHVGpiNVhGOVlaYV94dE1kRXpZTzFUTVB4NEhHNVJHYm9MeWZ0VEtHd3p0b1ZzNXV6V19qZ19sZ19BRWdqX1FwZEQ4RHFFaXRXS3kwTW8wcFBxTWkzV3hQenZ4YXM5TnlJRlJXQ2tkMk1yYXpSUlZ2a212U1RrNEJQdnNUeUtNWkZoYnBwVXFfTUE0LXhtSkF4Q3E4RQ?oc=5</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Google News - LatAm Fintech</t>
+          <t>Google News - Mercados</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Fintech &amp; Innovation</t>
+          <t>Financial Markets</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Tether backs Argentine fintech belo in bid to expand Latin America stablecoin payments    Trade Finance Global</t>
+          <t>Rally de acciones y bonos: los ADRs treparon hasta 11% y el riesgo país se hundió 7% tras la mejora de la nota soberana    Ambito</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Tether Backs Argentine Fintech belo With $14M to Expand Stablecoin Use in Latin America - CryptoRank</t>
+          <t>Argentina - Resources, Power, Economy - Britannica</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOajQwbU5JWHdQWGMxeFpxSlZFR3NPOFpNS0FKbWtqWlpzT1BZZ2dYZUlnMWxkZ3F1SDQ2N18tdEhWMVluLTVsbkhqeFdOYnpKaWFWbFU5U2U3M2kwVkx4by1NZlJBZDdtS0tucFFWRkU5RmJEejdubmVTSjg5Q2dseUZTdGk4dXBuNzdUYUlrSklZNUVWenh2RUx6b2h0SHpLNU05c1FiZk85dG5kQnJjUjNwVEhTN3BiSXlhNTJ3WDRfUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5OaWRwb2M3MHFRX2kzRERsVEhjRnJiNTFnRTBPdXVYSFplUlJ1UGJOWFJocWc1TWxlOU5XUU1Cb3VuSzJBN1lfVUIzanBMSnM3MGdBaEI5NFZwQ193YXI5MUNVR21pbW1SeEZLa1QyNA?oc=5</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>Google News - Argentina EN</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>International Impact</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Argentina - Resources, Power, Economy    Britannica</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Buenos Aires - Financial Hub, Trade, Manufacturing - Britannica</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTFBkdDB4SEV3UENlWDZIZnhKUzkyVnYyZ0MzQWNvZExERjZJYjBZQ2dxV3ZhSDBUbFdUV0ZZcDdvcUhjbEEwVkh3WE5MZFhBcTcwamdLTWhXNWlVdHQyUmw2MjJOSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Google News - Argentina EN</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>International Impact</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Buenos Aires - Financial Hub, Trade, Manufacturing    Britannica</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Startup argentina impulsa bancos y billeteras: trabaja con YPF y llega a Latinoamérica - iProUP</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQZmVGTE0wM2wzazBJZER0NlRaYURVdFNaQXoyTkM2WkFIUDAtUVpORmJLOVVNTXkteUNIaWF2X21aU0ZaR2tmcDVjeHFDOVRtMVN0NUtrNW4xWjBFcDNNN2R4cU9OXzZsaE53Ynp3VzRBbHFqTFRvcjlwdVhsZ0dTMmIzZlRrcldCeU84eEQxdkFNY2NMLTh0Q3NBTDUxTFduXzBrSVpDV0hWU18xVFpjZdIBtgFBVV95cUxNel9pZHE3WFNaWlNQYjhjZlZwZUxLaE01czRzYU5Rd2pBWFpEY044dU5DelJaSkpoazgtV21pNnRTenl6bWdkSzl0WlJIZE5udmlUdEZIaHNCRUhXODJYN0pfYnVsR0JJRlBjb0psTGdaR0VpVDlBbVBFdS10RktFR0xXdDMtMFhKQnhQSlQ4dHpOMlVhcHpYSl9LWVFrbzBqamFoYkJsSnBXOVZYSEhLaW1HTE1RZw?oc=5</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Google News - Fintech AR</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Fintech &amp; Innovation</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Startup argentina impulsa bancos y billeteras: trabaja con YPF y llega a Latinoamérica    iProUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Tether leads $14M Series A in Argentine crypto fintech belo to scale stablecoins across LatAm - Tech Funding News</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQMWFFUjl1bmZpczFnU3dpUXQwckpsZWFmRFR5RkFVR2RxTmlrWjZVX2NIWFA0M1lUSnF0QWVRLXl1Zm5KUktOVXhib19LalgwUEdtdjRSR29xZVpHblg0ZW9YX2IwSEZCZXpfVUlaWkJWUmFJZGdNRXJkbnhSOURVSWJn?oc=5</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
           <t>Google News - LatAm Fintech</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Fintech &amp; Innovation</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Tether Backs Argentine Fintech belo With $14M to Expand Stablecoin Use in Latin America    CryptoRank</t>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Tether leads $14M Series A in Argentine crypto fintech belo to scale stablecoins across LatAm    Tech Funding News</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Tether backs Argentine fintech belo in bid to expand Latin America stablecoin payments - Trade Finance Global</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeWFLWGNwU2RmeTJrVlg4NjR2SE5CZXhYam5Lb2MtZzRTR1U0ck9EOURkTDhYQVVzcml3TFo4TDA2ZmltSzFUSVY4Z3c3Mm1NY1BMdmhNaGlRYUVNc2d0NDJKOC14dWJGVnVET21LUEctbVFhc3dSbVdiVDU1dmZIRDhuclZtWGs5VnFOWUFVUXNpeEhVSE9rOG8xdFQ3ak9fZmk2OUpJWXZ6Yng5YTVxUlpBN0tBOUdBT1F1LU41TQ?oc=5</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Google News - LatAm Fintech</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Fintech &amp; Innovation</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Tether backs Argentine fintech belo in bid to expand Latin America stablecoin payments    Trade Finance Global</t>
         </is>
       </c>
     </row>
